--- a/public/Raja_Sansi_2022_Assembly_Booth_Results.xlsx
+++ b/public/Raja_Sansi_2022_Assembly_Booth_Results.xlsx
@@ -626,7 +626,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L224"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="38" customWidth="1" min="2" max="2"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Mukhwinder Singh Mahal (BJP)</t>
+          <t>Mukhwinder Singh (BJP)</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -710,17 +710,17 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>ਗੁਲਗੜ + ਨਿਆਮਤਾਬਾਦ</t>
+          <t>ਗੁਲਗੜ੍ਹ</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>ਗੁਲਗੜ + ਨਿਆਮਤਾਬਾਦ</t>
+          <t>ਗੁਲਗੜ੍ਹ</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Gulgarh + Niamatabad</t>
+          <t>Gulgarh</t>
         </is>
       </c>
       <c r="E2" s="4" t="n">
@@ -757,17 +757,17 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>ਅਵਾਨ ਬਸਾਊ + ਡਿਆਲ</t>
+          <t>ਅਵਾਨ ਬਸਾਊ</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>ਅਵਾਨ ਬਸਾਊ + ਡਿਆਲ</t>
+          <t>ਅਵਾਨ ਬਸਾਊ</t>
         </is>
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>Awan Basau + Dial</t>
+          <t>Awan Basau</t>
         </is>
       </c>
       <c r="E3" s="8" t="n">
@@ -814,7 +814,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Awan Basau</t>
+          <t>Awan Bassau</t>
         </is>
       </c>
       <c r="E4" s="4" t="n">
@@ -945,17 +945,17 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>ਬੁਰਜ + ਛਿੰਡੀ ਨੈਣ</t>
+          <t>ਬੁਰਜ</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>ਬੁਰਜ + ਛਿੰਡੀ ਨੈਣ</t>
+          <t>ਬੁਰਜ</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Burj + Chindi Nain</t>
+          <t>Burj</t>
         </is>
       </c>
       <c r="E7" s="8" t="n">
@@ -1039,12 +1039,12 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>ਭਿੰਡੀ ਅੌਲਖ ਕਲਾਂ</t>
+          <t>ਭਿੰਡੀ ਔਲਖ ਕਲਾਂ</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>ਭਿੰਡੀ ਅੌਲਖ ਕਲਾਂ</t>
+          <t>ਭਿੰਡੀ ਔਲਖ ਕਲਾਂ</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>ਭਿੰਡੀ ਅੌਲਖ ਕਲਾਂ</t>
+          <t>ਭਿੰਡੀ ਔਲਖ ਕਲਾਂ</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>ਭਿੰਡੀ ਅੌਲਖ ਕਲਾਂ</t>
+          <t>ਭਿੰਡੀ ਔਲਖ ਕਲਾਂ</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -1133,17 +1133,17 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>ਝੁੰਜ</t>
+          <t>ਭਿੰਡੀ ਔਲਖ ਖੁਰਦ</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>ਝੁੰਜ</t>
+          <t>ਭਿੰਡੀ ਔਲਖ ਖੁਰਦ</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Jhunj</t>
+          <t>Bhindi Aulakh Khurd</t>
         </is>
       </c>
       <c r="E11" s="8" t="n">
@@ -1180,17 +1180,17 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>ਭਿੰਡੀ ਅੌਲਖ ਖੁਰਦ</t>
+          <t>ਜਸਰੌਰ</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>ਭਿੰਡੀ ਅੌਲਖ ਖੁਰਦ</t>
+          <t>ਜਸਰੌਰ</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Bhindi Aulakh Khurd</t>
+          <t>Jasarour</t>
         </is>
       </c>
       <c r="E12" s="4" t="n">
@@ -1227,17 +1227,17 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>ਭਿੰਡੀ ਅੌਲਖ ਖੁਰਦ</t>
+          <t>ਜਸਰੌਰ</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>ਭਿੰਡੀ ਅੌਲਖ ਖੁਰਦ</t>
+          <t>ਜਸਰੌਰ</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Bhindi Aulakh Khurd</t>
+          <t>Jasarour</t>
         </is>
       </c>
       <c r="E13" s="8" t="n">
@@ -1274,17 +1274,17 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>ਜਸਰੌਰ</t>
+          <t>ਕੋਟਲਾ ਸੂਰਜ ਲੋਹਾਰ</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>ਜਸਰੌਰ</t>
+          <t>ਕੋਟਲਾ ਸੂਰਜ ਲੋਹਾਰ</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>Jasraur</t>
+          <t>Kotla Suraaj Lohar</t>
         </is>
       </c>
       <c r="E14" s="4" t="n">
@@ -1321,17 +1321,17 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>ਜਸਰੌਰ</t>
+          <t>ਮੋਤਲਾ</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>ਜਸਰੌਰ</t>
+          <t>ਮੋਤਲਾ</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Jasraur</t>
+          <t>Motala</t>
         </is>
       </c>
       <c r="E15" s="8" t="n">
@@ -1368,17 +1368,17 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>ਕੋਟਲਾ ਸੁਰਾਜ ਲੋਹਾਰ + ਜੈ ਰਾਮ ਕੋਟ</t>
+          <t>ਕੋਟਲੀ ਖੇੜਾ</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>ਕੋਟਲਾ ਸੁਰਾਜ ਲੋਹਾਰ + ਜੈ ਰਾਮ ਕੋਟ</t>
+          <t>ਕੋਟਲੀ ਖੇੜਾ</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Kotla Suraj Lohar + Jai Ram Kot</t>
+          <t>Kotli Khera</t>
         </is>
       </c>
       <c r="E16" s="4" t="n">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>ਮੇਤਲਾ</t>
+          <t>ਪੰਜੂ ਕਲਾਲ</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>ਮੇਤਲਾ</t>
+          <t>ਪੰਜੂ ਕਲਾਲ</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Metla</t>
+          <t>Panju Kalal</t>
         </is>
       </c>
       <c r="E17" s="8" t="n">
@@ -1462,17 +1462,17 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>ਕੋਟਲੀ ਖਹਿਰਾ + ਵੰਡਾਲ + ਭਲੋਟ</t>
+          <t>ਸ਼ਾਹਪੁਰ</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>ਕੋਟਲੀ ਖਹਿਰਾ + ਵੰਡਾਲ + ਭਲੋਟ</t>
+          <t>ਸ਼ਾਹਪੁਰ</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Kotli Khaira + Vandal + Bhalot</t>
+          <t>Shahpur</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
@@ -1509,17 +1509,17 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>ਪੰਜ ਕਲਾ + ਚੱਕ ਬਾਜੀਦ</t>
+          <t>ਭਿੰਡੀ ਸੈਦਾਂ</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>ਪੰਜ ਕਲਾ + ਚੱਕ ਬਾਜੀਦ</t>
+          <t>ਭਿੰਡੀ ਸੈਦਾਂ</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Panj Kala + Chak Bajid</t>
+          <t>Bhindi Saidan</t>
         </is>
       </c>
       <c r="E19" s="8" t="n">
@@ -1556,17 +1556,17 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>ਸ਼ਾਹਪੁਰ + ਮਿਆਦੀ ਖੁਰਦ + ਆਲਮਪੁਰ + ਚੱਕ ਫਤਿਹ ਖਾਂ</t>
+          <t>ਭਿੰਡੀ ਸੈਦਾਂ</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>ਸ਼ਾਹਪੁਰ + ਮਿਆਦੀ ਖੁਰਦ + ਆਲਮਪੁਰ + ਚੱਕ ਫਤਿਹ ਖਾਂ</t>
+          <t>ਭਿੰਡੀ ਸੈਦਾਂ</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Shahpur + Miadi Khurd + Alampur + Chak Fateh Khan</t>
+          <t>Bhindi Saidan</t>
         </is>
       </c>
       <c r="E20" s="4" t="n">
@@ -1885,17 +1885,17 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>ਭਿੰਡੀ ਸੈਦਾਂ</t>
+          <t>ਕੁੱਤੀਵਾਲ</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>ਭਿੰਡੀ ਸੈਦਾਂ</t>
+          <t>ਕੁੱਤੀਵਾਲ</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>Bhindi Saidan</t>
+          <t>Kuttiwal</t>
         </is>
       </c>
       <c r="E27" s="8" t="n">
@@ -1932,17 +1932,17 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>ਭਿੰਡੀ ਸੈਦਾਂ</t>
+          <t>ਕੋਟਲੀ ਦੁਸੰਧੀ</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>ਭਿੰਡੀ ਸੈਦਾਂ</t>
+          <t>ਕੋਟਲੀ ਦੁਸੰਧੀ</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Bhindi Saidan</t>
+          <t>Kotli Dosandhi</t>
         </is>
       </c>
       <c r="E28" s="4" t="n">
@@ -1979,17 +1979,17 @@
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>ਕੁੱਤੀਵਾਲ</t>
+          <t>ਕੋਟਲੀ ਦੁਸੰਧੀ</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>ਕੁੱਤੀਵਾਲ</t>
+          <t>ਕੋਟਲੀ ਦੁਸੰਧੀ</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>Kuttiwal</t>
+          <t>Kotli Dosandhi</t>
         </is>
       </c>
       <c r="E29" s="8" t="n">
@@ -2026,17 +2026,17 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>ਕੋਟਲੀ ਦੋਸੰਧੀ</t>
+          <t>ਭਾਗੂਪੁਰ ਬੇਟ</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>ਕੋਟਲੀ ਦੋਸੰਧੀ</t>
+          <t>ਭਾਗੂਪੁਰ ਬੇਟ</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Kotli Dosandhi</t>
+          <t>Bhagupur Bet</t>
         </is>
       </c>
       <c r="E30" s="4" t="n">
@@ -2073,17 +2073,17 @@
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>ਕੋਟਲੀ ਦੇਸਾਂ</t>
+          <t>ਵੇਹੜਾ</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>ਕੋਟਲੀ ਦੇਸਾਂ</t>
+          <t>ਵੇਹੜਾ</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>Kotli Desan</t>
+          <t>Vehra</t>
         </is>
       </c>
       <c r="E31" s="8" t="n">
@@ -2120,17 +2120,17 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>ਭੱਗੂਪੁਰ ਬੇਟ</t>
+          <t>ਦੁੱਗ</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>ਭੱਗੂਪੁਰ ਬੇਟ</t>
+          <t>ਦੁੱਗ</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Bhaggupur Bet</t>
+          <t>Dugg</t>
         </is>
       </c>
       <c r="E32" s="4" t="n">
@@ -2167,17 +2167,17 @@
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>ਵਿਹੜਾ + ਵਿਹੜਾ ਅਬਾਦੀ ਵਾਲਾ ਨੂਰੇਵਾਲ</t>
+          <t>ਦੁੱਗ ਡੋਗਰ</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>ਵਿਹੜਾ + ਵਿਹੜਾ ਅਬਾਦੀ ਵਾਲਾ ਨੂਰੇਵਾਲ</t>
+          <t>ਦੁੱਗ ਡੋਗਰ</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>Vehra + Vehra Abadi Wala Nurewal</t>
+          <t>Dugg Dogar</t>
         </is>
       </c>
       <c r="E33" s="8" t="n">
@@ -2214,17 +2214,17 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>ਡੱਗ</t>
+          <t>ਸੈਦਪੁਰ ਕਲਾਂ</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>ਡੱਗ</t>
+          <t>ਸੈਦਪੁਰ ਕਲਾਂ</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Dagg</t>
+          <t>Saidpur Kalan</t>
         </is>
       </c>
       <c r="E34" s="4" t="n">
@@ -2261,17 +2261,17 @@
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>ਡੱਗ ਡੋਗਰ</t>
+          <t>ਤੂਤ</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>ਡੱਗ ਡੋਗਰ</t>
+          <t>ਤੂਤ</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>Dagg Dogar</t>
+          <t>Toot</t>
         </is>
       </c>
       <c r="E35" s="8" t="n">
@@ -2308,17 +2308,17 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>ਸੈਦਪੁਰ ਕਲਾਂ</t>
+          <t>ਛੰਨ ਕਲਾਂ</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>ਸੈਦਪੁਰ ਕਲਾਂ</t>
+          <t>ਛੰਨ ਕਲਾਂ</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Saidpur Kalan</t>
+          <t>Chhan Kalan</t>
         </is>
       </c>
       <c r="E36" s="4" t="n">
@@ -2355,17 +2355,17 @@
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>ਤੁਤ</t>
+          <t>ਮੋਹਲੇਕੇ</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>ਤੁਤ</t>
+          <t>ਮੋਹਲੇਕੇ</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>Tut</t>
+          <t>Mohaleke</t>
         </is>
       </c>
       <c r="E37" s="8" t="n">
@@ -2402,17 +2402,17 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>ਛੰਨ ਕਲਾਂ</t>
+          <t>ਮੰਡੀਆਵਾਲਾ</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>ਛੰਨ ਕਲਾਂ</t>
+          <t>ਮੰਡੀਆਵਾਲਾ</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Chhann Kalan</t>
+          <t>Mandiawala</t>
         </is>
       </c>
       <c r="E38" s="4" t="n">
@@ -2449,17 +2449,17 @@
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>ਮੇਹਲੇਕੇ</t>
+          <t>ਲੋਧੀ ਗੁੱਜਰ</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>ਮੇਹਲੇਕੇ</t>
+          <t>ਲੋਧੀ ਗੁੱਜਰ</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>Mehleke</t>
+          <t>Lodhi Gujjar</t>
         </is>
       </c>
       <c r="E39" s="8" t="n">
@@ -2496,17 +2496,17 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>ਮੰਡਿਆਵਾਲਾ</t>
+          <t>ਮੰਜ</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>ਮੰਡਿਆਵਾਲਾ</t>
+          <t>ਮੰਜ</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>Mandiawala</t>
+          <t>Manj</t>
         </is>
       </c>
       <c r="E40" s="4" t="n">
@@ -2543,17 +2543,17 @@
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>ਲੇਪੀ ਗੁੱਜਰ</t>
+          <t>ਕੱਕੜ</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>ਲੇਪੀ ਗੁੱਜਰ</t>
+          <t>ਕੱਕੜ</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>Lepi Gujjar</t>
+          <t>Kakkar</t>
         </is>
       </c>
       <c r="E41" s="8" t="n">
@@ -2590,17 +2590,17 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>ਨਵਾ ਜੀਵਨ + ਨਥੂਪੁਰਾ</t>
+          <t>ਕੱਕੜ</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>ਨਵਾ ਜੀਵਨ + ਨਥੂਪੁਰਾ</t>
+          <t>ਕੱਕੜ</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>Nawa Jeevan + Nathupura</t>
+          <t>Kakkar</t>
         </is>
       </c>
       <c r="E42" s="4" t="n">
@@ -2637,17 +2637,17 @@
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>ਮੰਜ</t>
+          <t>ਕੱਕੜ</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>ਮੰਜ</t>
+          <t>ਕੱਕੜ</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>Manj</t>
+          <t>Kakkar</t>
         </is>
       </c>
       <c r="E43" s="8" t="n">
@@ -2684,17 +2684,17 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>ਮੰਜ + ਦਸਮੇਸ਼ ਨਗਰ</t>
+          <t>ਕੱਕੜ</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>ਮੰਜ + ਦਸਮੇਸ਼ ਨਗਰ</t>
+          <t>ਕੱਕੜ</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>Manj + Dasmesh Nagar</t>
+          <t>Kakkar</t>
         </is>
       </c>
       <c r="E44" s="4" t="n">
@@ -2731,17 +2731,17 @@
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>ਕੱਕੜ</t>
+          <t>ਰਾਣੀਆਂ</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>ਕੱਕੜ</t>
+          <t>ਰਾਣੀਆਂ</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>Kakkar</t>
+          <t>Ranian</t>
         </is>
       </c>
       <c r="E45" s="8" t="n">
@@ -2778,17 +2778,17 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>ਕੱਕੜ</t>
+          <t>ਚੱਕ ਅੱਲਾ ਬਖ਼ਸ਼</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>ਕੱਕੜ</t>
+          <t>ਚੱਕ ਅੱਲਾ ਬਖ਼ਸ਼</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>Kakkar</t>
+          <t>Chakk Alla Bakhsh</t>
         </is>
       </c>
       <c r="E46" s="4" t="n">
@@ -2825,17 +2825,17 @@
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>ਕੱਕੜ</t>
+          <t>ਧਾਰੀਵਾਲ</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>ਕੱਕੜ</t>
+          <t>ਧਾਰੀਵਾਲ</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>Kakkar</t>
+          <t>Dhariwal</t>
         </is>
       </c>
       <c r="E47" s="8" t="n">
@@ -2872,17 +2872,17 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>ਕੱਕੜ</t>
+          <t>ਪੰਡੋਰੀ</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>ਕੱਕੜ</t>
+          <t>ਪੰਡੋਰੀ</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>Kakkar</t>
+          <t>Pandori</t>
         </is>
       </c>
       <c r="E48" s="4" t="n">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>ਰਾਣੀਆਂ</t>
+          <t>ਰਾਏ</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>ਰਾਣੀਆਂ</t>
+          <t>ਰਾਏ</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>Rania</t>
+          <t>Rai</t>
         </is>
       </c>
       <c r="E49" s="8" t="n">
@@ -2966,17 +2966,17 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>ਚੱਕ ਅੱਲਾ ਬਖਸ਼</t>
+          <t>ਗੱਗੜਮੱਲ</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>ਚੱਕ ਅੱਲਾ ਬਖਸ਼</t>
+          <t>ਗੱਗੜਮੱਲ</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>Chak Alla Baksh</t>
+          <t>Gagarmal</t>
         </is>
       </c>
       <c r="E50" s="4" t="n">
@@ -3013,17 +3013,17 @@
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>ਧਾਰੀਵਾਲ + ਉਧਰ + ਮੁਲਾ ਕੋਟ</t>
+          <t>ਸਾਰੰਗੜਾ</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>ਧਾਰੀਵਾਲ + ਉਧਰ + ਮੁਲਾ ਕੋਟ</t>
+          <t>ਸਾਰੰਗੜਾ</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>Dhariwal + Udhar + Mulla Kot</t>
+          <t>Sarangra</t>
         </is>
       </c>
       <c r="E51" s="8" t="n">
@@ -3060,17 +3060,17 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>ਪੰਡੇਰੀ + ਮੱਧਪੁਰਾ</t>
+          <t>ਸਾਰੰਗੜਾ</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>ਪੰਡੇਰੀ + ਮੱਧਪੁਰਾ</t>
+          <t>ਸਾਰੰਗੜਾ</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>Panderi + Madhpura</t>
+          <t>Sarangra</t>
         </is>
       </c>
       <c r="E52" s="4" t="n">
@@ -3107,17 +3107,17 @@
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>ਰਾਏ</t>
+          <t>ਸਾਰੰਗੜਾ</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>ਰਾਏ</t>
+          <t>ਸਾਰੰਗੜਾ</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>Rai</t>
+          <t>Sarangra</t>
         </is>
       </c>
       <c r="E53" s="8" t="n">
@@ -3154,17 +3154,17 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>ਗਾਗਰਾਮਲ</t>
+          <t>ਲੇਲੀਅਨ</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>ਗਾਗਰਾਮਲ</t>
+          <t>ਲੇਲੀਅਨ</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>Gagramal</t>
+          <t>Lelian</t>
         </is>
       </c>
       <c r="E54" s="4" t="n">
@@ -3201,17 +3201,17 @@
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>ਸਾਰੰਗੜਾ</t>
+          <t>ਪੰਜੂ ਰਾਏ</t>
         </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>ਸਾਰੰਗੜਾ</t>
+          <t>ਪੰਜੂ ਰਾਏ</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>Sarangra</t>
+          <t>Panju Rai</t>
         </is>
       </c>
       <c r="E55" s="8" t="n">
@@ -3248,17 +3248,17 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>ਸਾਰੰਗੜਾ</t>
+          <t>ਹੇਤਮਪੁਰਾ</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>ਸਾਰੰਗੜਾ</t>
+          <t>ਹੇਤਮਪੁਰਾ</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>Sarangra</t>
+          <t>Hetampura</t>
         </is>
       </c>
       <c r="E56" s="4" t="n">
@@ -3295,17 +3295,17 @@
       </c>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>ਸਾਰੰਗੜਾ</t>
+          <t>ਕੰਵੈ</t>
         </is>
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>ਸਾਰੰਗੜਾ</t>
+          <t>ਕੰਵੈ</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>Sarangra</t>
+          <t>Kanve</t>
         </is>
       </c>
       <c r="E57" s="8" t="n">
@@ -3342,17 +3342,17 @@
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>ਲੇਲੀਆਂ</t>
+          <t>ਲੋਪੋਕੇ</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>ਲੇਲੀਆਂ</t>
+          <t>ਲੋਪੋਕੇ</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>Lelian</t>
+          <t>Lopoke</t>
         </is>
       </c>
       <c r="E58" s="4" t="n">
@@ -3389,17 +3389,17 @@
       </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>ਪੰਜ ਰਾਏ</t>
+          <t>ਲੋਪੋਕੇ</t>
         </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>ਪੰਜ ਰਾਏ</t>
+          <t>ਲੋਪੋਕੇ</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>Panj Rai</t>
+          <t>Lopoke</t>
         </is>
       </c>
       <c r="E59" s="8" t="n">
@@ -3436,17 +3436,17 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>ਹੇਤਮਪੁਰਾ</t>
+          <t>ਲੋਪੋਕੇ</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>ਹੇਤਮਪੁਰਾ</t>
+          <t>ਲੋਪੋਕੇ</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>Hetampura</t>
+          <t>Lopoke</t>
         </is>
       </c>
       <c r="E60" s="4" t="n">
@@ -3483,17 +3483,17 @@
       </c>
       <c r="B61" s="7" t="inlineStr">
         <is>
-          <t>ਕਾਂਦੇ</t>
+          <t>ਲੋਪੋਕੇ</t>
         </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>ਕਾਂਦੇ</t>
+          <t>ਲੋਪੋਕੇ</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>Kande</t>
+          <t>Lopoke</t>
         </is>
       </c>
       <c r="E61" s="8" t="n">
@@ -3530,17 +3530,17 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>ਲੇਪੋਕੇ</t>
+          <t>ਲੋਪੋਕੇ</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>ਲੇਪੋਕੇ</t>
+          <t>ਲੋਪੋਕੇ</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>Lepoke</t>
+          <t>Lopoke</t>
         </is>
       </c>
       <c r="E62" s="4" t="n">
@@ -3577,17 +3577,17 @@
       </c>
       <c r="B63" s="7" t="inlineStr">
         <is>
-          <t>ਲੇਪੋਕੇ</t>
+          <t>ਪ੍ਰੀਤ ਨਗਰ</t>
         </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>ਲੇਪੋਕੇ</t>
+          <t>ਪ੍ਰੀਤ ਨਗਰ</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>Lepoke</t>
+          <t>Preet Nagar</t>
         </is>
       </c>
       <c r="E63" s="8" t="n">
@@ -3624,17 +3624,17 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>ਲੇਪੋਕੇ</t>
+          <t>ਵੇਰੋਕੇ</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>ਲੇਪੋਕੇ</t>
+          <t>ਵੇਰੋਕੇ</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>Lepoke</t>
+          <t>Veroke</t>
         </is>
       </c>
       <c r="E64" s="4" t="n">
@@ -3671,17 +3671,17 @@
       </c>
       <c r="B65" s="7" t="inlineStr">
         <is>
-          <t>ਲੇਪੋਕੇ</t>
+          <t>ਭਿਲੋਵਾਲ ਕਾਕੇ ਜੀ</t>
         </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
-          <t>ਲੇਪੋਕੇ</t>
+          <t>ਭਿਲੋਵਾਲ ਕਾਕੇ ਜੀ</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>Lepoke</t>
+          <t>Bhilaowal Kakeji</t>
         </is>
       </c>
       <c r="E65" s="8" t="n">
@@ -3718,17 +3718,17 @@
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>ਲੇਪੋਕੇ</t>
+          <t>ਭਾਗੂਪੁਰ ਉਤਾੜ</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>ਲੇਪੋਕੇ</t>
+          <t>ਭਾਗੂਪੁਰ ਉਤਾੜ</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>Lepoke</t>
+          <t>Bhagupur Utarh</t>
         </is>
       </c>
       <c r="E66" s="4" t="n">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="B67" s="7" t="inlineStr">
         <is>
-          <t>ਪ੍ਰੀਤ ਨਗਰ ਰ.ਬ.ਨੰ. 167 + ਓਵਰਸੀਜ਼ ਇਲੈਕਟਰ</t>
+          <t>ਭਿਲੋਵਾਲ ਪੱਕਾ</t>
         </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>ਪ੍ਰੀਤ ਨਗਰ ਰ.ਬ.ਨੰ. 167 + ਓਵਰਸੀਜ਼ ਇਲੈਕਟਰ</t>
+          <t>ਭਿਲੋਵਾਲ ਪੱਕਾ</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>Preet Nagar R.B.No. 167 + Overseas Elector</t>
+          <t>Bhillowal Pakka</t>
         </is>
       </c>
       <c r="E67" s="8" t="n">
@@ -3812,17 +3812,17 @@
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>ਵੈਰੋਕੇ</t>
+          <t>ਮੁੱਢ</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>ਵੈਰੋਕੇ</t>
+          <t>ਮੁੱਢ</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>Vairoke</t>
+          <t>Mudh</t>
         </is>
       </c>
       <c r="E68" s="4" t="n">
@@ -3859,17 +3859,17 @@
       </c>
       <c r="B69" s="7" t="inlineStr">
         <is>
-          <t>ਭੀਲੇਵਾਲ ਕਕੇਜੀ</t>
+          <t>ਚੂਚਕਵਾਲ</t>
         </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>ਭੀਲੇਵਾਲ ਕਕੇਜੀ</t>
+          <t>ਚੂਚਕਵਾਲ</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>Bhilewal Kakeji</t>
+          <t>Chuchakwal</t>
         </is>
       </c>
       <c r="E69" s="8" t="n">
@@ -3906,17 +3906,17 @@
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>ਭੱਗੂਪੁਰ ਉਤਾੜ + ਛੰਨਾ</t>
+          <t>ਅਵਾਨ ਲੱਖਾ ਸਿੰਘ</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>ਭੱਗੂਪੁਰ ਉਤਾੜ + ਛੰਨਾ</t>
+          <t>ਅਵਾਨ ਲੱਖਾ ਸਿੰਘ</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>Bhaggupur Utar + Chhanna</t>
+          <t>Awan Lakha Singh</t>
         </is>
       </c>
       <c r="E70" s="4" t="n">
@@ -3953,17 +3953,17 @@
       </c>
       <c r="B71" s="7" t="inlineStr">
         <is>
-          <t>ਭੀਲੇਵਾਲ ਪੱਕਾ</t>
+          <t>ਵੜਿਆਹ</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>ਭੀਲੇਵਾਲ ਪੱਕਾ</t>
+          <t>ਵੜਿਆਹ</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>Bhilewal Pakka</t>
+          <t>Waryah</t>
         </is>
       </c>
       <c r="E71" s="8" t="n">
@@ -4000,17 +4000,17 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>ਮੁੱਧ</t>
+          <t>ਖੁਸੂਪੁਰਾ</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>ਮੁੱਧ</t>
+          <t>ਖੁਸੂਪੁਰਾ</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>Muddh</t>
+          <t>Khusupura</t>
         </is>
       </c>
       <c r="E72" s="4" t="n">
@@ -4047,17 +4047,17 @@
       </c>
       <c r="B73" s="7" t="inlineStr">
         <is>
-          <t>ਚੁਚਕਵਾਲ + ਮੁਜੱਫਰਪੁਰਾ</t>
+          <t>ਤਰੀਨ</t>
         </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>ਚੁਚਕਵਾਲ + ਮੁਜੱਫਰਪੁਰਾ</t>
+          <t>ਤਰੀਨ</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>Chuchakwal + Mujaffarpura</t>
+          <t>Tareen</t>
         </is>
       </c>
       <c r="E73" s="8" t="n">
@@ -4094,17 +4094,17 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>ਅਵਾਨ ਲੱਖਾ ਸਿੰਘ</t>
+          <t>ਸੌੜੀਆਂ</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>ਅਵਾਨ ਲੱਖਾ ਸਿੰਘ</t>
+          <t>ਸੌੜੀਆਂ</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>Awan Lakha Singh</t>
+          <t>Saurhiyan</t>
         </is>
       </c>
       <c r="E74" s="4" t="n">
@@ -4141,17 +4141,17 @@
       </c>
       <c r="B75" s="7" t="inlineStr">
         <is>
-          <t>ਵਰਿਆਹ</t>
+          <t>ਤੱਲਾ</t>
         </is>
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
-          <t>ਵਰਿਆਹ</t>
+          <t>ਤੱਲਾ</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>Wariah</t>
+          <t>Tallah</t>
         </is>
       </c>
       <c r="E75" s="8" t="n">
@@ -4188,17 +4188,17 @@
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>ਖੁਸ਼ਪੁਰਾ + ਹਸਨਪੁਰਾ</t>
+          <t>ਕੋਟ ਸਿੱਧੂ</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>ਖੁਸ਼ਪੁਰਾ + ਹਸਨਪੁਰਾ</t>
+          <t>ਕੋਟ ਸਿੱਧੂ</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>Khushpura + Hasanpura</t>
+          <t>Kot Sidhu</t>
         </is>
       </c>
       <c r="E76" s="4" t="n">
@@ -4235,17 +4235,17 @@
       </c>
       <c r="B77" s="7" t="inlineStr">
         <is>
-          <t>ਤਰੀਨ + ਕਾਕੜ</t>
+          <t>ਕਰਿਆਲ</t>
         </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
-          <t>ਤਰੀਨ + ਕਾਕੜ</t>
+          <t>ਕਰਿਆਲ</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>Tareen + Kakar</t>
+          <t>Karyal</t>
         </is>
       </c>
       <c r="E77" s="8" t="n">
@@ -4282,17 +4282,17 @@
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>ਸੱੜੀਆਂ</t>
+          <t>ਕਰਿਆਲ</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>ਸੱੜੀਆਂ</t>
+          <t>ਕਰਿਆਲ</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>Sarrian</t>
+          <t>Karyal</t>
         </is>
       </c>
       <c r="E78" s="4" t="n">
@@ -4329,17 +4329,17 @@
       </c>
       <c r="B79" s="7" t="inlineStr">
         <is>
-          <t>ਤੱਲਾ</t>
+          <t>ਮਿਆਦੀ ਕਲਾਂ</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>ਤੱਲਾ</t>
+          <t>ਮਿਆਦੀ ਕਲਾਂ</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>Talla</t>
+          <t>Miadi Kalan</t>
         </is>
       </c>
       <c r="E79" s="8" t="n">
@@ -4376,17 +4376,17 @@
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>ਕੋਟ ਸਿੰਘ</t>
+          <t>ਜੱਸੜਵਾਲ</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>ਕੋਟ ਸਿੰਘ</t>
+          <t>ਜੱਸੜਵਾਲ</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>Kot Singh</t>
+          <t>Jastarwal</t>
         </is>
       </c>
       <c r="E80" s="4" t="n">
@@ -4423,17 +4423,17 @@
       </c>
       <c r="B81" s="7" t="inlineStr">
         <is>
-          <t>ਕੜਿਆਲ</t>
+          <t>ਛੀਨਾ ਕਰਮ ਸਿੰਘ</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>ਕੜਿਆਲ</t>
+          <t>ਛੀਨਾ ਕਰਮ ਸਿੰਘ</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>Karial</t>
+          <t>Chhina Karam Singh</t>
         </is>
       </c>
       <c r="E81" s="8" t="n">
@@ -4470,17 +4470,17 @@
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>ਕੜਿਆਲ</t>
+          <t>ਨੇਪਾਲ</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>ਕੜਿਆਲ</t>
+          <t>ਨੇਪਾਲ</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>Karial</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="E82" s="4" t="n">
@@ -4517,17 +4517,17 @@
       </c>
       <c r="B83" s="7" t="inlineStr">
         <is>
-          <t>ਮਿਆਦੀ ਕਲਾਂ + ਕੋਟਲੀ ਮੁਗਲਾਂ</t>
+          <t>ਕੋਟਲੀ ਕੋਰੋਟਾਣਾ</t>
         </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>ਮਿਆਦੀ ਕਲਾਂ + ਕੋਟਲੀ ਮੁਗਲਾਂ</t>
+          <t>ਕੋਟਲੀ ਕੋਰੋਟਾਣਾ</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>Miadi Kalan + Kotli Muglan</t>
+          <t>Kotli Korotana</t>
         </is>
       </c>
       <c r="E83" s="8" t="n">
@@ -4564,17 +4564,17 @@
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>ਜਸਤਰਵਾਲ</t>
+          <t>ਬੋਹਲੀਆ</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>ਜਸਤਰਵਾਲ</t>
+          <t>ਬੋਹਲੀਆ</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>Jastarwal</t>
+          <t>Bohlian</t>
         </is>
       </c>
       <c r="E84" s="4" t="n">
@@ -4611,17 +4611,17 @@
       </c>
       <c r="B85" s="7" t="inlineStr">
         <is>
-          <t>ਜਸਤਰਵਾਲ</t>
+          <t>ਬੋਹਲੀਆ</t>
         </is>
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>ਜਸਤਰਵਾਲ</t>
+          <t>ਬੋਹਲੀਆ</t>
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>Jastarwal</t>
+          <t>Bohlian</t>
         </is>
       </c>
       <c r="E85" s="8" t="n">
@@ -4658,17 +4658,17 @@
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>ਛੀਨਾ ਕਰਮ ਸਿੰਘ</t>
+          <t>ਈਸਾਪੁਰ</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>ਛੀਨਾ ਕਰਮ ਸਿੰਘ</t>
+          <t>ਈਸਾਪੁਰ</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>Chhina Karam Singh</t>
+          <t>Isapur</t>
         </is>
       </c>
       <c r="E86" s="4" t="n">
@@ -4705,17 +4705,17 @@
       </c>
       <c r="B87" s="7" t="inlineStr">
         <is>
-          <t>ਨੇਪਾਲ</t>
+          <t>ਰਾਏਪੁਰ ਖੁਰਦ</t>
         </is>
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>ਨੇਪਾਲ</t>
+          <t>ਰਾਏਪੁਰ ਖੁਰਦ</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Raipur Khurd</t>
         </is>
       </c>
       <c r="E87" s="8" t="n">
@@ -4752,17 +4752,17 @@
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>ਕੋਟਲੀ ਕੋਰੇਟਾਨਾ</t>
+          <t>ਮਤੀਆ</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>ਕੋਟਲੀ ਕੋਰੇਟਾਨਾ</t>
+          <t>ਮਤੀਆ</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>Kotli Koretana</t>
+          <t>Matiya</t>
         </is>
       </c>
       <c r="E88" s="4" t="n">
@@ -4799,17 +4799,17 @@
       </c>
       <c r="B89" s="7" t="inlineStr">
         <is>
-          <t>ਬੋਹਲੀਆਂ</t>
+          <t>ਮੋਹਰ</t>
         </is>
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>ਬੋਹਲੀਆਂ</t>
+          <t>ਮੋਹਰ</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>Bohlian</t>
+          <t>Mohar</t>
         </is>
       </c>
       <c r="E89" s="8" t="n">
@@ -4846,17 +4846,17 @@
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>ਬੋਹਲੀਆਂ</t>
+          <t>ਉਮਰਪੁਰਾ</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>ਬੋਹਲੀਆਂ</t>
+          <t>ਉਮਰਪੁਰਾ</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>Bohlian</t>
+          <t>Umarpura</t>
         </is>
       </c>
       <c r="E90" s="4" t="n">
@@ -4893,17 +4893,17 @@
       </c>
       <c r="B91" s="7" t="inlineStr">
         <is>
-          <t>ਈਸਾਪੁਰ</t>
+          <t>ਉਮਰਪੁਰਾ</t>
         </is>
       </c>
       <c r="C91" s="7" t="inlineStr">
         <is>
-          <t>ਈਸਾਪੁਰ</t>
+          <t>ਉਮਰਪੁਰਾ</t>
         </is>
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>Isapur</t>
+          <t>Umarpura</t>
         </is>
       </c>
       <c r="E91" s="8" t="n">
@@ -4940,17 +4940,17 @@
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>ਰਾਏਪੁਰ ਖੁਰਦ</t>
+          <t>ਜੌਂਸ</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>ਰਾਏਪੁਰ ਖੁਰਦ</t>
+          <t>ਜੌਂਸ</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>Raipur Khurd</t>
+          <t>Jauns</t>
         </is>
       </c>
       <c r="E92" s="4" t="n">
@@ -4987,17 +4987,17 @@
       </c>
       <c r="B93" s="7" t="inlineStr">
         <is>
-          <t>ਮਟੀਆ</t>
+          <t>ਓਠੀਆਂ</t>
         </is>
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
-          <t>ਮਟੀਆ</t>
+          <t>ਓਠੀਆਂ</t>
         </is>
       </c>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>Matia</t>
+          <t>Othian</t>
         </is>
       </c>
       <c r="E93" s="8" t="n">
@@ -5034,17 +5034,17 @@
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>ਮੇਹਾਰ</t>
+          <t>ਓਠੀਆਂ</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>ਮੇਹਾਰ</t>
+          <t>ਓਠੀਆਂ</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>Mehar</t>
+          <t>Othian</t>
         </is>
       </c>
       <c r="E94" s="4" t="n">
@@ -5081,17 +5081,17 @@
       </c>
       <c r="B95" s="7" t="inlineStr">
         <is>
-          <t>ਉਮਰਪੁਰਾ</t>
+          <t>ਓਠੀਆਂ</t>
         </is>
       </c>
       <c r="C95" s="7" t="inlineStr">
         <is>
-          <t>ਉਮਰਪੁਰਾ</t>
+          <t>ਓਠੀਆਂ</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>Umarpura</t>
+          <t>Othian</t>
         </is>
       </c>
       <c r="E95" s="8" t="n">
@@ -5128,17 +5128,17 @@
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>ਉਮਰਪੁਰਾ + ਚਾਹੀਆਂ</t>
+          <t>ਧਰਮਕੋਟ</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>ਉਮਰਪੁਰਾ + ਚਾਹੀਆਂ</t>
+          <t>ਧਰਮਕੋਟ</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>Umarpura + Chahian</t>
+          <t>Dharamkot</t>
         </is>
       </c>
       <c r="E96" s="4" t="n">
@@ -5175,17 +5175,17 @@
       </c>
       <c r="B97" s="7" t="inlineStr">
         <is>
-          <t>ਜੱਸ</t>
+          <t>ਚੱਕ ਕਮਾਲ ਖ਼ਾਨ</t>
         </is>
       </c>
       <c r="C97" s="7" t="inlineStr">
         <is>
-          <t>ਜੱਸ</t>
+          <t>ਚੱਕ ਕਮਾਲ ਖ਼ਾਨ</t>
         </is>
       </c>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>Jass</t>
+          <t>Chakk Kamal Khan</t>
         </is>
       </c>
       <c r="E97" s="8" t="n">
@@ -5222,17 +5222,17 @@
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>ਜੱਸ</t>
+          <t>ਕੋਟਲੀ ਸੱਕਾ</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>ਜੱਸ</t>
+          <t>ਕੋਟਲੀ ਸੱਕਾ</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>Jass</t>
+          <t>Kotli Sakka</t>
         </is>
       </c>
       <c r="E98" s="4" t="n">
@@ -5269,17 +5269,17 @@
       </c>
       <c r="B99" s="7" t="inlineStr">
         <is>
-          <t>ਓਠੀਆਂ</t>
+          <t>ਮਹਿਮਦਪੁਰਾ</t>
         </is>
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
-          <t>ਓਠੀਆਂ</t>
+          <t>ਮਹਿਮਦਪੁਰਾ</t>
         </is>
       </c>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>Othian</t>
+          <t>Mehmadpura</t>
         </is>
       </c>
       <c r="E99" s="8" t="n">
@@ -5316,17 +5316,17 @@
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>ਓਠੀਆਂ + ਰੱਖ ਓਠੀਆਂ</t>
+          <t>ਜੱਜੇ</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>ਓਠੀਆਂ + ਰੱਖ ਓਠੀਆਂ</t>
+          <t>ਜੱਜੇ</t>
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>Othian + Rakh Othian</t>
+          <t>Jajje</t>
         </is>
       </c>
       <c r="E100" s="4" t="n">
@@ -5363,17 +5363,17 @@
       </c>
       <c r="B101" s="7" t="inlineStr">
         <is>
-          <t>ਓਠੀਆਂ</t>
+          <t>ਚੱਕ ਮਿਸ਼ਰੀ ਖ਼ਾਨ</t>
         </is>
       </c>
       <c r="C101" s="7" t="inlineStr">
         <is>
-          <t>ਓਠੀਆਂ</t>
+          <t>ਚੱਕ ਮਿਸ਼ਰੀ ਖ਼ਾਨ</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>Othian</t>
+          <t>Chakk Mishri Khan</t>
         </is>
       </c>
       <c r="E101" s="8" t="n">
@@ -5410,17 +5410,17 @@
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>ਧਰਮਕੋਟ</t>
+          <t>ਚੱਕ ਮਿਸ਼ਰੀ ਖ਼ਾਨ</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>ਧਰਮਕੋਟ</t>
+          <t>ਚੱਕ ਮਿਸ਼ਰੀ ਖ਼ਾਨ</t>
         </is>
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
-          <t>Dharmkot</t>
+          <t>Chakk Mishri Khan</t>
         </is>
       </c>
       <c r="E102" s="4" t="n">
@@ -5457,17 +5457,17 @@
       </c>
       <c r="B103" s="7" t="inlineStr">
         <is>
-          <t>ਚੱਕ ਕਮਾਲ ਖਾਂ</t>
+          <t>ਮੌੜੇ</t>
         </is>
       </c>
       <c r="C103" s="7" t="inlineStr">
         <is>
-          <t>ਚੱਕ ਕਮਾਲ ਖਾਂ</t>
+          <t>ਮੌੜੇ</t>
         </is>
       </c>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>Chak Kamal Khan</t>
+          <t>Maure</t>
         </is>
       </c>
       <c r="E103" s="8" t="n">
@@ -5504,17 +5504,17 @@
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>ਕੋਟਲੀ ਸੱਕਾ</t>
+          <t>ਮੌੜੇ</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>ਕੋਟਲੀ ਸੱਕਾ</t>
+          <t>ਮੌੜੇ</t>
         </is>
       </c>
       <c r="D104" s="3" t="inlineStr">
         <is>
-          <t>Kotli Sakka</t>
+          <t>Maure</t>
         </is>
       </c>
       <c r="E104" s="4" t="n">
@@ -5551,17 +5551,17 @@
       </c>
       <c r="B105" s="7" t="inlineStr">
         <is>
-          <t>ਮਹਿਮਦਪੁਰਾ + ਕਮੀਰਪੁਰਾ</t>
+          <t>ਮਾਨਾਵਾਲਾ</t>
         </is>
       </c>
       <c r="C105" s="7" t="inlineStr">
         <is>
-          <t>ਮਹਿਮਦਪੁਰਾ + ਕਮੀਰਪੁਰਾ</t>
+          <t>ਮਾਨਾਵਾਲਾ</t>
         </is>
       </c>
       <c r="D105" s="7" t="inlineStr">
         <is>
-          <t>Mahmadpura + Kamirpura</t>
+          <t>Manawala</t>
         </is>
       </c>
       <c r="E105" s="8" t="n">
@@ -5598,17 +5598,17 @@
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>ਜੱਜੇ + ਮਾਲਾਕੀੜੀ</t>
+          <t>ਮਾਨਾਵਾਲਾ</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>ਜੱਜੇ + ਮਾਲਾਕੀੜੀ</t>
+          <t>ਮਾਨਾਵਾਲਾ</t>
         </is>
       </c>
       <c r="D106" s="3" t="inlineStr">
         <is>
-          <t>Jajje + Malakiri</t>
+          <t>Manawala</t>
         </is>
       </c>
       <c r="E106" s="4" t="n">
@@ -5645,17 +5645,17 @@
       </c>
       <c r="B107" s="7" t="inlineStr">
         <is>
-          <t>ਚੱਕ ਮਿਸਰੀ ਖਾਂ</t>
+          <t>ਚੋਗਾਵਾਂ</t>
         </is>
       </c>
       <c r="C107" s="7" t="inlineStr">
         <is>
-          <t>ਚੱਕ ਮਿਸਰੀ ਖਾਂ</t>
+          <t>ਚੋਗਾਵਾਂ</t>
         </is>
       </c>
       <c r="D107" s="7" t="inlineStr">
         <is>
-          <t>Chak Misri Khan</t>
+          <t>Chogawan</t>
         </is>
       </c>
       <c r="E107" s="8" t="n">
@@ -5692,17 +5692,17 @@
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>ਚੱਕ ਮਿਸਰੀ ਖਾਂ</t>
+          <t>ਚੋਗਾਵਾਂ</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>ਚੱਕ ਮਿਸਰੀ ਖਾਂ</t>
+          <t>ਚੋਗਾਵਾਂ</t>
         </is>
       </c>
       <c r="D108" s="3" t="inlineStr">
         <is>
-          <t>Chak Misri Khan</t>
+          <t>Chogawan</t>
         </is>
       </c>
       <c r="E108" s="4" t="n">
@@ -5739,17 +5739,17 @@
       </c>
       <c r="B109" s="7" t="inlineStr">
         <is>
-          <t>ਮੋੜੇ</t>
+          <t>ਚੋਗਾਵਾਂ</t>
         </is>
       </c>
       <c r="C109" s="7" t="inlineStr">
         <is>
-          <t>ਮੋੜੇ</t>
+          <t>ਚੋਗਾਵਾਂ</t>
         </is>
       </c>
       <c r="D109" s="7" t="inlineStr">
         <is>
-          <t>More</t>
+          <t>Chogawan</t>
         </is>
       </c>
       <c r="E109" s="8" t="n">
@@ -5786,17 +5786,17 @@
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>ਮੋੜੇ</t>
+          <t>ਚੋਗਾਵਾਂ</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>ਮੋੜੇ</t>
+          <t>ਚੋਗਾਵਾਂ</t>
         </is>
       </c>
       <c r="D110" s="3" t="inlineStr">
         <is>
-          <t>More</t>
+          <t>Chogawan</t>
         </is>
       </c>
       <c r="E110" s="4" t="n">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="B111" s="7" t="inlineStr">
         <is>
-          <t>ਮਾਨਾਵਾਲਾ</t>
+          <t>ਚੋਗਾਵਾਂ</t>
         </is>
       </c>
       <c r="C111" s="7" t="inlineStr">
         <is>
-          <t>ਮਾਨਾਵਾਲਾ</t>
+          <t>ਚੋਗਾਵਾਂ</t>
         </is>
       </c>
       <c r="D111" s="7" t="inlineStr">
         <is>
-          <t>Manawala</t>
+          <t>Chogawan</t>
         </is>
       </c>
       <c r="E111" s="8" t="n">
@@ -5880,17 +5880,17 @@
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>ਮਾਨਾਵਾਲਾ</t>
+          <t>ਚੋਗਾਵਾਂ</t>
         </is>
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>ਮਾਨਾਵਾਲਾ</t>
+          <t>ਚੋਗਾਵਾਂ</t>
         </is>
       </c>
       <c r="D112" s="3" t="inlineStr">
         <is>
-          <t>Manawala</t>
+          <t>Chogawan</t>
         </is>
       </c>
       <c r="E112" s="4" t="n">
@@ -5927,17 +5927,17 @@
       </c>
       <c r="B113" s="7" t="inlineStr">
         <is>
-          <t>ਚੋਗਾਵਾਂ</t>
+          <t>ਭੁੱਲਰ</t>
         </is>
       </c>
       <c r="C113" s="7" t="inlineStr">
         <is>
-          <t>ਚੋਗਾਵਾਂ</t>
+          <t>ਭੁੱਲਰ</t>
         </is>
       </c>
       <c r="D113" s="7" t="inlineStr">
         <is>
-          <t>Chogawan</t>
+          <t>Bhullar</t>
         </is>
       </c>
       <c r="E113" s="8" t="n">
@@ -5974,17 +5974,17 @@
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>ਚੋਗਾਵਾਂ</t>
+          <t>ਭੁੱਲਰ</t>
         </is>
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>ਚੋਗਾਵਾਂ</t>
+          <t>ਭੁੱਲਰ</t>
         </is>
       </c>
       <c r="D114" s="3" t="inlineStr">
         <is>
-          <t>Chogawan</t>
+          <t>Bhullar</t>
         </is>
       </c>
       <c r="E114" s="4" t="n">
@@ -6021,17 +6021,17 @@
       </c>
       <c r="B115" s="7" t="inlineStr">
         <is>
-          <t>ਚੋਗਾਵਾਂ</t>
+          <t>ਭੁੱਲਰ</t>
         </is>
       </c>
       <c r="C115" s="7" t="inlineStr">
         <is>
-          <t>ਚੋਗਾਵਾਂ</t>
+          <t>ਭੁੱਲਰ</t>
         </is>
       </c>
       <c r="D115" s="7" t="inlineStr">
         <is>
-          <t>Chogawan</t>
+          <t>Bhullar</t>
         </is>
       </c>
       <c r="E115" s="8" t="n">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>ਚੋਗਾਵਾਂ</t>
+          <t>ਤਪਿਆਲਾ</t>
         </is>
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>ਚੋਗਾਵਾਂ</t>
+          <t>ਤਪਿਆਲਾ</t>
         </is>
       </c>
       <c r="D116" s="3" t="inlineStr">
         <is>
-          <t>Chogawan</t>
+          <t>Tapiala</t>
         </is>
       </c>
       <c r="E116" s="4" t="n">
@@ -6115,17 +6115,17 @@
       </c>
       <c r="B117" s="7" t="inlineStr">
         <is>
-          <t>ਚੋਗਾਵਾਂ</t>
+          <t>ਤਪਿਆਲਾ</t>
         </is>
       </c>
       <c r="C117" s="7" t="inlineStr">
         <is>
-          <t>ਚੋਗਾਵਾਂ</t>
+          <t>ਤਪਿਆਲਾ</t>
         </is>
       </c>
       <c r="D117" s="7" t="inlineStr">
         <is>
-          <t>Chogawan</t>
+          <t>Tapiala</t>
         </is>
       </c>
       <c r="E117" s="8" t="n">
@@ -6162,17 +6162,17 @@
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>ਚੋਗਾਵਾਂ</t>
+          <t>ਠੱਠੀ</t>
         </is>
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>ਚੋਗਾਵਾਂ</t>
+          <t>ਠੱਠੀ</t>
         </is>
       </c>
       <c r="D118" s="3" t="inlineStr">
         <is>
-          <t>Chogawan</t>
+          <t>Thathi</t>
         </is>
       </c>
       <c r="E118" s="4" t="n">
@@ -6209,17 +6209,17 @@
       </c>
       <c r="B119" s="7" t="inlineStr">
         <is>
-          <t>ਭੁੱਲਰ</t>
+          <t>ਠੱਠਾ</t>
         </is>
       </c>
       <c r="C119" s="7" t="inlineStr">
         <is>
-          <t>ਭੁੱਲਰ</t>
+          <t>ਠੱਠਾ</t>
         </is>
       </c>
       <c r="D119" s="7" t="inlineStr">
         <is>
-          <t>Bhullar</t>
+          <t>Thatha</t>
         </is>
       </c>
       <c r="E119" s="8" t="n">
@@ -6256,17 +6256,17 @@
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>ਭੁੱਲਰ</t>
+          <t>ਭੰਗਵਾਂ</t>
         </is>
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>ਭੁੱਲਰ</t>
+          <t>ਭੰਗਵਾਂ</t>
         </is>
       </c>
       <c r="D120" s="3" t="inlineStr">
         <is>
-          <t>Bhullar</t>
+          <t>Bhangwan</t>
         </is>
       </c>
       <c r="E120" s="4" t="n">
@@ -6303,17 +6303,17 @@
       </c>
       <c r="B121" s="7" t="inlineStr">
         <is>
-          <t>ਭੁੱਲਰ</t>
+          <t>ਓਦੜ</t>
         </is>
       </c>
       <c r="C121" s="7" t="inlineStr">
         <is>
-          <t>ਭੁੱਲਰ</t>
+          <t>ਓਦੜ</t>
         </is>
       </c>
       <c r="D121" s="7" t="inlineStr">
         <is>
-          <t>Bhullar</t>
+          <t>Odar</t>
         </is>
       </c>
       <c r="E121" s="8" t="n">
@@ -6350,17 +6350,17 @@
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>ਟਪਿਆਲਾ</t>
+          <t>ਜੋਏਕੇ</t>
         </is>
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>ਟਪਿਆਲਾ</t>
+          <t>ਜੋਏਕੇ</t>
         </is>
       </c>
       <c r="D122" s="3" t="inlineStr">
         <is>
-          <t>Tapiala</t>
+          <t>Joeke</t>
         </is>
       </c>
       <c r="E122" s="4" t="n">
@@ -6397,17 +6397,17 @@
       </c>
       <c r="B123" s="7" t="inlineStr">
         <is>
-          <t>ਟਪਿਆਲਾ</t>
+          <t>ਕਮਾਸਕਾ</t>
         </is>
       </c>
       <c r="C123" s="7" t="inlineStr">
         <is>
-          <t>ਟਪਿਆਲਾ</t>
+          <t>ਕਮਾਸਕਾ</t>
         </is>
       </c>
       <c r="D123" s="7" t="inlineStr">
         <is>
-          <t>Tapiala</t>
+          <t>Kamaska</t>
         </is>
       </c>
       <c r="E123" s="8" t="n">
@@ -6444,17 +6444,17 @@
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
-          <t>ਠੱਠੀ</t>
+          <t>ਬਾਚੀਵਿੰਡ</t>
         </is>
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>ਠੱਠੀ</t>
+          <t>ਬਾਚੀਵਿੰਡ</t>
         </is>
       </c>
       <c r="D124" s="3" t="inlineStr">
         <is>
-          <t>Thathi</t>
+          <t>Bachiwind</t>
         </is>
       </c>
       <c r="E124" s="4" t="n">
@@ -6491,17 +6491,17 @@
       </c>
       <c r="B125" s="7" t="inlineStr">
         <is>
-          <t>ਠੱਠਾ</t>
+          <t>ਬਾਚੀਵਿੰਡ</t>
         </is>
       </c>
       <c r="C125" s="7" t="inlineStr">
         <is>
-          <t>ਠੱਠਾ</t>
+          <t>ਬਾਚੀਵਿੰਡ</t>
         </is>
       </c>
       <c r="D125" s="7" t="inlineStr">
         <is>
-          <t>Thattha</t>
+          <t>Bachiwind</t>
         </is>
       </c>
       <c r="E125" s="8" t="n">
@@ -6538,17 +6538,17 @@
       </c>
       <c r="B126" s="3" t="inlineStr">
         <is>
-          <t>ਭੰਗਵਾਂ + ਸਿਧਵਾਂ + ਠੀਕਰੀਵਾਲਾ</t>
+          <t>ਬਾਚੀਵਿੰਡ</t>
         </is>
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>ਭੰਗਵਾਂ + ਸਿਧਵਾਂ + ਠੀਕਰੀਵਾਲਾ</t>
+          <t>ਬਾਚੀਵਿੰਡ</t>
         </is>
       </c>
       <c r="D126" s="3" t="inlineStr">
         <is>
-          <t>Bhangwan + Sidhwan + Theekriwala</t>
+          <t>Bachiwind</t>
         </is>
       </c>
       <c r="E126" s="4" t="n">
@@ -6585,17 +6585,17 @@
       </c>
       <c r="B127" s="7" t="inlineStr">
         <is>
-          <t>ਉਡਰ</t>
+          <t>ਡਾਲਾ</t>
         </is>
       </c>
       <c r="C127" s="7" t="inlineStr">
         <is>
-          <t>ਉਡਰ</t>
+          <t>ਡਾਲਾ</t>
         </is>
       </c>
       <c r="D127" s="7" t="inlineStr">
         <is>
-          <t>Udar</t>
+          <t>Dala</t>
         </is>
       </c>
       <c r="E127" s="8" t="n">
@@ -6632,17 +6632,17 @@
       </c>
       <c r="B128" s="3" t="inlineStr">
         <is>
-          <t>ਜੋਏਕੇ</t>
+          <t>ਕਿਰਲਗੜ੍ਹ</t>
         </is>
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>ਜੋਏਕੇ</t>
+          <t>ਕਿਰਲਗੜ੍ਹ</t>
         </is>
       </c>
       <c r="D128" s="3" t="inlineStr">
         <is>
-          <t>Joeke</t>
+          <t>Kiralgarh</t>
         </is>
       </c>
       <c r="E128" s="4" t="n">
@@ -6679,17 +6679,17 @@
       </c>
       <c r="B129" s="7" t="inlineStr">
         <is>
-          <t>ਕਮਾਸਕੇ + ਖਿਜਰਪੁਰਾ</t>
+          <t>ਸ਼ਾਹੂਰਾ</t>
         </is>
       </c>
       <c r="C129" s="7" t="inlineStr">
         <is>
-          <t>ਕਮਾਸਕੇ + ਖਿਜਰਪੁਰਾ</t>
+          <t>ਸ਼ਾਹੂਰਾ</t>
         </is>
       </c>
       <c r="D129" s="7" t="inlineStr">
         <is>
-          <t>Kamaske + Khijarpura</t>
+          <t>Shahura</t>
         </is>
       </c>
       <c r="E129" s="8" t="n">
@@ -6726,17 +6726,17 @@
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>ਬੱਚੀਵਿੰਡ</t>
+          <t>ਸ਼ਾਹੂਰਾ</t>
         </is>
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>ਬੱਚੀਵਿੰਡ</t>
+          <t>ਸ਼ਾਹੂਰਾ</t>
         </is>
       </c>
       <c r="D130" s="3" t="inlineStr">
         <is>
-          <t>Bachhiwind</t>
+          <t>Shahura</t>
         </is>
       </c>
       <c r="E130" s="4" t="n">
@@ -6773,17 +6773,17 @@
       </c>
       <c r="B131" s="7" t="inlineStr">
         <is>
-          <t>ਬੱਚੀਵਿੰਡ</t>
+          <t>ਸ਼ਾਹੂਰਾ</t>
         </is>
       </c>
       <c r="C131" s="7" t="inlineStr">
         <is>
-          <t>ਬੱਚੀਵਿੰਡ</t>
+          <t>ਸ਼ਾਹੂਰਾ</t>
         </is>
       </c>
       <c r="D131" s="7" t="inlineStr">
         <is>
-          <t>Bachhiwind</t>
+          <t>Shahura</t>
         </is>
       </c>
       <c r="E131" s="8" t="n">
@@ -6820,17 +6820,17 @@
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>ਬੱਚੀਵਿੰਡ</t>
+          <t>ਡੱਲੇਕੇ</t>
         </is>
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>ਬੱਚੀਵਿੰਡ</t>
+          <t>ਡੱਲੇਕੇ</t>
         </is>
       </c>
       <c r="D132" s="3" t="inlineStr">
         <is>
-          <t>Bachhiwind</t>
+          <t>Dalleki</t>
         </is>
       </c>
       <c r="E132" s="4" t="n">
@@ -6867,17 +6867,17 @@
       </c>
       <c r="B133" s="7" t="inlineStr">
         <is>
-          <t>ਡਾਲਾ</t>
+          <t>ਬਹਿੜਵਾਲ</t>
         </is>
       </c>
       <c r="C133" s="7" t="inlineStr">
         <is>
-          <t>ਡਾਲਾ</t>
+          <t>ਬਹਿੜਵਾਲ</t>
         </is>
       </c>
       <c r="D133" s="7" t="inlineStr">
         <is>
-          <t>Dala</t>
+          <t>Beharwal</t>
         </is>
       </c>
       <c r="E133" s="8" t="n">
@@ -6914,17 +6914,17 @@
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>ਕਿਰਲਗੜ</t>
+          <t>ਵੈਣੇਕੇ</t>
         </is>
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>ਕਿਰਲਗੜ</t>
+          <t>ਵੈਣੇਕੇ</t>
         </is>
       </c>
       <c r="D134" s="3" t="inlineStr">
         <is>
-          <t>Kirlgarh</t>
+          <t>Vaineke</t>
         </is>
       </c>
       <c r="E134" s="4" t="n">
@@ -6961,17 +6961,17 @@
       </c>
       <c r="B135" s="7" t="inlineStr">
         <is>
-          <t>ਸ਼ਹੂਰਾ</t>
+          <t>ਵੈਣੇਕੇ</t>
         </is>
       </c>
       <c r="C135" s="7" t="inlineStr">
         <is>
-          <t>ਸ਼ਹੂਰਾ</t>
+          <t>ਵੈਣੇਕੇ</t>
         </is>
       </c>
       <c r="D135" s="7" t="inlineStr">
         <is>
-          <t>Shahura</t>
+          <t>Vaineke</t>
         </is>
       </c>
       <c r="E135" s="8" t="n">
@@ -7008,17 +7008,17 @@
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t>ਸ਼ਹੂਰਾ</t>
+          <t>ਚੇਲੇਕੇ</t>
         </is>
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
-          <t>ਸ਼ਹੂਰਾ</t>
+          <t>ਚੇਲੇਕੇ</t>
         </is>
       </c>
       <c r="D136" s="3" t="inlineStr">
         <is>
-          <t>Shahura</t>
+          <t>Cheleki</t>
         </is>
       </c>
       <c r="E136" s="4" t="n">
@@ -7055,17 +7055,17 @@
       </c>
       <c r="B137" s="7" t="inlineStr">
         <is>
-          <t>ਸ਼ਹੂਰਾ</t>
+          <t>ਕੋਹਾਲਾ</t>
         </is>
       </c>
       <c r="C137" s="7" t="inlineStr">
         <is>
-          <t>ਸ਼ਹੂਰਾ</t>
+          <t>ਕੋਹਾਲਾ</t>
         </is>
       </c>
       <c r="D137" s="7" t="inlineStr">
         <is>
-          <t>Shahura</t>
+          <t>Kohala</t>
         </is>
       </c>
       <c r="E137" s="8" t="n">
@@ -7102,17 +7102,17 @@
       </c>
       <c r="B138" s="3" t="inlineStr">
         <is>
-          <t>ਡੱਲੇਕੀ</t>
+          <t>ਕੋਹਾਲਾ</t>
         </is>
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>ਡੱਲੇਕੀ</t>
+          <t>ਕੋਹਾਲਾ</t>
         </is>
       </c>
       <c r="D138" s="3" t="inlineStr">
         <is>
-          <t>Dalleki</t>
+          <t>Kohala</t>
         </is>
       </c>
       <c r="E138" s="4" t="n">
@@ -7149,17 +7149,17 @@
       </c>
       <c r="B139" s="7" t="inlineStr">
         <is>
-          <t>ਬਹਿੜਵਾਲ</t>
+          <t>ਛਵਿੰਡਾ ਕਲਾਂ</t>
         </is>
       </c>
       <c r="C139" s="7" t="inlineStr">
         <is>
-          <t>ਬਹਿੜਵਾਲ</t>
+          <t>ਛਵਿੰਡਾ ਕਲਾਂ</t>
         </is>
       </c>
       <c r="D139" s="7" t="inlineStr">
         <is>
-          <t>Bahirwal</t>
+          <t>Chawinda Kalan</t>
         </is>
       </c>
       <c r="E139" s="8" t="n">
@@ -7196,17 +7196,17 @@
       </c>
       <c r="B140" s="3" t="inlineStr">
         <is>
-          <t>ਵਣੀਏਕੇ</t>
+          <t>ਛਵਿੰਡਾ ਕਲਾਂ</t>
         </is>
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t>ਵਣੀਏਕੇ</t>
+          <t>ਛਵਿੰਡਾ ਕਲਾਂ</t>
         </is>
       </c>
       <c r="D140" s="3" t="inlineStr">
         <is>
-          <t>Wanieke</t>
+          <t>Chawinda Kalan</t>
         </is>
       </c>
       <c r="E140" s="4" t="n">
@@ -7243,17 +7243,17 @@
       </c>
       <c r="B141" s="7" t="inlineStr">
         <is>
-          <t>ਵਣੀਏਕੇ</t>
+          <t>ਛਵਿੰਡਾ ਖੁਰਦ</t>
         </is>
       </c>
       <c r="C141" s="7" t="inlineStr">
         <is>
-          <t>ਵਣੀਏਕੇ</t>
+          <t>ਛਵਿੰਡਾ ਖੁਰਦ</t>
         </is>
       </c>
       <c r="D141" s="7" t="inlineStr">
         <is>
-          <t>Wanieke</t>
+          <t>Chawinda Khurd</t>
         </is>
       </c>
       <c r="E141" s="8" t="n">
@@ -7290,17 +7290,17 @@
       </c>
       <c r="B142" s="3" t="inlineStr">
         <is>
-          <t>ਚੇਲੇਕੀ + ਕੋਟਲੀ ਅੱਲਖ</t>
+          <t>ਪੱਧਰੀ</t>
         </is>
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>ਚੇਲੇਕੀ + ਕੋਟਲੀ ਅੱਲਖ</t>
+          <t>ਪੱਧਰੀ</t>
         </is>
       </c>
       <c r="D142" s="3" t="inlineStr">
         <is>
-          <t>Cheleki + Kotli Allakh</t>
+          <t>Padhari</t>
         </is>
       </c>
       <c r="E142" s="4" t="n">
@@ -7337,17 +7337,17 @@
       </c>
       <c r="B143" s="7" t="inlineStr">
         <is>
-          <t>ਕੋਹਾਲਾ (ਸੱਜਾ ਪਾਸਾ)</t>
+          <t>ਪੱਧਰੀ</t>
         </is>
       </c>
       <c r="C143" s="7" t="inlineStr">
         <is>
-          <t>ਕੋਹਾਲਾ (ਸੱਜਾ ਪਾਸਾ)</t>
+          <t>ਪੱਧਰੀ</t>
         </is>
       </c>
       <c r="D143" s="7" t="inlineStr">
         <is>
-          <t>Kohala (Sajja Pasa)</t>
+          <t>Padhari</t>
         </is>
       </c>
       <c r="E143" s="8" t="n">
@@ -7384,17 +7384,17 @@
       </c>
       <c r="B144" s="3" t="inlineStr">
         <is>
-          <t>ਕੋਹਾਲਾ (ਖੱਬਾ ਪਾਸਾ)</t>
+          <t>ਲਾਂਵੇ</t>
         </is>
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>ਕੋਹਾਲਾ (ਖੱਬਾ ਪਾਸਾ)</t>
+          <t>ਲਾਂਵੇ</t>
         </is>
       </c>
       <c r="D144" s="3" t="inlineStr">
         <is>
-          <t>Kohala (Khabba Pasa)</t>
+          <t>Lanven</t>
         </is>
       </c>
       <c r="E144" s="4" t="n">
@@ -7431,17 +7431,17 @@
       </c>
       <c r="B145" s="7" t="inlineStr">
         <is>
-          <t>ਚਵਿੰਡਾ ਕਲਾਂ</t>
+          <t>ਨੂਰਪੁਰ</t>
         </is>
       </c>
       <c r="C145" s="7" t="inlineStr">
         <is>
-          <t>ਚਵਿੰਡਾ ਕਲਾਂ</t>
+          <t>ਨੂਰਪੁਰ</t>
         </is>
       </c>
       <c r="D145" s="7" t="inlineStr">
         <is>
-          <t>Chawinda Kalan</t>
+          <t>Nurpur</t>
         </is>
       </c>
       <c r="E145" s="8" t="n">
@@ -7478,17 +7478,17 @@
       </c>
       <c r="B146" s="3" t="inlineStr">
         <is>
-          <t>ਚਵਿੰਡਾ ਕਲਾਂ</t>
+          <t>ਛਿੱਦਣ</t>
         </is>
       </c>
       <c r="C146" s="3" t="inlineStr">
         <is>
-          <t>ਚਵਿੰਡਾ ਕਲਾਂ</t>
+          <t>ਛਿੱਦਣ</t>
         </is>
       </c>
       <c r="D146" s="3" t="inlineStr">
         <is>
-          <t>Chawinda Kalan</t>
+          <t>Chhidan</t>
         </is>
       </c>
       <c r="E146" s="4" t="n">
@@ -7525,17 +7525,17 @@
       </c>
       <c r="B147" s="7" t="inlineStr">
         <is>
-          <t>ਚਵਿੰਡਾ ਖੁਰਦ</t>
+          <t>ਛਿੱਦਣ</t>
         </is>
       </c>
       <c r="C147" s="7" t="inlineStr">
         <is>
-          <t>ਚਵਿੰਡਾ ਖੁਰਦ</t>
+          <t>ਛਿੱਦਣ</t>
         </is>
       </c>
       <c r="D147" s="7" t="inlineStr">
         <is>
-          <t>Chawinda Khurd</t>
+          <t>Chhidan</t>
         </is>
       </c>
       <c r="E147" s="8" t="n">
@@ -7572,17 +7572,17 @@
       </c>
       <c r="B148" s="3" t="inlineStr">
         <is>
-          <t>ਪੱਧਰੀ</t>
+          <t>ਬੋਪਾਰਾਏ ਕਲਾਂ</t>
         </is>
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t>ਪੱਧਰੀ</t>
+          <t>ਬੋਪਾਰਾਏ ਕਲਾਂ</t>
         </is>
       </c>
       <c r="D148" s="3" t="inlineStr">
         <is>
-          <t>Paddhari</t>
+          <t>Bopa Rai Kalan</t>
         </is>
       </c>
       <c r="E148" s="4" t="n">
@@ -7619,17 +7619,17 @@
       </c>
       <c r="B149" s="7" t="inlineStr">
         <is>
-          <t>ਪੱਧਰੀ</t>
+          <t>ਬੋਪਾਰਾਏ ਕਲਾਂ</t>
         </is>
       </c>
       <c r="C149" s="7" t="inlineStr">
         <is>
-          <t>ਪੱਧਰੀ</t>
+          <t>ਬੋਪਾਰਾਏ ਕਲਾਂ</t>
         </is>
       </c>
       <c r="D149" s="7" t="inlineStr">
         <is>
-          <t>Paddhari</t>
+          <t>Bopa Rai Kalan</t>
         </is>
       </c>
       <c r="E149" s="8" t="n">
@@ -7666,17 +7666,17 @@
       </c>
       <c r="B150" s="3" t="inlineStr">
         <is>
-          <t>ਲਾਂਦੇ</t>
+          <t>ਬੋਪਾਰਾਏ ਖੁਰਦ</t>
         </is>
       </c>
       <c r="C150" s="3" t="inlineStr">
         <is>
-          <t>ਲਾਂਦੇ</t>
+          <t>ਬੋਪਾਰਾਏ ਖੁਰਦ</t>
         </is>
       </c>
       <c r="D150" s="3" t="inlineStr">
         <is>
-          <t>Lande</t>
+          <t>Bopa Rai Khurd</t>
         </is>
       </c>
       <c r="E150" s="4" t="n">
@@ -7713,17 +7713,17 @@
       </c>
       <c r="B151" s="7" t="inlineStr">
         <is>
-          <t>ਨੂਰਪੁਰ</t>
+          <t>ਬੋਪਾਰਾਏ ਖੁਰਦ</t>
         </is>
       </c>
       <c r="C151" s="7" t="inlineStr">
         <is>
-          <t>ਨੂਰਪੁਰ</t>
+          <t>ਬੋਪਾਰਾਏ ਖੁਰਦ</t>
         </is>
       </c>
       <c r="D151" s="7" t="inlineStr">
         <is>
-          <t>Nurpur</t>
+          <t>Bopa Rai Khurd</t>
         </is>
       </c>
       <c r="E151" s="8" t="n">
@@ -7760,17 +7760,17 @@
       </c>
       <c r="B152" s="3" t="inlineStr">
         <is>
-          <t>ਛਿੱਡਣ</t>
+          <t>ਕੋਲੋਵਾਲ</t>
         </is>
       </c>
       <c r="C152" s="3" t="inlineStr">
         <is>
-          <t>ਛਿੱਡਣ</t>
+          <t>ਕੋਲੋਵਾਲ</t>
         </is>
       </c>
       <c r="D152" s="3" t="inlineStr">
         <is>
-          <t>Chhiddan</t>
+          <t>Kolowal</t>
         </is>
       </c>
       <c r="E152" s="4" t="n">
@@ -7807,17 +7807,17 @@
       </c>
       <c r="B153" s="7" t="inlineStr">
         <is>
-          <t>ਛਿੱਡਣ</t>
+          <t>ਬਰਾੜ</t>
         </is>
       </c>
       <c r="C153" s="7" t="inlineStr">
         <is>
-          <t>ਛਿੱਡਣ</t>
+          <t>ਬਰਾੜ</t>
         </is>
       </c>
       <c r="D153" s="7" t="inlineStr">
         <is>
-          <t>Chhiddan</t>
+          <t>Brar</t>
         </is>
       </c>
       <c r="E153" s="8" t="n">
@@ -7854,17 +7854,17 @@
       </c>
       <c r="B154" s="3" t="inlineStr">
         <is>
-          <t>ਬੋਪਾਰਾਏ ਕਲਾਂ</t>
+          <t>ਬਰਾੜ</t>
         </is>
       </c>
       <c r="C154" s="3" t="inlineStr">
         <is>
-          <t>ਬੋਪਾਰਾਏ ਕਲਾਂ</t>
+          <t>ਬਰਾੜ</t>
         </is>
       </c>
       <c r="D154" s="3" t="inlineStr">
         <is>
-          <t>Boparai Kalan</t>
+          <t>Brar</t>
         </is>
       </c>
       <c r="E154" s="4" t="n">
@@ -7901,17 +7901,17 @@
       </c>
       <c r="B155" s="7" t="inlineStr">
         <is>
-          <t>ਬੋਪਾਰਾਏ ਕਲਾਂ</t>
+          <t>ਮੱਧੋਕੇ</t>
         </is>
       </c>
       <c r="C155" s="7" t="inlineStr">
         <is>
-          <t>ਬੋਪਾਰਾਏ ਕਲਾਂ</t>
+          <t>ਮੱਧੋਕੇ</t>
         </is>
       </c>
       <c r="D155" s="7" t="inlineStr">
         <is>
-          <t>Boparai Kalan</t>
+          <t>Madhoke</t>
         </is>
       </c>
       <c r="E155" s="8" t="n">
@@ -7948,17 +7948,17 @@
       </c>
       <c r="B156" s="3" t="inlineStr">
         <is>
-          <t>ਬੋਪਾਰਾਏ ਖੁਰਦ</t>
+          <t>ਖਿਆਲਾ ਕਲਾਂ</t>
         </is>
       </c>
       <c r="C156" s="3" t="inlineStr">
         <is>
-          <t>ਬੋਪਾਰਾਏ ਖੁਰਦ</t>
+          <t>ਖਿਆਲਾ ਕਲਾਂ</t>
         </is>
       </c>
       <c r="D156" s="3" t="inlineStr">
         <is>
-          <t>Boparai Khurd</t>
+          <t>Khiala Kalan</t>
         </is>
       </c>
       <c r="E156" s="4" t="n">
@@ -7995,17 +7995,17 @@
       </c>
       <c r="B157" s="7" t="inlineStr">
         <is>
-          <t>ਬੋਪਾਰਾਏ ਖੁਰਦ</t>
+          <t>ਖਿਆਲਾ ਕਲਾਂ</t>
         </is>
       </c>
       <c r="C157" s="7" t="inlineStr">
         <is>
-          <t>ਬੋਪਾਰਾਏ ਖੁਰਦ</t>
+          <t>ਖਿਆਲਾ ਕਲਾਂ</t>
         </is>
       </c>
       <c r="D157" s="7" t="inlineStr">
         <is>
-          <t>Boparai Khurd</t>
+          <t>Khiala Kalan</t>
         </is>
       </c>
       <c r="E157" s="8" t="n">
@@ -8042,17 +8042,17 @@
       </c>
       <c r="B158" s="3" t="inlineStr">
         <is>
-          <t>ਕੋਲੇਵਾਲ</t>
+          <t>ਖਿਆਲਾ ਕਲਾਂ</t>
         </is>
       </c>
       <c r="C158" s="3" t="inlineStr">
         <is>
-          <t>ਕੋਲੇਵਾਲ</t>
+          <t>ਖਿਆਲਾ ਕਲਾਂ</t>
         </is>
       </c>
       <c r="D158" s="3" t="inlineStr">
         <is>
-          <t>Kolewal</t>
+          <t>Khiala Kalan</t>
         </is>
       </c>
       <c r="E158" s="4" t="n">
@@ -8089,17 +8089,17 @@
       </c>
       <c r="B159" s="7" t="inlineStr">
         <is>
-          <t>ਬਰਾੜ</t>
+          <t>ਬੋਪਾਰਾਏ ਬਾਜ ਸਿੰਘ</t>
         </is>
       </c>
       <c r="C159" s="7" t="inlineStr">
         <is>
-          <t>ਬਰਾੜ</t>
+          <t>ਬੋਪਾਰਾਏ ਬਾਜ ਸਿੰਘ</t>
         </is>
       </c>
       <c r="D159" s="7" t="inlineStr">
         <is>
-          <t>Brar</t>
+          <t>Bopa Rai Baj Singh</t>
         </is>
       </c>
       <c r="E159" s="8" t="n">
@@ -8136,17 +8136,17 @@
       </c>
       <c r="B160" s="3" t="inlineStr">
         <is>
-          <t>ਬਰਾੜ</t>
+          <t>ਬੋਪਾਰਾਏ ਬਾਜ ਸਿੰਘ</t>
         </is>
       </c>
       <c r="C160" s="3" t="inlineStr">
         <is>
-          <t>ਬਰਾੜ</t>
+          <t>ਬੋਪਾਰਾਏ ਬਾਜ ਸਿੰਘ</t>
         </is>
       </c>
       <c r="D160" s="3" t="inlineStr">
         <is>
-          <t>Brar</t>
+          <t>Bopa Rai Baj Singh</t>
         </is>
       </c>
       <c r="E160" s="4" t="n">
@@ -8183,17 +8183,17 @@
       </c>
       <c r="B161" s="7" t="inlineStr">
         <is>
-          <t>ਮਾਦੇਕੇ</t>
+          <t>ਕਲੇਰ</t>
         </is>
       </c>
       <c r="C161" s="7" t="inlineStr">
         <is>
-          <t>ਮਾਦੇਕੇ</t>
+          <t>ਕਲੇਰ</t>
         </is>
       </c>
       <c r="D161" s="7" t="inlineStr">
         <is>
-          <t>Madeke</t>
+          <t>Kaler</t>
         </is>
       </c>
       <c r="E161" s="8" t="n">
@@ -8230,17 +8230,17 @@
       </c>
       <c r="B162" s="3" t="inlineStr">
         <is>
-          <t>ਖਿਆਲਾ ਕਲਾਂ</t>
+          <t>ਕਲੇਰ</t>
         </is>
       </c>
       <c r="C162" s="3" t="inlineStr">
         <is>
-          <t>ਖਿਆਲਾ ਕਲਾਂ</t>
+          <t>ਕਲੇਰ</t>
         </is>
       </c>
       <c r="D162" s="3" t="inlineStr">
         <is>
-          <t>Khiala Kalan</t>
+          <t>Kaler</t>
         </is>
       </c>
       <c r="E162" s="4" t="n">
@@ -8277,17 +8277,17 @@
       </c>
       <c r="B163" s="7" t="inlineStr">
         <is>
-          <t>ਖਿਆਲਾ ਕਲਾਂ</t>
+          <t>ਬਾਬਾ ਮਾਈਕ ਸ਼ਾਹ ਕਾਲੋਨੀ</t>
         </is>
       </c>
       <c r="C163" s="7" t="inlineStr">
         <is>
-          <t>ਖਿਆਲਾ ਕਲਾਂ</t>
+          <t>ਬਾਬਾ ਮਾਈਕ ਸ਼ਾਹ ਕਾਲੋਨੀ</t>
         </is>
       </c>
       <c r="D163" s="7" t="inlineStr">
         <is>
-          <t>Khiala Kalan</t>
+          <t>Baba Mike Shah Colony</t>
         </is>
       </c>
       <c r="E163" s="8" t="n">
@@ -8371,17 +8371,17 @@
       </c>
       <c r="B165" s="7" t="inlineStr">
         <is>
-          <t>ਬੋਪਾ ਰਾਏ ਬਾਜ ਸਿੰਘ</t>
+          <t>ਕੋਹਾਲੀ</t>
         </is>
       </c>
       <c r="C165" s="7" t="inlineStr">
         <is>
-          <t>ਬੋਪਾ ਰਾਏ ਬਾਜ ਸਿੰਘ</t>
+          <t>ਕੋਹਾਲੀ</t>
         </is>
       </c>
       <c r="D165" s="7" t="inlineStr">
         <is>
-          <t>Bopa Rai Baj Singh</t>
+          <t>Kohali</t>
         </is>
       </c>
       <c r="E165" s="8" t="n">
@@ -8418,17 +8418,17 @@
       </c>
       <c r="B166" s="3" t="inlineStr">
         <is>
-          <t>ਬੋਪਾ ਰਾਏ ਬਾਜ ਸਿੰਘ</t>
+          <t>ਕੋਹਾਲੀ</t>
         </is>
       </c>
       <c r="C166" s="3" t="inlineStr">
         <is>
-          <t>ਬੋਪਾ ਰਾਏ ਬਾਜ ਸਿੰਘ</t>
+          <t>ਕੋਹਾਲੀ</t>
         </is>
       </c>
       <c r="D166" s="3" t="inlineStr">
         <is>
-          <t>Bopa Rai Baj Singh</t>
+          <t>Kohali</t>
         </is>
       </c>
       <c r="E166" s="4" t="n">
@@ -8465,17 +8465,17 @@
       </c>
       <c r="B167" s="7" t="inlineStr">
         <is>
-          <t>ਕਲੇਰ</t>
+          <t>ਕੋਹਾਲੀ</t>
         </is>
       </c>
       <c r="C167" s="7" t="inlineStr">
         <is>
-          <t>ਕਲੇਰ</t>
+          <t>ਕੋਹਾਲੀ</t>
         </is>
       </c>
       <c r="D167" s="7" t="inlineStr">
         <is>
-          <t>Kaler</t>
+          <t>Kohali</t>
         </is>
       </c>
       <c r="E167" s="8" t="n">
@@ -8512,17 +8512,17 @@
       </c>
       <c r="B168" s="3" t="inlineStr">
         <is>
-          <t>ਕਲੇਰ</t>
+          <t>ਕੋਹਾਲੀ</t>
         </is>
       </c>
       <c r="C168" s="3" t="inlineStr">
         <is>
-          <t>ਕਲੇਰ</t>
+          <t>ਕੋਹਾਲੀ</t>
         </is>
       </c>
       <c r="D168" s="3" t="inlineStr">
         <is>
-          <t>Kaler</t>
+          <t>Kohali</t>
         </is>
       </c>
       <c r="E168" s="4" t="n">
@@ -8559,17 +8559,17 @@
       </c>
       <c r="B169" s="7" t="inlineStr">
         <is>
-          <t>ਬਾਬਾ ਮੀਕੇ ਸ਼ਾਹ ਕਲੋਨੀ</t>
+          <t>ਭਿੱਟੇਵੱਡ</t>
         </is>
       </c>
       <c r="C169" s="7" t="inlineStr">
         <is>
-          <t>ਬਾਬਾ ਮੀਕੇ ਸ਼ਾਹ ਕਲੋਨੀ</t>
+          <t>ਭਿੱਟੇਵੱਡ</t>
         </is>
       </c>
       <c r="D169" s="7" t="inlineStr">
         <is>
-          <t>Baba Meeke Shah Colony</t>
+          <t>Bhittewad</t>
         </is>
       </c>
       <c r="E169" s="8" t="n">
@@ -8606,17 +8606,17 @@
       </c>
       <c r="B170" s="3" t="inlineStr">
         <is>
-          <t>ਖਿਆਲਾ ਖੁਰਦ</t>
+          <t>ਭਿੱਟੇਵੱਡ</t>
         </is>
       </c>
       <c r="C170" s="3" t="inlineStr">
         <is>
-          <t>ਖਿਆਲਾ ਖੁਰਦ</t>
+          <t>ਭਿੱਟੇਵੱਡ</t>
         </is>
       </c>
       <c r="D170" s="3" t="inlineStr">
         <is>
-          <t>Khiala Khurd</t>
+          <t>Bhittewad</t>
         </is>
       </c>
       <c r="E170" s="4" t="n">
@@ -8653,17 +8653,17 @@
       </c>
       <c r="B171" s="7" t="inlineStr">
         <is>
-          <t>ਕੋਹਾਲੀ</t>
+          <t>ਭਿੱਟੇਵੱਡ</t>
         </is>
       </c>
       <c r="C171" s="7" t="inlineStr">
         <is>
-          <t>ਕੋਹਾਲੀ</t>
+          <t>ਭਿੱਟੇਵੱਡ</t>
         </is>
       </c>
       <c r="D171" s="7" t="inlineStr">
         <is>
-          <t>Kohali</t>
+          <t>Bhittewad</t>
         </is>
       </c>
       <c r="E171" s="8" t="n">
@@ -8700,17 +8700,17 @@
       </c>
       <c r="B172" s="3" t="inlineStr">
         <is>
-          <t>ਕੋਹਾਲੀ</t>
+          <t>ਬੱਗਾ ਖੁਰਦ</t>
         </is>
       </c>
       <c r="C172" s="3" t="inlineStr">
         <is>
-          <t>ਕੋਹਾਲੀ</t>
+          <t>ਬੱਗਾ ਖੁਰਦ</t>
         </is>
       </c>
       <c r="D172" s="3" t="inlineStr">
         <is>
-          <t>Kohali</t>
+          <t>Bagga Khurd</t>
         </is>
       </c>
       <c r="E172" s="4" t="n">
@@ -8747,17 +8747,17 @@
       </c>
       <c r="B173" s="7" t="inlineStr">
         <is>
-          <t>ਕੋਹਾਲੀ</t>
+          <t>ਬੱਗਾ ਕਲਾਂ</t>
         </is>
       </c>
       <c r="C173" s="7" t="inlineStr">
         <is>
-          <t>ਕੋਹਾਲੀ</t>
+          <t>ਬੱਗਾ ਕਲਾਂ</t>
         </is>
       </c>
       <c r="D173" s="7" t="inlineStr">
         <is>
-          <t>Kohali</t>
+          <t>Bagga Kalan</t>
         </is>
       </c>
       <c r="E173" s="8" t="n">
@@ -8794,17 +8794,17 @@
       </c>
       <c r="B174" s="3" t="inlineStr">
         <is>
-          <t>ਕੋਹਾਲੀ + ਰੱਖ ਕੋਹਾਲੀ</t>
+          <t>ਬੱਗਾ ਕਲਾਂ</t>
         </is>
       </c>
       <c r="C174" s="3" t="inlineStr">
         <is>
-          <t>ਕੋਹਾਲੀ + ਰੱਖ ਕੋਹਾਲੀ</t>
+          <t>ਬੱਗਾ ਕਲਾਂ</t>
         </is>
       </c>
       <c r="D174" s="3" t="inlineStr">
         <is>
-          <t>Kohali + Rakh Kohali</t>
+          <t>Bagga Kalan</t>
         </is>
       </c>
       <c r="E174" s="4" t="n">
@@ -8841,17 +8841,17 @@
       </c>
       <c r="B175" s="7" t="inlineStr">
         <is>
-          <t>ਭਿੱਟੇਵੱਡ</t>
+          <t>ਧਾਰੀਵਾਲ</t>
         </is>
       </c>
       <c r="C175" s="7" t="inlineStr">
         <is>
-          <t>ਭਿੱਟੇਵੱਡ</t>
+          <t>ਧਾਰੀਵਾਲ</t>
         </is>
       </c>
       <c r="D175" s="7" t="inlineStr">
         <is>
-          <t>Bhittewad</t>
+          <t>Dhariwal</t>
         </is>
       </c>
       <c r="E175" s="8" t="n">
@@ -8888,17 +8888,17 @@
       </c>
       <c r="B176" s="3" t="inlineStr">
         <is>
-          <t>ਭਿੱਟੇਵੱਡ</t>
+          <t>ਲੱਲਾ ਅਫ਼ਗ਼ਾਨਾ</t>
         </is>
       </c>
       <c r="C176" s="3" t="inlineStr">
         <is>
-          <t>ਭਿੱਟੇਵੱਡ</t>
+          <t>ਲੱਲਾ ਅਫ਼ਗ਼ਾਨਾ</t>
         </is>
       </c>
       <c r="D176" s="3" t="inlineStr">
         <is>
-          <t>Bhittewad</t>
+          <t>Lalla Afgana</t>
         </is>
       </c>
       <c r="E176" s="4" t="n">
@@ -8935,17 +8935,17 @@
       </c>
       <c r="B177" s="7" t="inlineStr">
         <is>
-          <t>ਭਿੱਟੇਵੱਡ</t>
+          <t>ਹਰਸ਼ਾ ਛੀਨਾ (ਅਬਾਦੀ ਉੱਚਾ ਕਿਲ੍ਹਾ)</t>
         </is>
       </c>
       <c r="C177" s="7" t="inlineStr">
         <is>
-          <t>ਭਿੱਟੇਵੱਡ</t>
+          <t>ਹਰਸ਼ਾ ਛੀਨਾ (ਅਬਾਦੀ ਉੱਚਾ ਕਿਲ੍ਹਾ)</t>
         </is>
       </c>
       <c r="D177" s="7" t="inlineStr">
         <is>
-          <t>Bhittewad</t>
+          <t>Harsha Chhina (Abadi Ucha Qila)</t>
         </is>
       </c>
       <c r="E177" s="8" t="n">
@@ -8982,17 +8982,17 @@
       </c>
       <c r="B178" s="3" t="inlineStr">
         <is>
-          <t>ਬੱਗਾ ਖੁਰਦ + ਓਵਰਸੀਜ਼ ਇਲੈਕਟਰ</t>
+          <t>ਹਰਸ਼ਾ ਛੀਨਾ (ਅਬਾਦੀ ਉੱਚਾ ਕਿਲ੍ਹਾ)</t>
         </is>
       </c>
       <c r="C178" s="3" t="inlineStr">
         <is>
-          <t>ਬੱਗਾ ਖੁਰਦ + ਓਵਰਸੀਜ਼ ਇਲੈਕਟਰ</t>
+          <t>ਹਰਸ਼ਾ ਛੀਨਾ (ਅਬਾਦੀ ਉੱਚਾ ਕਿਲ੍ਹਾ)</t>
         </is>
       </c>
       <c r="D178" s="3" t="inlineStr">
         <is>
-          <t>Bagga Khurd + Overseas Elector</t>
+          <t>Harsha Chhina (Abadi Ucha Qila)</t>
         </is>
       </c>
       <c r="E178" s="4" t="n">
@@ -9029,17 +9029,17 @@
       </c>
       <c r="B179" s="7" t="inlineStr">
         <is>
-          <t>ਬੱਗਾ ਕਲਾਂ</t>
+          <t>ਹਰਸ਼ਾ ਛੀਨਾ (ਅਬਾਦੀ ਵਿਚਲਾ ਕਿਲ੍ਹਾ)</t>
         </is>
       </c>
       <c r="C179" s="7" t="inlineStr">
         <is>
-          <t>ਬੱਗਾ ਕਲਾਂ</t>
+          <t>ਹਰਸ਼ਾ ਛੀਨਾ (ਅਬਾਦੀ ਵਿਚਲਾ ਕਿਲ੍ਹਾ)</t>
         </is>
       </c>
       <c r="D179" s="7" t="inlineStr">
         <is>
-          <t>Bagga Kalan</t>
+          <t>Harsha Chhina (Abadi Vichla Qila)</t>
         </is>
       </c>
       <c r="E179" s="8" t="n">
@@ -9076,17 +9076,17 @@
       </c>
       <c r="B180" s="3" t="inlineStr">
         <is>
-          <t>ਬੱਗਾ ਕਲਾਂ</t>
+          <t>ਹਰਸ਼ਾ ਛੀਨਾ (ਅਬਾਦੀ ਵਿਚਲਾ ਕਿਲ੍ਹਾ)</t>
         </is>
       </c>
       <c r="C180" s="3" t="inlineStr">
         <is>
-          <t>ਬੱਗਾ ਕਲਾਂ</t>
+          <t>ਹਰਸ਼ਾ ਛੀਨਾ (ਅਬਾਦੀ ਵਿਚਲਾ ਕਿਲ੍ਹਾ)</t>
         </is>
       </c>
       <c r="D180" s="3" t="inlineStr">
         <is>
-          <t>Bagga Kalan</t>
+          <t>Harsha Chhina (Abadi Vichla Qila)</t>
         </is>
       </c>
       <c r="E180" s="4" t="n">
@@ -9123,17 +9123,17 @@
       </c>
       <c r="B181" s="7" t="inlineStr">
         <is>
-          <t>ਧਾਰੀਵਾਲ</t>
+          <t>ਹਰਸ਼ਾ ਛੀਨਾ (ਅਬਾਦੀ ਵਿਚਲਾ ਕਿਲ੍ਹਾ)</t>
         </is>
       </c>
       <c r="C181" s="7" t="inlineStr">
         <is>
-          <t>ਧਾਰੀਵਾਲ</t>
+          <t>ਹਰਸ਼ਾ ਛੀਨਾ (ਅਬਾਦੀ ਵਿਚਲਾ ਕਿਲ੍ਹਾ)</t>
         </is>
       </c>
       <c r="D181" s="7" t="inlineStr">
         <is>
-          <t>Dhariwal</t>
+          <t>Harsha Chhina (Abadi Vichla Qila)</t>
         </is>
       </c>
       <c r="E181" s="8" t="n">
@@ -9170,17 +9170,17 @@
       </c>
       <c r="B182" s="3" t="inlineStr">
         <is>
-          <t>ਲੱਲਾ ਅਫਗਾਨਾ</t>
+          <t>ਹਰਸ਼ਾ ਛੀਨਾ (ਅਬਾਦੀ ਕੁੱਕੜਾਂਵਾਲਾ)</t>
         </is>
       </c>
       <c r="C182" s="3" t="inlineStr">
         <is>
-          <t>ਲੱਲਾ ਅਫਗਾਨਾ</t>
+          <t>ਹਰਸ਼ਾ ਛੀਨਾ (ਅਬਾਦੀ ਕੁੱਕੜਾਂਵਾਲਾ)</t>
         </is>
       </c>
       <c r="D182" s="3" t="inlineStr">
         <is>
-          <t>Lalla Afgana</t>
+          <t>Harsha Chhina (Abadi Kukkranwala)</t>
         </is>
       </c>
       <c r="E182" s="4" t="n">
@@ -9217,17 +9217,17 @@
       </c>
       <c r="B183" s="7" t="inlineStr">
         <is>
-          <t>ਹਰਸ਼ਾ ਛੀਨਾ (ਅਬਾਦੀ ਉੱਚਾ ਕਿਲਾ)</t>
+          <t>ਹਰਸ਼ਾ ਛੀਨਾ (ਅਬਾਦੀ ਸਬਾਜਪੁਰ)</t>
         </is>
       </c>
       <c r="C183" s="7" t="inlineStr">
         <is>
-          <t>ਹਰਸ਼ਾ ਛੀਨਾ (ਅਬਾਦੀ ਉੱਚਾ ਕਿਲਾ)</t>
+          <t>ਹਰਸ਼ਾ ਛੀਨਾ (ਅਬਾਦੀ ਸਬਾਜਪੁਰ)</t>
         </is>
       </c>
       <c r="D183" s="7" t="inlineStr">
         <is>
-          <t>Harsha Chhina (Abadi Ucha Kila)</t>
+          <t>Harsha Chhina (Abadi Sabajpur)</t>
         </is>
       </c>
       <c r="E183" s="8" t="n">
@@ -9264,17 +9264,17 @@
       </c>
       <c r="B184" s="3" t="inlineStr">
         <is>
-          <t>ਹਰਸ਼ਾ ਛੀਨਾ (ਅਬਾਦੀ ਉੱਚਾ ਕਿਲਾ)</t>
+          <t>ਹਰਸ਼ਾ ਛੀਨਾ (ਅਬਾਦੀ ਸਬਾਜਪੁਰ)</t>
         </is>
       </c>
       <c r="C184" s="3" t="inlineStr">
         <is>
-          <t>ਹਰਸ਼ਾ ਛੀਨਾ (ਅਬਾਦੀ ਉੱਚਾ ਕਿਲਾ)</t>
+          <t>ਹਰਸ਼ਾ ਛੀਨਾ (ਅਬਾਦੀ ਸਬਾਜਪੁਰ)</t>
         </is>
       </c>
       <c r="D184" s="3" t="inlineStr">
         <is>
-          <t>Harsha Chhina (Abadi Ucha Kila)</t>
+          <t>Harsha Chhina (Abadi Sabajpur)</t>
         </is>
       </c>
       <c r="E184" s="4" t="n">
@@ -9311,17 +9311,17 @@
       </c>
       <c r="B185" s="7" t="inlineStr">
         <is>
-          <t>ਹਰਸ਼ਾ ਛੀਨਾ (ਅਬਾਦੀ ਵਿਚਲਾ ਕਿਲਾ)</t>
+          <t>ਨੰਗਲ ਤੋਲਾ</t>
         </is>
       </c>
       <c r="C185" s="7" t="inlineStr">
         <is>
-          <t>ਹਰਸ਼ਾ ਛੀਨਾ (ਅਬਾਦੀ ਵਿਚਲਾ ਕਿਲਾ)</t>
+          <t>ਨੰਗਲ ਤੋਲਾ</t>
         </is>
       </c>
       <c r="D185" s="7" t="inlineStr">
         <is>
-          <t>Harsha Chhina (Abadi Vichla Kila)</t>
+          <t>Nangal Tola</t>
         </is>
       </c>
       <c r="E185" s="8" t="n">
@@ -9358,17 +9358,17 @@
       </c>
       <c r="B186" s="3" t="inlineStr">
         <is>
-          <t>ਹਰਸ਼ਾ ਛੀਨਾ (ਅਬਾਦੀ ਵਿਚਲਾ ਕਿਲਾ)</t>
+          <t>ਨੰਗਲ ਤੋਲਾ</t>
         </is>
       </c>
       <c r="C186" s="3" t="inlineStr">
         <is>
-          <t>ਹਰਸ਼ਾ ਛੀਨਾ (ਅਬਾਦੀ ਵਿਚਲਾ ਕਿਲਾ)</t>
+          <t>ਨੰਗਲ ਤੋਲਾ</t>
         </is>
       </c>
       <c r="D186" s="3" t="inlineStr">
         <is>
-          <t>Harsha Chhina (Abadi Vichla Kila)</t>
+          <t>Nangal Tola</t>
         </is>
       </c>
       <c r="E186" s="4" t="n">
@@ -9405,17 +9405,17 @@
       </c>
       <c r="B187" s="7" t="inlineStr">
         <is>
-          <t>ਹਰਸ਼ਾ ਛੀਨਾ (ਅਬਾਦੀ ਵਿਚਲਾ ਕਿਲਾ)</t>
+          <t>ਝੰਜੋਟੀ</t>
         </is>
       </c>
       <c r="C187" s="7" t="inlineStr">
         <is>
-          <t>ਹਰਸ਼ਾ ਛੀਨਾ (ਅਬਾਦੀ ਵਿਚਲਾ ਕਿਲਾ)</t>
+          <t>ਝੰਜੋਟੀ</t>
         </is>
       </c>
       <c r="D187" s="7" t="inlineStr">
         <is>
-          <t>Harsha Chhina (Abadi Vichla Kila)</t>
+          <t>Jhanjoti</t>
         </is>
       </c>
       <c r="E187" s="8" t="n">
@@ -9452,17 +9452,17 @@
       </c>
       <c r="B188" s="3" t="inlineStr">
         <is>
-          <t>ਹਰਸ਼ਾ ਛੀਨਾ (ਕੁੱਕੜਾਂਵਾਲਾ)</t>
+          <t>ਝੰਜੋਟੀ</t>
         </is>
       </c>
       <c r="C188" s="3" t="inlineStr">
         <is>
-          <t>ਹਰਸ਼ਾ ਛੀਨਾ (ਕੁੱਕੜਾਂਵਾਲਾ)</t>
+          <t>ਝੰਜੋਟੀ</t>
         </is>
       </c>
       <c r="D188" s="3" t="inlineStr">
         <is>
-          <t>Harsha Chhina (Kukranwala)</t>
+          <t>Jhanjoti</t>
         </is>
       </c>
       <c r="E188" s="4" t="n">
@@ -9499,17 +9499,17 @@
       </c>
       <c r="B189" s="7" t="inlineStr">
         <is>
-          <t>ਹਰਸ਼ਾ ਛੀਨਾ (ਅਬਾਦੀ ਸਬਾਜਪੁਰ)</t>
+          <t>ਝੰਜੋਟੀ</t>
         </is>
       </c>
       <c r="C189" s="7" t="inlineStr">
         <is>
-          <t>ਹਰਸ਼ਾ ਛੀਨਾ (ਅਬਾਦੀ ਸਬਾਜਪੁਰ)</t>
+          <t>ਝੰਜੋਟੀ</t>
         </is>
       </c>
       <c r="D189" s="7" t="inlineStr">
         <is>
-          <t>Harsha Chhina (Abadi Sabajpur)</t>
+          <t>Jhanjoti</t>
         </is>
       </c>
       <c r="E189" s="8" t="n">
@@ -9546,17 +9546,17 @@
       </c>
       <c r="B190" s="3" t="inlineStr">
         <is>
-          <t>ਹਰਸ਼ਾ ਛੀਨਾ (ਅਬਾਦੀ ਸਬਾਜਪੁਰ)</t>
+          <t>ਚੈਨਪੁਰ</t>
         </is>
       </c>
       <c r="C190" s="3" t="inlineStr">
         <is>
-          <t>ਹਰਸ਼ਾ ਛੀਨਾ (ਅਬਾਦੀ ਸਬਾਜਪੁਰ)</t>
+          <t>ਚੈਨਪੁਰ</t>
         </is>
       </c>
       <c r="D190" s="3" t="inlineStr">
         <is>
-          <t>Harsha Chhina (Abadi Sabajpur)</t>
+          <t>Chainpur</t>
         </is>
       </c>
       <c r="E190" s="4" t="n">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="B191" s="7" t="inlineStr">
         <is>
-          <t>ਨੰਗਲ ਤੋਲਾ</t>
+          <t>ਬਲਾਗਣ</t>
         </is>
       </c>
       <c r="C191" s="7" t="inlineStr">
         <is>
-          <t>ਨੰਗਲ ਤੋਲਾ</t>
+          <t>ਬਲਾਗਣ</t>
         </is>
       </c>
       <c r="D191" s="7" t="inlineStr">
         <is>
-          <t>Nangal Tola</t>
+          <t>Balagan</t>
         </is>
       </c>
       <c r="E191" s="8" t="n">
@@ -9640,17 +9640,17 @@
       </c>
       <c r="B192" s="3" t="inlineStr">
         <is>
-          <t>ਨੰਗਲ ਤੋਲਾ</t>
+          <t>ਬਲਾਗਣ ਸਿੱਧੂ</t>
         </is>
       </c>
       <c r="C192" s="3" t="inlineStr">
         <is>
-          <t>ਨੰਗਲ ਤੋਲਾ</t>
+          <t>ਬਲਾਗਣ ਸਿੱਧੂ</t>
         </is>
       </c>
       <c r="D192" s="3" t="inlineStr">
         <is>
-          <t>Nangal Tola</t>
+          <t>Balagan Sidhu</t>
         </is>
       </c>
       <c r="E192" s="4" t="n">
@@ -9687,17 +9687,17 @@
       </c>
       <c r="B193" s="7" t="inlineStr">
         <is>
-          <t>ਝੋਜੇਟੀ</t>
+          <t>ਕੋਟਲਾ ਡੂਮ</t>
         </is>
       </c>
       <c r="C193" s="7" t="inlineStr">
         <is>
-          <t>ਝੋਜੇਟੀ</t>
+          <t>ਕੋਟਲਾ ਡੂਮ</t>
         </is>
       </c>
       <c r="D193" s="7" t="inlineStr">
         <is>
-          <t>Jhojeti</t>
+          <t>Kotla Doom</t>
         </is>
       </c>
       <c r="E193" s="8" t="n">
@@ -9734,17 +9734,17 @@
       </c>
       <c r="B194" s="3" t="inlineStr">
         <is>
-          <t>ਝੰਜੋਟੀ</t>
+          <t>ਕੋਟਲਾ ਡੂਮ</t>
         </is>
       </c>
       <c r="C194" s="3" t="inlineStr">
         <is>
-          <t>ਝੰਜੋਟੀ</t>
+          <t>ਕੋਟਲਾ ਡੂਮ</t>
         </is>
       </c>
       <c r="D194" s="3" t="inlineStr">
         <is>
-          <t>Jhanjoti</t>
+          <t>Kotla Doom</t>
         </is>
       </c>
       <c r="E194" s="4" t="n">
@@ -9781,17 +9781,17 @@
       </c>
       <c r="B195" s="7" t="inlineStr">
         <is>
-          <t>ਝੰਜੋਟੀ</t>
+          <t>ਸੈਦਪੁਰ</t>
         </is>
       </c>
       <c r="C195" s="7" t="inlineStr">
         <is>
-          <t>ਝੰਜੋਟੀ</t>
+          <t>ਸੈਦਪੁਰ</t>
         </is>
       </c>
       <c r="D195" s="7" t="inlineStr">
         <is>
-          <t>Jhanjoti</t>
+          <t>Saidpur</t>
         </is>
       </c>
       <c r="E195" s="8" t="n">
@@ -9828,17 +9828,17 @@
       </c>
       <c r="B196" s="3" t="inlineStr">
         <is>
-          <t>ਚੈਨਪੁਰ</t>
+          <t>ਰਡਾਲਾ</t>
         </is>
       </c>
       <c r="C196" s="3" t="inlineStr">
         <is>
-          <t>ਚੈਨਪੁਰ</t>
+          <t>ਰਡਾਲਾ</t>
         </is>
       </c>
       <c r="D196" s="3" t="inlineStr">
         <is>
-          <t>Chainpur</t>
+          <t>Radala</t>
         </is>
       </c>
       <c r="E196" s="4" t="n">
@@ -9875,17 +9875,17 @@
       </c>
       <c r="B197" s="7" t="inlineStr">
         <is>
-          <t>ਬਲੱਗਣ</t>
+          <t>ਰਾਜਾ ਸਾਂਸੀ</t>
         </is>
       </c>
       <c r="C197" s="7" t="inlineStr">
         <is>
-          <t>ਬਲੱਗਣ</t>
+          <t>ਰਾਜਾ ਸਾਂਸੀ</t>
         </is>
       </c>
       <c r="D197" s="7" t="inlineStr">
         <is>
-          <t>Balaggan</t>
+          <t>Raja Sansi</t>
         </is>
       </c>
       <c r="E197" s="8" t="n">
@@ -9922,17 +9922,17 @@
       </c>
       <c r="B198" s="3" t="inlineStr">
         <is>
-          <t>ਬੱਲਗਣ ਸਿੰਧੂ</t>
+          <t>ਰਾਜਾ ਸਾਂਸੀ</t>
         </is>
       </c>
       <c r="C198" s="3" t="inlineStr">
         <is>
-          <t>ਬੱਲਗਣ ਸਿੰਧੂ</t>
+          <t>ਰਾਜਾ ਸਾਂਸੀ</t>
         </is>
       </c>
       <c r="D198" s="3" t="inlineStr">
         <is>
-          <t>Balaggan Sindhu</t>
+          <t>Raja Sansi</t>
         </is>
       </c>
       <c r="E198" s="4" t="n">
@@ -9969,17 +9969,17 @@
       </c>
       <c r="B199" s="7" t="inlineStr">
         <is>
-          <t>ਕੋਟਲਾ ਡੂਮ</t>
+          <t>ਰਾਜਾ ਸਾਂਸੀ</t>
         </is>
       </c>
       <c r="C199" s="7" t="inlineStr">
         <is>
-          <t>ਕੋਟਲਾ ਡੂਮ</t>
+          <t>ਰਾਜਾ ਸਾਂਸੀ</t>
         </is>
       </c>
       <c r="D199" s="7" t="inlineStr">
         <is>
-          <t>Kotla Doom</t>
+          <t>Raja Sansi</t>
         </is>
       </c>
       <c r="E199" s="8" t="n">
@@ -10016,17 +10016,17 @@
       </c>
       <c r="B200" s="3" t="inlineStr">
         <is>
-          <t>ਕੋਟਲਾ ਡੂਮ</t>
+          <t>ਰਾਜਾ ਸਾਂਸੀ</t>
         </is>
       </c>
       <c r="C200" s="3" t="inlineStr">
         <is>
-          <t>ਕੋਟਲਾ ਡੂਮ</t>
+          <t>ਰਾਜਾ ਸਾਂਸੀ</t>
         </is>
       </c>
       <c r="D200" s="3" t="inlineStr">
         <is>
-          <t>Kotla Doom</t>
+          <t>Raja Sansi</t>
         </is>
       </c>
       <c r="E200" s="4" t="n">
@@ -10063,17 +10063,17 @@
       </c>
       <c r="B201" s="7" t="inlineStr">
         <is>
-          <t>ਸੈਦਪੁਰ</t>
+          <t>ਰਾਜਾ ਸਾਂਸੀ</t>
         </is>
       </c>
       <c r="C201" s="7" t="inlineStr">
         <is>
-          <t>ਸੈਦਪੁਰ</t>
+          <t>ਰਾਜਾ ਸਾਂਸੀ</t>
         </is>
       </c>
       <c r="D201" s="7" t="inlineStr">
         <is>
-          <t>Saidpur</t>
+          <t>Raja Sansi</t>
         </is>
       </c>
       <c r="E201" s="8" t="n">
@@ -10110,17 +10110,17 @@
       </c>
       <c r="B202" s="3" t="inlineStr">
         <is>
-          <t>ਰਡਾਲਾ</t>
+          <t>ਰਾਜਾ ਸਾਂਸੀ</t>
         </is>
       </c>
       <c r="C202" s="3" t="inlineStr">
         <is>
-          <t>ਰਡਾਲਾ</t>
+          <t>ਰਾਜਾ ਸਾਂਸੀ</t>
         </is>
       </c>
       <c r="D202" s="3" t="inlineStr">
         <is>
-          <t>Radala</t>
+          <t>Raja Sansi</t>
         </is>
       </c>
       <c r="E202" s="4" t="n">
@@ -10157,17 +10157,17 @@
       </c>
       <c r="B203" s="7" t="inlineStr">
         <is>
-          <t>ਵਾਰਡ ਨੰ. 1 ਮੁਹੱਲਾ ਗਾਂਧੀ ਨਗਰ + ਵਾਰਡ ਨੰ.1 ਮੁਹੱਲਾ ਗਾਂਧੀ ਨਗਰ + ਵਾਰਡ ਨੰ.1 ਮੁਹੱਲਾ ਗਾਂਧੀ ਨਗਰ + ਵਾਰਡ ਨੰ.1 ਮੁਹੱਲਾ ਗਾਂਧੀ ਨਗਰ</t>
+          <t>ਰਾਜਾ ਸਾਂਸੀ</t>
         </is>
       </c>
       <c r="C203" s="7" t="inlineStr">
         <is>
-          <t>ਵਾਰਡ ਨੰ. 1 ਮੁਹੱਲਾ ਗਾਂਧੀ ਨਗਰ + ਵਾਰਡ ਨੰ.1 ਮੁਹੱਲਾ ਗਾਂਧੀ ਨਗਰ + ਵਾਰਡ ਨੰ.1 ਮੁਹੱਲਾ ਗਾਂਧੀ ਨਗਰ + ਵਾਰਡ ਨੰ.1 ਮੁਹੱਲਾ ਗਾਂਧੀ ਨਗਰ</t>
+          <t>ਰਾਜਾ ਸਾਂਸੀ</t>
         </is>
       </c>
       <c r="D203" s="7" t="inlineStr">
         <is>
-          <t>Ward No. 1 Muhalla Gandhi Nagar + Ward No. 1 Muhalla Gandhi Nagar + Ward No. 1 Muhalla Gandhi Nagar + Ward No. 1 Muhalla Gandhi Nagar</t>
+          <t>Raja Sansi</t>
         </is>
       </c>
       <c r="E203" s="8" t="n">
@@ -10204,17 +10204,17 @@
       </c>
       <c r="B204" s="3" t="inlineStr">
         <is>
-          <t>ਵਾਰਡ ਨੰ.12 ਰਾਜਾਸਾਂਸੀ ਮੁਹੱਲਾ ਗਾਂਧੀ ਨਗਰ + ਵਾਰਡ ਨੰ.12 ਮੁਹੱਲਾ ਗਾਂਧੀ ਨਗਰ</t>
+          <t>ਰਾਜਾ ਸਾਂਸੀ</t>
         </is>
       </c>
       <c r="C204" s="3" t="inlineStr">
         <is>
-          <t>ਵਾਰਡ ਨੰ.12 ਰਾਜਾਸਾਂਸੀ ਮੁਹੱਲਾ ਗਾਂਧੀ ਨਗਰ + ਵਾਰਡ ਨੰ.12 ਮੁਹੱਲਾ ਗਾਂਧੀ ਨਗਰ</t>
+          <t>ਰਾਜਾ ਸਾਂਸੀ</t>
         </is>
       </c>
       <c r="D204" s="3" t="inlineStr">
         <is>
-          <t>Ward No. 12 Rajasansi Muhalla Gandhi Nagar + Ward No. 12 Muhalla Gandhi Nagar</t>
+          <t>Raja Sansi</t>
         </is>
       </c>
       <c r="E204" s="4" t="n">
@@ -10251,17 +10251,17 @@
       </c>
       <c r="B205" s="7" t="inlineStr">
         <is>
-          <t>ਵਾਰਡ ਨੰ 2 ਮੁਹੱਲਾ ਗਾਧੀ ਨਗਰ ਰਾਜਾਸਾਂਸੀ + ਵਾਰਡ ਨੰ 2 ਮੁਹੱਲਾ ਗਾਧੀ ਨਗਰ ਰਾਜਾਸਾਂਸੀ</t>
+          <t>ਰਾਜਾ ਸਾਂਸੀ</t>
         </is>
       </c>
       <c r="C205" s="7" t="inlineStr">
         <is>
-          <t>ਵਾਰਡ ਨੰ 2 ਮੁਹੱਲਾ ਗਾਧੀ ਨਗਰ ਰਾਜਾਸਾਂਸੀ + ਵਾਰਡ ਨੰ 2 ਮੁਹੱਲਾ ਗਾਧੀ ਨਗਰ ਰਾਜਾਸਾਂਸੀ</t>
+          <t>ਰਾਜਾ ਸਾਂਸੀ</t>
         </is>
       </c>
       <c r="D205" s="7" t="inlineStr">
         <is>
-          <t>Ward No 2 Muhalla Gandhi Nagar Rajasansi + Ward No 2 Muhalla Gandhi Nagar Rajasansi</t>
+          <t>Raja Sansi</t>
         </is>
       </c>
       <c r="E205" s="8" t="n">
@@ -10285,7 +10285,7 @@
       </c>
       <c r="K205" s="11" t="inlineStr">
         <is>
-          <t>Mukhwinder Singh Mahal (BJP)</t>
+          <t>Mukhwinder Singh (BJP)</t>
         </is>
       </c>
       <c r="L205" s="8" t="n">
@@ -10298,17 +10298,17 @@
       </c>
       <c r="B206" s="3" t="inlineStr">
         <is>
-          <t>ਵਾਰਡ ਨੰ.10 ਗਲੀ ਸੰਭ ਵਾਲੀ + ਵਾਰਡ ਨੰ.10 ਗਲੀ ਘਾਹ ਮੰਡੀ + ਵਾਰਡ ਨੰ.10 ਗਲੀ ਜੈਲਦਾਰਾ ਵਾਲੀ</t>
+          <t>ਰਾਜਾ ਸਾਂਸੀ</t>
         </is>
       </c>
       <c r="C206" s="3" t="inlineStr">
         <is>
-          <t>ਵਾਰਡ ਨੰ.10 ਗਲੀ ਸੰਭ ਵਾਲੀ + ਵਾਰਡ ਨੰ.10 ਗਲੀ ਘਾਹ ਮੰਡੀ + ਵਾਰਡ ਨੰ.10 ਗਲੀ ਜੈਲਦਾਰਾ ਵਾਲੀ</t>
+          <t>ਰਾਜਾ ਸਾਂਸੀ</t>
         </is>
       </c>
       <c r="D206" s="3" t="inlineStr">
         <is>
-          <t>Ward No. 10 Gali Sambh Wali + Ward No. 10 Gali Ghah Mandi + Ward No. 10 Gali Zaildara Wali</t>
+          <t>Raja Sansi</t>
         </is>
       </c>
       <c r="E206" s="4" t="n">
@@ -10345,17 +10345,17 @@
       </c>
       <c r="B207" s="7" t="inlineStr">
         <is>
-          <t>ਰਾਜਾਸਾਂਸੀ ਵਾਰਡ ਨੰ. 3 ਗਲੀ ਡਾਕਟਰ ਅਮਰ ਸਿੰਘ ਵਾਲੀ + ਵਾਰਡ ਨੰ.3 ਅਦਲੀ ਵਾਲਾ ਰੋਡ ਖੱਬਾ ਪਾਸਾ ਰਾਜਾਸਾਂਸੀ + ਵਾਰਡ ਨੰ.3 ਗਲੀ ਪਰੋਹਿਤਾਂ ਵਾਲੀ + ਵਾਰਡ ਨੰ.3 ਵਾਲਾ ਖੂਹ ਲੇਲੀਆ ਵਾਲਾ, ਨਵੀ ਕਲੋਨੀ</t>
+          <t>ਰਾਜਾ ਸਾਂਸੀ</t>
         </is>
       </c>
       <c r="C207" s="7" t="inlineStr">
         <is>
-          <t>ਰਾਜਾਸਾਂਸੀ ਵਾਰਡ ਨੰ. 3 ਗਲੀ ਡਾਕਟਰ ਅਮਰ ਸਿੰਘ ਵਾਲੀ + ਵਾਰਡ ਨੰ.3 ਅਦਲੀ ਵਾਲਾ ਰੋਡ ਖੱਬਾ ਪਾਸਾ ਰਾਜਾਸਾਂਸੀ + ਵਾਰਡ ਨੰ.3 ਗਲੀ ਪਰੋਹਿਤਾਂ ਵਾਲੀ + ਵਾਰਡ ਨੰ.3 ਵਾਲਾ ਖੂਹ ਲੇਲੀਆ ਵਾਲਾ, ਨਵੀ ਕਲੋਨੀ</t>
+          <t>ਰਾਜਾ ਸਾਂਸੀ</t>
         </is>
       </c>
       <c r="D207" s="7" t="inlineStr">
         <is>
-          <t>Rajasansi Ward No. 3 Gali Doctor Amar Singh Wali + Ward No. 3 Adli Wala Road Khabba Pasa Rajasansi + Ward No. 3 Gali Purohita Wali + Ward No. 3 Wala Khooh Lelia Wala, Navi Colony</t>
+          <t>Raja Sansi</t>
         </is>
       </c>
       <c r="E207" s="8" t="n">
@@ -10392,17 +10392,17 @@
       </c>
       <c r="B208" s="3" t="inlineStr">
         <is>
-          <t>ਵਾਰਡ ਨੰ.6 ਮੁਹੱਲਾ ਮੰਦਰ ਦੇਵੀ ਦੁਆਰ + ਵਾਰਡ ਨੰ.6 ਮੁਹੱਲਾ ਗਾਂਧੀ ਨਗਰ + ਵਾਰਡ ਨੰ.6 ਕਲੋਨੀ ਬਾਬਾ ਜਵੰਦ ਸਿੰਘ ਖੂਹ ਚੂਹੜ ਸਿੰਘ ਵਾਲਾ</t>
+          <t>ਰਾਜਾ ਸਾਂਸੀ</t>
         </is>
       </c>
       <c r="C208" s="3" t="inlineStr">
         <is>
-          <t>ਵਾਰਡ ਨੰ.6 ਮੁਹੱਲਾ ਮੰਦਰ ਦੇਵੀ ਦੁਆਰ + ਵਾਰਡ ਨੰ.6 ਮੁਹੱਲਾ ਗਾਂਧੀ ਨਗਰ + ਵਾਰਡ ਨੰ.6 ਕਲੋਨੀ ਬਾਬਾ ਜਵੰਦ ਸਿੰਘ ਖੂਹ ਚੂਹੜ ਸਿੰਘ ਵਾਲਾ</t>
+          <t>ਰਾਜਾ ਸਾਂਸੀ</t>
         </is>
       </c>
       <c r="D208" s="3" t="inlineStr">
         <is>
-          <t>Ward No. 6 Muhalla Mandir Devi Dwar + Ward No. 6 Muhalla Gandhi Nagar + Ward No. 6 Colony Baba Jawand Singh Khooh Chuhar Singh Wala</t>
+          <t>Raja Sansi</t>
         </is>
       </c>
       <c r="E208" s="4" t="n">
@@ -10439,17 +10439,17 @@
       </c>
       <c r="B209" s="7" t="inlineStr">
         <is>
-          <t>ਵਾਰਡ ਨੰ:7 ਰਾਜਾਸਾਂਸੀ ਮੁਹੱਲਾ ਸ੍ਰੀ ਪ੍ਰੀਤਮ ਸਿੰਘ ਗਲੀ ਬਜਾਜਾਂ ਵਾਲੀ ਮੇਨ ਬਜਾਰ + ਵਾਰਡ ਨੰ:7 ਮੇਨ ਬਜਾਰ ਸਾਹਮਣੇ ਗੁਰਦੁਆਰਾ ਸਿੰਘ ਸਭਾ + ਵਾਰਡ ਨੰ:7 ਮੁਹੱਲਾ ਸ੍ਰੀ ਪ੍ਰੀਤਮ ਸਿੰਘ ਗਲੀ ਲੇਹੇ ਵਾਲੀ + ਵਾਰਡ ਨੰ:7 ਮੁਹੱਲਾ ਪ੍ਰੀਤਮ ਸਿੰਘ ਗਲੀ ਲੇਹੇ ਵਾਲੀ + ਵਾਰਡ ਨੰ:7 ਗਲੀ ਸਹਿਜਾਦਾ + ਵਾਰਡ ਨੰ:7 ਗਲੀ ਲੇਹੇ ਵਾਲੀ + ਓਵਰਸੀਜ਼ ਇਲੈਕਟਰ</t>
+          <t>ਰਾਜਾ ਸਾਂਸੀ</t>
         </is>
       </c>
       <c r="C209" s="7" t="inlineStr">
         <is>
-          <t>ਵਾਰਡ ਨੰ:7 ਰਾਜਾਸਾਂਸੀ ਮੁਹੱਲਾ ਸ੍ਰੀ ਪ੍ਰੀਤਮ ਸਿੰਘ ਗਲੀ ਬਜਾਜਾਂ ਵਾਲੀ ਮੇਨ ਬਜਾਰ + ਵਾਰਡ ਨੰ:7 ਮੇਨ ਬਜਾਰ ਸਾਹਮਣੇ ਗੁਰਦੁਆਰਾ ਸਿੰਘ ਸਭਾ + ਵਾਰਡ ਨੰ:7 ਮੁਹੱਲਾ ਸ੍ਰੀ ਪ੍ਰੀਤਮ ਸਿੰਘ ਗਲੀ ਲੇਹੇ ਵਾਲੀ + ਵਾਰਡ ਨੰ:7 ਮੁਹੱਲਾ ਪ੍ਰੀਤਮ ਸਿੰਘ ਗਲੀ ਲੇਹੇ ਵਾਲੀ + ਵਾਰਡ ਨੰ:7 ਗਲੀ ਸਹਿਜਾਦਾ + ਵਾਰਡ ਨੰ:7 ਗਲੀ ਲੇਹੇ ਵਾਲੀ + ਓਵਰਸੀਜ਼ ਇਲੈਕਟਰ</t>
+          <t>ਰਾਜਾ ਸਾਂਸੀ</t>
         </is>
       </c>
       <c r="D209" s="7" t="inlineStr">
         <is>
-          <t>Ward No: 7 Rajasansi Muhalla Sri Pritam Singh Gali Bajaja Wali Main Bazar + Ward No: 7 Main Bazar Sahamne Gurdwara Singh Sabha + Ward No: 7 Muhalla Sri Pritam Singh Gali Lehe Wali + Ward No: 7 Muhalla Pritam Singh Gali Lehe Wali + Ward No: 7 Gali Sahzada + Ward No: 7 Gali Lehe Wali + Overseas Elector</t>
+          <t>Raja Sansi</t>
         </is>
       </c>
       <c r="E209" s="8" t="n">
@@ -10486,17 +10486,17 @@
       </c>
       <c r="B210" s="3" t="inlineStr">
         <is>
-          <t>ਵਾਰਡ ਨੰ. 11 ਗਲੀ ਘੁਮਿਆਰਾਂ ਵਾਲੀ + ਵਾਰਡ ਨੰ. 11 ਗਲੀ ਜੈਲਦਾਰਾਂ ਵਾਲੀ + ਵਾਰਡ ਨੰ. 11 ਗਲੀ ਗੁਰਦੁਆਰਾ ਕਲਗੀਧਰ + ਵਾਰਡ ਨੰ. 11 ਮੇਨ ਬਜਾਰ ਗੁਰਦੁਆਰਾ ਕਲਗੀਧਰ + ਵਾਰਡ ਨੰ.11 ਮੇਨ ਬਜਾਰ + ਵਾਰਡ ਨੰ.11 ਗਲੀ ਵਜੀਰਾ ਵਾਲੀ + ਵਾਰਡ ਨੰ.11 ਮੇਨ ਬਜਾਰ + ਵਾਰਡ ਨੰ.11 ਮੇਨ ਬਜਾਰ</t>
+          <t>ਰਾਜਾ ਸਾਂਸੀ</t>
         </is>
       </c>
       <c r="C210" s="3" t="inlineStr">
         <is>
-          <t>ਵਾਰਡ ਨੰ. 11 ਗਲੀ ਘੁਮਿਆਰਾਂ ਵਾਲੀ + ਵਾਰਡ ਨੰ. 11 ਗਲੀ ਜੈਲਦਾਰਾਂ ਵਾਲੀ + ਵਾਰਡ ਨੰ. 11 ਗਲੀ ਗੁਰਦੁਆਰਾ ਕਲਗੀਧਰ + ਵਾਰਡ ਨੰ. 11 ਮੇਨ ਬਜਾਰ ਗੁਰਦੁਆਰਾ ਕਲਗੀਧਰ + ਵਾਰਡ ਨੰ.11 ਮੇਨ ਬਜਾਰ + ਵਾਰਡ ਨੰ.11 ਗਲੀ ਵਜੀਰਾ ਵਾਲੀ + ਵਾਰਡ ਨੰ.11 ਮੇਨ ਬਜਾਰ + ਵਾਰਡ ਨੰ.11 ਮੇਨ ਬਜਾਰ</t>
+          <t>ਰਾਜਾ ਸਾਂਸੀ</t>
         </is>
       </c>
       <c r="D210" s="3" t="inlineStr">
         <is>
-          <t>Ward No. 11 Gali Ghumiara Wali + Ward No. 11 Gali Zaildara Wali + Ward No. 11 Gali Gurdwara Kalgidhar + Ward No. 11 Main Bazar Gurdwara Kalgidhar + Ward No. 11 Main Bazar + Ward No. 11 Gali Wajira Wali + Ward No. 11 Main Bazar + Ward No. 11 Main Bazar</t>
+          <t>Raja Sansi</t>
         </is>
       </c>
       <c r="E210" s="4" t="n">
@@ -10533,17 +10533,17 @@
       </c>
       <c r="B211" s="7" t="inlineStr">
         <is>
-          <t>ਵਾਰਡ ਨੰ 4 ਨਵੀ ਕਲੋਨੀ ਸਾਹਮਣੇ ਏਅਰਪੋਰਟ ਰਾਜਾਸਾਂਸੀ + ਵਾਰਡ ਨੰ 4 ਅਜਨਾਲਾ ਰੋਡ ਏਅਰਪੋਰਟ ਕਲੋਨੀ ਰਾਜਾਸਾਂਸੀ + ਵਾਰਡ ਨੰ 4 ਅਜਨਾਲਾ ਰੋਡ ਏਅਰਪੋਰਟ ਕਲੋਨੀ ਰਾਜਾਸਾਂਸੀ</t>
+          <t>ਲੱਧੇਹ</t>
         </is>
       </c>
       <c r="C211" s="7" t="inlineStr">
         <is>
-          <t>ਵਾਰਡ ਨੰ 4 ਨਵੀ ਕਲੋਨੀ ਸਾਹਮਣੇ ਏਅਰਪੋਰਟ ਰਾਜਾਸਾਂਸੀ + ਵਾਰਡ ਨੰ 4 ਅਜਨਾਲਾ ਰੋਡ ਏਅਰਪੋਰਟ ਕਲੋਨੀ ਰਾਜਾਸਾਂਸੀ + ਵਾਰਡ ਨੰ 4 ਅਜਨਾਲਾ ਰੋਡ ਏਅਰਪੋਰਟ ਕਲੋਨੀ ਰਾਜਾਸਾਂਸੀ</t>
+          <t>ਲੱਧੇਹ</t>
         </is>
       </c>
       <c r="D211" s="7" t="inlineStr">
         <is>
-          <t>Ward No 4 Navi Colony Sahamne Airport Rajasansi + Ward No 4 Ajnala Road Airport Colony Rajasansi + Ward No 4 Ajnala Road Airport Colony Rajasansi</t>
+          <t>Ladeh</t>
         </is>
       </c>
       <c r="E211" s="8" t="n">
@@ -10580,17 +10580,17 @@
       </c>
       <c r="B212" s="3" t="inlineStr">
         <is>
-          <t>ਵਾਰਡ ਨੰ.5 ਕਲੋਨੀ ਬਾਬਾ ਜਵੰਦ ਸਿੰਘ ਅਜਨਾਲਾ ਰੋਡ + ਵਾਰਡ ਨੰ.5 ਨਵਾਂ ਅੱਡਾ ਰਾਜਾਸਾਂਸੀ + ਵਾਰਡ ਨੰ.5 ਅਜਨਾਲਾ ਰੋਡ ਨੇੜੇ ਅਜੀਤ ਪੈਲਸ + ਵਾਰਡ ਨੰ.5 ਅਜਨਾਲਾ ਰੋਡ ਖੱਬਾ ਪਾਸਾ ਖੂਹ ਚੂਹੜ ਸਿੰਘ ਵਾਲਾ + ਵਾਰਡ ਨੰ.5 ਅਜਨਾਲਾ ਰੋਡ ਖੱਬਾ ਪਾਸਾ ਖੂਹ ਚੂਹੜ ਸਿੰਘ ਵਾਲਾ + ਵਾਰਡ ਨੰ.5 ਅਜਨਾਲਾ ਰੋਡ ਖੱਬਾ ਪਾਸਾ ਖੂਹ ਚੂਹੜ ਸਿੰਘ ਵਾਲਾ + ਵਾਰਡ ਨੰ.5 ਅਜਨਾਲਾ ਰੋਡ ਸਿਵਲ ਕਲੋਨੀ ਏਅਰ ਪੋਰਟ</t>
+          <t>ਰਾਣੇਵਾਲੀ</t>
         </is>
       </c>
       <c r="C212" s="3" t="inlineStr">
         <is>
-          <t>ਵਾਰਡ ਨੰ.5 ਕਲੋਨੀ ਬਾਬਾ ਜਵੰਦ ਸਿੰਘ ਅਜਨਾਲਾ ਰੋਡ + ਵਾਰਡ ਨੰ.5 ਨਵਾਂ ਅੱਡਾ ਰਾਜਾਸਾਂਸੀ + ਵਾਰਡ ਨੰ.5 ਅਜਨਾਲਾ ਰੋਡ ਨੇੜੇ ਅਜੀਤ ਪੈਲਸ + ਵਾਰਡ ਨੰ.5 ਅਜਨਾਲਾ ਰੋਡ ਖੱਬਾ ਪਾਸਾ ਖੂਹ ਚੂਹੜ ਸਿੰਘ ਵਾਲਾ + ਵਾਰਡ ਨੰ.5 ਅਜਨਾਲਾ ਰੋਡ ਖੱਬਾ ਪਾਸਾ ਖੂਹ ਚੂਹੜ ਸਿੰਘ ਵਾਲਾ + ਵਾਰਡ ਨੰ.5 ਅਜਨਾਲਾ ਰੋਡ ਖੱਬਾ ਪਾਸਾ ਖੂਹ ਚੂਹੜ ਸਿੰਘ ਵਾਲਾ + ਵਾਰਡ ਨੰ.5 ਅਜਨਾਲਾ ਰੋਡ ਸਿਵਲ ਕਲੋਨੀ ਏਅਰ ਪੋਰਟ</t>
+          <t>ਰਾਣੇਵਾਲੀ</t>
         </is>
       </c>
       <c r="D212" s="3" t="inlineStr">
         <is>
-          <t>Ward No. 5 Colony Baba Jawand Singh Ajnala Road + Ward No. 5 Nawan Adda Rajasansi + Ward No. 5 Ajnala Road Nere Ajit Palace + Ward No. 5 Ajnala Road Khabba Pasa Khooh Chuhar Singh Wala + Ward No. 5 Ajnala Road Khabba Pasa Khooh Chuhar Singh Wala + Ward No. 5 Ajnala Road Khabba Pasa Khooh Chuhar Singh Wala + Ward No. 5 Ajnala Road Civil Colony Airport</t>
+          <t>Ranewali</t>
         </is>
       </c>
       <c r="E212" s="4" t="n">
@@ -10627,17 +10627,17 @@
       </c>
       <c r="B213" s="7" t="inlineStr">
         <is>
-          <t>ਵਾਰਡ ਨੰ 8 ਮੁਹੱਲਾ ਠਾਕਰ ਸਿੰਘ ਗਲੀ ਘੁਮਿਆਰਾਂ ਵਾਲੀ + ਵਾਰਡ ਨੰ 8 ਮੁਹੱਲਾ ਠਾਕਰ ਸਿੰਘ ਗਲੀ ਘੁਮਿਆਰਾਂ ਵਾਲੀ + ਵਾਰਡ ਨੰ 8 ਮੁਹੱਲਾ ਠਾਕਰ ਸਿੰਘ ਗਲੀ ਘੁਮਿਆਰਾਂ ਵਾਲੀ</t>
+          <t>ਮੁਗਲਾਨੀ ਕੋਟ</t>
         </is>
       </c>
       <c r="C213" s="7" t="inlineStr">
         <is>
-          <t>ਵਾਰਡ ਨੰ 8 ਮੁਹੱਲਾ ਠਾਕਰ ਸਿੰਘ ਗਲੀ ਘੁਮਿਆਰਾਂ ਵਾਲੀ + ਵਾਰਡ ਨੰ 8 ਮੁਹੱਲਾ ਠਾਕਰ ਸਿੰਘ ਗਲੀ ਘੁਮਿਆਰਾਂ ਵਾਲੀ + ਵਾਰਡ ਨੰ 8 ਮੁਹੱਲਾ ਠਾਕਰ ਸਿੰਘ ਗਲੀ ਘੁਮਿਆਰਾਂ ਵਾਲੀ</t>
+          <t>ਮੁਗਲਾਨੀ ਕੋਟ</t>
         </is>
       </c>
       <c r="D213" s="7" t="inlineStr">
         <is>
-          <t>Ward No 8 Muhalla Thakar Singh Gali Ghumiara Wali + Ward No 8 Muhalla Thakar Singh Gali Ghumiara Wali + Ward No 8 Muhalla Thakar Singh Gali Ghumiara Wali</t>
+          <t>Muglani Kot</t>
         </is>
       </c>
       <c r="E213" s="8" t="n">
@@ -10674,17 +10674,17 @@
       </c>
       <c r="B214" s="3" t="inlineStr">
         <is>
-          <t>ਵਾਰਡ ਨੰ.9 ਮੇਨ ਬਜਾਰ ਗਲੀ ਲੋਹਾਰਾਂ ਵਾਲੀ + ਵਾਰਡ ਨੰ.9 ਗਲੀ ਮਿਸਤਰੀ ਮੇਹਰ ਸਿੰਘ ਵਾਲੀ + ਵਾਰਡ ਨੰ.9 ਗਲੀ ਮਿਸਤਰੀ ਮੇਹਰ ਸਿੰਘ ਵਾਲੀ + ਵਾਰਡ ਨੰ. 9 ਸਾਹਮਣੇ ਬਗੀਚੀ</t>
+          <t>ਜਗਦੇਵ ਕਲਾਂ</t>
         </is>
       </c>
       <c r="C214" s="3" t="inlineStr">
         <is>
-          <t>ਵਾਰਡ ਨੰ.9 ਮੇਨ ਬਜਾਰ ਗਲੀ ਲੋਹਾਰਾਂ ਵਾਲੀ + ਵਾਰਡ ਨੰ.9 ਗਲੀ ਮਿਸਤਰੀ ਮੇਹਰ ਸਿੰਘ ਵਾਲੀ + ਵਾਰਡ ਨੰ.9 ਗਲੀ ਮਿਸਤਰੀ ਮੇਹਰ ਸਿੰਘ ਵਾਲੀ + ਵਾਰਡ ਨੰ. 9 ਸਾਹਮਣੇ ਬਗੀਚੀ</t>
+          <t>ਜਗਦੇਵ ਕਲਾਂ</t>
         </is>
       </c>
       <c r="D214" s="3" t="inlineStr">
         <is>
-          <t>Ward No. 9 Main Bazar Gali Lohara Wali + Ward No. 9 Gali Mistri Mehar Singh Wali + Ward No. 9 Gali Mistri Mehar Singh Wali + Ward No. 9 Sahamne Bagichi</t>
+          <t>Jagdev Kalan</t>
         </is>
       </c>
       <c r="E214" s="4" t="n">
@@ -10721,17 +10721,17 @@
       </c>
       <c r="B215" s="7" t="inlineStr">
         <is>
-          <t>ਰਾਜਾਸਾਂਸੀ ਵਾਰਡ ਨੰ. 9 ਘਰ ਮੰਡੀ ਰੋਡ + ਵਾਰਡ ਨੰ. 9 ਗਲੀ ਛੀਬਿਆਂ ਵਾਲੀ + ਵਾਰਡ ਨੰ. 9 ਘਰ ਮੰਡੀ ਰਾਜਾਸਾਂਸੀ + ਵਾਰਡ ਨੰ. 9 ਸਾਹਮਣੇ ਬਗੀਚੀ + ਵਾਰਡ ਨੰ. 9 ਗਲੀ ਧੋਬੀਆਂ ਵਾਲੀ</t>
+          <t>ਜਗਦੇਵ ਕਲਾਂ</t>
         </is>
       </c>
       <c r="C215" s="7" t="inlineStr">
         <is>
-          <t>ਰਾਜਾਸਾਂਸੀ ਵਾਰਡ ਨੰ. 9 ਘਰ ਮੰਡੀ ਰੋਡ + ਵਾਰਡ ਨੰ. 9 ਗਲੀ ਛੀਬਿਆਂ ਵਾਲੀ + ਵਾਰਡ ਨੰ. 9 ਘਰ ਮੰਡੀ ਰਾਜਾਸਾਂਸੀ + ਵਾਰਡ ਨੰ. 9 ਸਾਹਮਣੇ ਬਗੀਚੀ + ਵਾਰਡ ਨੰ. 9 ਗਲੀ ਧੋਬੀਆਂ ਵਾਲੀ</t>
+          <t>ਜਗਦੇਵ ਕਲਾਂ</t>
         </is>
       </c>
       <c r="D215" s="7" t="inlineStr">
         <is>
-          <t>Rajasansi Ward No. 9 Ghar Mandi Road + Ward No. 9 Gali Chhibia Wali + Ward No. 9 Ghar Mandi Rajasansi + Ward No. 9 Sahamne Bagichi + Ward No. 9 Gali Dhobia Wali</t>
+          <t>Jagdev Kalan</t>
         </is>
       </c>
       <c r="E215" s="8" t="n">
@@ -10768,17 +10768,17 @@
       </c>
       <c r="B216" s="3" t="inlineStr">
         <is>
-          <t>ਵਾਰਡ ਨੰ.13 ਗਲੀ ਲੋਹਾਰਾਂ ਵਾਲੀ + ਵਾਰਡ ਨੰ.13 ਮੁਹੱਲਾ ਮਸੀਤ ਵਾਲਾ + ਵਾਰਡ ਨੰ.13 ਮੇਨ ਬਜਾਰ ਸਾਹਮਣੇ ਮੁਹੱਲਾ ਠਾਕਰ ਸਿੰਘ ਵਾਲਾ + ਵਾਰਡ ਨੰ.13 ਮੇਨ ਬਜਾਰ ਸਾਹਮਣੇ ਮੁਹੱਲਾ ਠਾਕਰ ਸਿੰਘ ਵਾਲਾ + ਓਵਰਸੀਜ਼ ਇਲੈਕਟਰ</t>
+          <t>ਜਗਦੇਵ ਕਲਾਂ</t>
         </is>
       </c>
       <c r="C216" s="3" t="inlineStr">
         <is>
-          <t>ਵਾਰਡ ਨੰ.13 ਗਲੀ ਲੋਹਾਰਾਂ ਵਾਲੀ + ਵਾਰਡ ਨੰ.13 ਮੁਹੱਲਾ ਮਸੀਤ ਵਾਲਾ + ਵਾਰਡ ਨੰ.13 ਮੇਨ ਬਜਾਰ ਸਾਹਮਣੇ ਮੁਹੱਲਾ ਠਾਕਰ ਸਿੰਘ ਵਾਲਾ + ਵਾਰਡ ਨੰ.13 ਮੇਨ ਬਜਾਰ ਸਾਹਮਣੇ ਮੁਹੱਲਾ ਠਾਕਰ ਸਿੰਘ ਵਾਲਾ + ਓਵਰਸੀਜ਼ ਇਲੈਕਟਰ</t>
+          <t>ਜਗਦੇਵ ਕਲਾਂ</t>
         </is>
       </c>
       <c r="D216" s="3" t="inlineStr">
         <is>
-          <t>Ward No. 13 Gali Lohara Wali + Ward No. 13 Muhalla Masit Wala + Ward No. 13 Main Bazar Sahamne Muhalla Thakar Singh Wala + Ward No. 13 Main Bazar Sahamne Muhalla Thakar Singh Wala + Overseas Elector</t>
+          <t>Jagdev Kalan</t>
         </is>
       </c>
       <c r="E216" s="4" t="n">
@@ -10815,17 +10815,17 @@
       </c>
       <c r="B217" s="7" t="inlineStr">
         <is>
-          <t>ਲਦੇਹ</t>
+          <t>ਜਗਦੇਵ ਕਲਾਂ</t>
         </is>
       </c>
       <c r="C217" s="7" t="inlineStr">
         <is>
-          <t>ਲਦੇਹ</t>
+          <t>ਜਗਦੇਵ ਕਲਾਂ</t>
         </is>
       </c>
       <c r="D217" s="7" t="inlineStr">
         <is>
-          <t>Ladeh</t>
+          <t>Jagdev Kalan</t>
         </is>
       </c>
       <c r="E217" s="8" t="n">
@@ -10862,17 +10862,17 @@
       </c>
       <c r="B218" s="3" t="inlineStr">
         <is>
-          <t>ਰਾਣੇਵਾਲੀ</t>
+          <t>ਮੱਲੂ ਨੰਗਲ</t>
         </is>
       </c>
       <c r="C218" s="3" t="inlineStr">
         <is>
-          <t>ਰਾਣੇਵਾਲੀ</t>
+          <t>ਮੱਲੂ ਨੰਗਲ</t>
         </is>
       </c>
       <c r="D218" s="3" t="inlineStr">
         <is>
-          <t>Ranewali</t>
+          <t>Mallu Nangal</t>
         </is>
       </c>
       <c r="E218" s="4" t="n">
@@ -10909,17 +10909,17 @@
       </c>
       <c r="B219" s="7" t="inlineStr">
         <is>
-          <t>ਮੁਗਲਾਣੀ ਕੋਟ</t>
+          <t>ਮੱਲੂ ਨੰਗਲ</t>
         </is>
       </c>
       <c r="C219" s="7" t="inlineStr">
         <is>
-          <t>ਮੁਗਲਾਣੀ ਕੋਟ</t>
+          <t>ਮੱਲੂ ਨੰਗਲ</t>
         </is>
       </c>
       <c r="D219" s="7" t="inlineStr">
         <is>
-          <t>Muglani Kot</t>
+          <t>Mallu Nangal</t>
         </is>
       </c>
       <c r="E219" s="8" t="n">
@@ -10956,17 +10956,17 @@
       </c>
       <c r="B220" s="3" t="inlineStr">
         <is>
-          <t>ਜਗਦੇਵ ਕਲਾਂ</t>
+          <t>ਅਦਲੀ ਵਾਲਾ</t>
         </is>
       </c>
       <c r="C220" s="3" t="inlineStr">
         <is>
-          <t>ਜਗਦੇਵ ਕਲਾਂ</t>
+          <t>ਅਦਲੀ ਵਾਲਾ</t>
         </is>
       </c>
       <c r="D220" s="3" t="inlineStr">
         <is>
-          <t>Jagdev Kalan</t>
+          <t>Adli Wala</t>
         </is>
       </c>
       <c r="E220" s="4" t="n">
@@ -11003,17 +11003,17 @@
       </c>
       <c r="B221" s="7" t="inlineStr">
         <is>
-          <t>ਜਗਦੇਵ ਕਲਾਂ</t>
+          <t>ਅਦਲੀ ਵਾਲਾ</t>
         </is>
       </c>
       <c r="C221" s="7" t="inlineStr">
         <is>
-          <t>ਜਗਦੇਵ ਕਲਾਂ</t>
+          <t>ਅਦਲੀ ਵਾਲਾ</t>
         </is>
       </c>
       <c r="D221" s="7" t="inlineStr">
         <is>
-          <t>Jagdev Kalan</t>
+          <t>Adli Wala</t>
         </is>
       </c>
       <c r="E221" s="8" t="n">
@@ -11050,17 +11050,17 @@
       </c>
       <c r="B222" s="3" t="inlineStr">
         <is>
-          <t>ਜਗਦੇਵ ਕਲਾਂ</t>
+          <t>ਅਦਲੀ ਵਾਲਾ</t>
         </is>
       </c>
       <c r="C222" s="3" t="inlineStr">
         <is>
-          <t>ਜਗਦੇਵ ਕਲਾਂ</t>
+          <t>ਅਦਲੀ ਵਾਲਾ</t>
         </is>
       </c>
       <c r="D222" s="3" t="inlineStr">
         <is>
-          <t>Jagdev Kalan</t>
+          <t>Adli Wala</t>
         </is>
       </c>
       <c r="E222" s="4" t="n">
@@ -11097,17 +11097,17 @@
       </c>
       <c r="B223" s="7" t="inlineStr">
         <is>
-          <t>ਜਗਦੇਵ ਕਲਾਂ</t>
+          <t>ਬੂਆ ਨੰਗਲੀ</t>
         </is>
       </c>
       <c r="C223" s="7" t="inlineStr">
         <is>
-          <t>ਜਗਦੇਵ ਕਲਾਂ</t>
+          <t>ਬੂਆ ਨੰਗਲੀ</t>
         </is>
       </c>
       <c r="D223" s="7" t="inlineStr">
         <is>
-          <t>Jagdev Kalan</t>
+          <t>Bua Nangali</t>
         </is>
       </c>
       <c r="E223" s="8" t="n">
@@ -11201,7 +11201,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:K223"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
@@ -11259,7 +11259,7 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Mukhwinder Singh Mahal (BJP)</t>
+          <t>Mukhwinder Singh (BJP)</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -11282,12 +11282,12 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>ਮੰਡਿਆਵਾਲਾ</t>
+          <t>ਮੰਜ</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Mandiawala</t>
+          <t>Manj</t>
         </is>
       </c>
       <c r="E2" s="4" t="n">
@@ -11323,12 +11323,12 @@
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>ਮੇਹਲੇਕੇ</t>
+          <t>ਲੋਧੀ ਗੁੱਜਰ</t>
         </is>
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>Mehleke</t>
+          <t>Lodhi Gujjar</t>
         </is>
       </c>
       <c r="E3" s="8" t="n">
@@ -11364,12 +11364,12 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>ਭੁੱਲਰ</t>
+          <t>ਭੰਗਵਾਂ</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Bhullar</t>
+          <t>Bhangwan</t>
         </is>
       </c>
       <c r="E4" s="4" t="n">
@@ -11405,12 +11405,12 @@
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>ਭਿੱਟੇਵੱਡ</t>
+          <t>ਧਾਰੀਵਾਲ</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Bhittewad</t>
+          <t>Dhariwal</t>
         </is>
       </c>
       <c r="E5" s="8" t="n">
@@ -11446,7 +11446,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>ਭਿੰਡੀ ਅੌਲਖ ਕਲਾਂ</t>
+          <t>ਭਿੰਡੀ ਔਲਖ ਕਲਾਂ</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -11487,12 +11487,12 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>ਰਾਏਪੁਰ ਖੁਰਦ</t>
+          <t>ਜੌਂਸ</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Raipur Khurd</t>
+          <t>Jauns</t>
         </is>
       </c>
       <c r="E7" s="8" t="n">
@@ -11528,12 +11528,12 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>ਚੇਲੇਕੀ + ਕੋਟਲੀ ਅੱਲਖ</t>
+          <t>ਪੱਧਰੀ</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>Cheleki + Kotli Allakh</t>
+          <t>Padhari</t>
         </is>
       </c>
       <c r="E8" s="4" t="n">
@@ -11569,12 +11569,12 @@
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>ਕੋਟ ਸਿੰਘ</t>
+          <t>ਜੱਸੜਵਾਲ</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>Kot Singh</t>
+          <t>Jastarwal</t>
         </is>
       </c>
       <c r="E9" s="8" t="n">
@@ -11610,12 +11610,12 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>ਸਾਰੰਗੜਾ</t>
+          <t>ਹੇਤਮਪੁਰਾ</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>Sarangra</t>
+          <t>Hetampura</t>
         </is>
       </c>
       <c r="E10" s="4" t="n">
@@ -11651,12 +11651,12 @@
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>ਕਲੇਰ</t>
+          <t>ਕੋਹਾਲੀ</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Kaler</t>
+          <t>Kohali</t>
         </is>
       </c>
       <c r="E11" s="8" t="n">
@@ -11692,12 +11692,12 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>ਕੜਿਆਲ</t>
+          <t>ਛੀਨਾ ਕਰਮ ਸਿੰਘ</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>Karial</t>
+          <t>Chhina Karam Singh</t>
         </is>
       </c>
       <c r="E12" s="4" t="n">
@@ -11733,12 +11733,12 @@
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>ਠੱਠੀ</t>
+          <t>ਬਾਚੀਵਿੰਡ</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>Thathi</t>
+          <t>Bachiwind</t>
         </is>
       </c>
       <c r="E13" s="8" t="n">
@@ -11815,12 +11815,12 @@
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>ਬੋਪਾਰਾਏ ਖੁਰਦ</t>
+          <t>ਖਿਆਲਾ ਕਲਾਂ</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>Boparai Khurd</t>
+          <t>Khiala Kalan</t>
         </is>
       </c>
       <c r="E15" s="8" t="n">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>ਮਹਿਮਦਪੁਰਾ + ਕਮੀਰਪੁਰਾ</t>
+          <t>ਮਾਨਾਵਾਲਾ</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Mahmadpura + Kamirpura</t>
+          <t>Manawala</t>
         </is>
       </c>
       <c r="E16" s="4" t="n">
@@ -11897,12 +11897,12 @@
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>ਕੋਹਾਲੀ</t>
+          <t>ਭਿੱਟੇਵੱਡ</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>Kohali</t>
+          <t>Bhittewad</t>
         </is>
       </c>
       <c r="E17" s="8" t="n">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>ਹਰਸ਼ਾ ਛੀਨਾ (ਅਬਾਦੀ ਵਿਚਲਾ ਕਿਲਾ)</t>
+          <t>ਝੰਜੋਟੀ</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>Harsha Chhina (Abadi Vichla Kila)</t>
+          <t>Jhanjoti</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
@@ -11979,12 +11979,12 @@
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>ਜਗਦੇਵ ਕਲਾਂ</t>
+          <t>ਅਦਲੀ ਵਾਲਾ</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>Jagdev Kalan</t>
+          <t>Adli Wala</t>
         </is>
       </c>
       <c r="E19" s="8" t="n">
@@ -12020,12 +12020,12 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>ਹਰਸ਼ਾ ਛੀਨਾ (ਅਬਾਦੀ ਸਬਾਜਪੁਰ)</t>
+          <t>ਚੈਨਪੁਰ</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>Harsha Chhina (Abadi Sabajpur)</t>
+          <t>Chainpur</t>
         </is>
       </c>
       <c r="E20" s="4" t="n">
@@ -12061,12 +12061,12 @@
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>ਛੰਨ ਕਲਾਂ</t>
+          <t>ਮੰਡੀਆਵਾਲਾ</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>Chhann Kalan</t>
+          <t>Mandiawala</t>
         </is>
       </c>
       <c r="E21" s="8" t="n">
@@ -12102,12 +12102,12 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>ਚੈਨਪੁਰ</t>
+          <t>ਰਡਾਲਾ</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Chainpur</t>
+          <t>Radala</t>
         </is>
       </c>
       <c r="E22" s="4" t="n">
@@ -12143,12 +12143,12 @@
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>ਛਿੱਡਣ</t>
+          <t>ਕੋਲੋਵਾਲ</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>Chhiddan</t>
+          <t>Kolowal</t>
         </is>
       </c>
       <c r="E23" s="8" t="n">
@@ -12184,12 +12184,12 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>ਭੁੱਲਰ</t>
+          <t>ਓਦੜ</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Bhullar</t>
+          <t>Odar</t>
         </is>
       </c>
       <c r="E24" s="4" t="n">
@@ -12225,7 +12225,7 @@
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>ਭਿੰਡੀ ਅੌਲਖ ਕਲਾਂ</t>
+          <t>ਭਿੰਡੀ ਔਲਖ ਕਲਾਂ</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
@@ -12266,12 +12266,12 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>ਕੋਹਾਲਾ (ਸੱਜਾ ਪਾਸਾ)</t>
+          <t>ਪੱਧਰੀ</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Kohala (Sajja Pasa)</t>
+          <t>Padhari</t>
         </is>
       </c>
       <c r="E26" s="4" t="n">
@@ -12307,12 +12307,12 @@
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>ਲੇਲੀਆਂ</t>
+          <t>ਲੋਪੋਕੇ</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>Lelian</t>
+          <t>Lopoke</t>
         </is>
       </c>
       <c r="E27" s="8" t="n">
@@ -12348,12 +12348,12 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>ਰਾਜਾਸਾਂਸੀ ਵਾਰਡ ਨੰ. 9 ਘਰ ਮੰਡੀ ਰੋਡ + ਵਾਰਡ ਨੰ. 9 ਗਲੀ ਛੀਬਿਆਂ ਵਾਲੀ + ਵਾਰਡ ਨੰ. 9 ਘਰ ਮੰਡੀ ਰਾਜਾਸਾਂਸੀ + ਵਾਰਡ ਨੰ. 9 ਸਾਹਮਣੇ ਬਗੀਚੀ + ਵਾਰਡ ਨੰ. 9 ਗਲੀ ਧੋਬੀਆਂ ਵਾਲੀ</t>
+          <t>ਜਗਦੇਵ ਕਲਾਂ</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Rajasansi Ward No. 9 Ghar Mandi Road + Ward No. 9 Gali Chhibia Wali + Ward No. 9 Ghar Mandi Rajasansi + Ward No. 9 Sahamne Bagichi + Ward No. 9 Gali Dhobia Wali</t>
+          <t>Jagdev Kalan</t>
         </is>
       </c>
       <c r="E28" s="4" t="n">
@@ -12389,12 +12389,12 @@
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>ਮਾਨਾਵਾਲਾ</t>
+          <t>ਚੋਗਾਵਾਂ</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>Manawala</t>
+          <t>Chogawan</t>
         </is>
       </c>
       <c r="E29" s="8" t="n">
@@ -12430,12 +12430,12 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>ਚੱਕ ਮਿਸਰੀ ਖਾਂ</t>
+          <t>ਚੋਗਾਵਾਂ</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Chak Misri Khan</t>
+          <t>Chogawan</t>
         </is>
       </c>
       <c r="E30" s="4" t="n">
@@ -12471,12 +12471,12 @@
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>ਕੜਿਆਲ</t>
+          <t>ਨੇਪਾਲ</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>Karial</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="E31" s="8" t="n">
@@ -12512,12 +12512,12 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>ਕੋਲੇਵਾਲ</t>
+          <t>ਖਿਆਲਾ ਕਲਾਂ</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Kolewal</t>
+          <t>Khiala Kalan</t>
         </is>
       </c>
       <c r="E32" s="4" t="n">
@@ -12553,12 +12553,12 @@
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>ਰਾਣੇਵਾਲੀ</t>
+          <t>ਮੱਲੂ ਨੰਗਲ</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>Ranewali</t>
+          <t>Mallu Nangal</t>
         </is>
       </c>
       <c r="E33" s="8" t="n">
@@ -12594,12 +12594,12 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>ਕਲੇਰ</t>
+          <t>ਕੋਹਾਲੀ</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Kaler</t>
+          <t>Kohali</t>
         </is>
       </c>
       <c r="E34" s="4" t="n">
@@ -12635,12 +12635,12 @@
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>ਸ਼ਹੂਰਾ</t>
+          <t>ਕੋਹਾਲਾ</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>Shahura</t>
+          <t>Kohala</t>
         </is>
       </c>
       <c r="E35" s="8" t="n">
@@ -12676,12 +12676,12 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>ਬੋਹਲੀਆਂ</t>
+          <t>ਮੋਹਰ</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>Bohlian</t>
+          <t>Mohar</t>
         </is>
       </c>
       <c r="E36" s="4" t="n">
@@ -12717,12 +12717,12 @@
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>ਕਿਰਲਗੜ</t>
+          <t>ਵੈਣੇਕੇ</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>Kirlgarh</t>
+          <t>Vaineke</t>
         </is>
       </c>
       <c r="E37" s="8" t="n">
@@ -12758,12 +12758,12 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>ਉਮਰਪੁਰਾ</t>
+          <t>ਓਠੀਆਂ</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>Umarpura</t>
+          <t>Othian</t>
         </is>
       </c>
       <c r="E38" s="4" t="n">
@@ -12799,12 +12799,12 @@
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>ਅਵਾਨ ਲੱਖਾ ਸਿੰਘ</t>
+          <t>ਸੌੜੀਆਂ</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>Awan Lakha Singh</t>
+          <t>Saurhiyan</t>
         </is>
       </c>
       <c r="E39" s="8" t="n">
@@ -12840,12 +12840,12 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>ਬੋਪਾ ਰਾਏ ਬਾਜ ਸਿੰਘ</t>
+          <t>ਕੋਹਾਲੀ</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>Bopa Rai Baj Singh</t>
+          <t>Kohali</t>
         </is>
       </c>
       <c r="E40" s="4" t="n">
@@ -12881,12 +12881,12 @@
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>ਮੋੜੇ</t>
+          <t>ਚੋਗਾਵਾਂ</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>More</t>
+          <t>Chogawan</t>
         </is>
       </c>
       <c r="E41" s="8" t="n">
@@ -12922,12 +12922,12 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>ਹਰਸ਼ਾ ਛੀਨਾ (ਅਬਾਦੀ ਵਿਚਲਾ ਕਿਲਾ)</t>
+          <t>ਨੰਗਲ ਤੋਲਾ</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>Harsha Chhina (Abadi Vichla Kila)</t>
+          <t>Nangal Tola</t>
         </is>
       </c>
       <c r="E42" s="4" t="n">
@@ -12963,12 +12963,12 @@
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
-          <t>ਵਣੀਏਕੇ</t>
+          <t>ਛਵਿੰਡਾ ਖੁਰਦ</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>Wanieke</t>
+          <t>Chawinda Khurd</t>
         </is>
       </c>
       <c r="E43" s="8" t="n">
@@ -13004,12 +13004,12 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>ਜਗਦੇਵ ਕਲਾਂ</t>
+          <t>ਅਦਲੀ ਵਾਲਾ</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>Jagdev Kalan</t>
+          <t>Adli Wala</t>
         </is>
       </c>
       <c r="E44" s="4" t="n">
@@ -13086,12 +13086,12 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>ਟਪਿਆਲਾ</t>
+          <t>ਕਮਾਸਕਾ</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>Tapiala</t>
+          <t>Kamaska</t>
         </is>
       </c>
       <c r="E46" s="4" t="n">
@@ -13127,12 +13127,12 @@
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>ਜੱਸ</t>
+          <t>ਕੋਟਲੀ ਸੱਕਾ</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>Jass</t>
+          <t>Kotli Sakka</t>
         </is>
       </c>
       <c r="E47" s="8" t="n">
@@ -13168,12 +13168,12 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>ਭੁੱਲਰ</t>
+          <t>ਠੱਠਾ</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
         <is>
-          <t>Bhullar</t>
+          <t>Thatha</t>
         </is>
       </c>
       <c r="E48" s="4" t="n">
@@ -13209,12 +13209,12 @@
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>ਜਗਦੇਵ ਕਲਾਂ</t>
+          <t>ਅਦਲੀ ਵਾਲਾ</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>Jagdev Kalan</t>
+          <t>Adli Wala</t>
         </is>
       </c>
       <c r="E49" s="8" t="n">
@@ -13250,12 +13250,12 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>ਕੋਟਲੀ ਦੋਸੰਧੀ</t>
+          <t>ਭਾਗੂਪੁਰ ਬੇਟ</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>Kotli Dosandhi</t>
+          <t>Bhagupur Bet</t>
         </is>
       </c>
       <c r="E50" s="4" t="n">
@@ -13291,12 +13291,12 @@
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>ਜਗਦੇਵ ਕਲਾਂ</t>
+          <t>ਬੂਆ ਨੰਗਲੀ</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>Jagdev Kalan</t>
+          <t>Bua Nangali</t>
         </is>
       </c>
       <c r="E51" s="8" t="n">
@@ -13332,12 +13332,12 @@
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>ਮਾਦੇਕੇ</t>
+          <t>ਕਲੇਰ</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>Madeke</t>
+          <t>Kaler</t>
         </is>
       </c>
       <c r="E52" s="4" t="n">
@@ -13373,12 +13373,12 @@
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>ਬੋਪਾਰਾਏ ਕਲਾਂ</t>
+          <t>ਮੱਧੋਕੇ</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>Boparai Kalan</t>
+          <t>Madhoke</t>
         </is>
       </c>
       <c r="E53" s="8" t="n">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>ਓਠੀਆਂ</t>
+          <t>ਚੱਕ ਮਿਸ਼ਰੀ ਖ਼ਾਨ</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>Othian</t>
+          <t>Chakk Mishri Khan</t>
         </is>
       </c>
       <c r="E54" s="4" t="n">
@@ -13455,12 +13455,12 @@
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>ਚੱਕ ਮਿਸਰੀ ਖਾਂ</t>
+          <t>ਚੋਗਾਵਾਂ</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>Chak Misri Khan</t>
+          <t>Chogawan</t>
         </is>
       </c>
       <c r="E55" s="8" t="n">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>ਬੱਗਾ ਕਲਾਂ</t>
+          <t>ਹਰਸ਼ਾ ਛੀਨਾ (ਅਬਾਦੀ ਵਿਚਲਾ ਕਿਲ੍ਹਾ)</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>Bagga Kalan</t>
+          <t>Harsha Chhina (Abadi Vichla Qila)</t>
         </is>
       </c>
       <c r="E56" s="4" t="n">
@@ -13537,12 +13537,12 @@
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>ਨੰਗਲ ਤੋਲਾ</t>
+          <t>ਬਲਾਗਣ</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>Nangal Tola</t>
+          <t>Balagan</t>
         </is>
       </c>
       <c r="E57" s="8" t="n">
@@ -13578,12 +13578,12 @@
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>ਭੰਗਵਾਂ + ਸਿਧਵਾਂ + ਠੀਕਰੀਵਾਲਾ</t>
+          <t>ਬਾਚੀਵਿੰਡ</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>Bhangwan + Sidhwan + Theekriwala</t>
+          <t>Bachiwind</t>
         </is>
       </c>
       <c r="E58" s="4" t="n">
@@ -13619,12 +13619,12 @@
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>ਬੁਰਜ + ਛਿੰਡੀ ਨੈਣ</t>
+          <t>ਬੁਰਜ</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>Burj + Chindi Nain</t>
+          <t>Burj</t>
         </is>
       </c>
       <c r="E59" s="8" t="n">
@@ -13660,12 +13660,12 @@
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>ਠੱਠਾ</t>
+          <t>ਬਾਚੀਵਿੰਡ</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>Thattha</t>
+          <t>Bachiwind</t>
         </is>
       </c>
       <c r="E60" s="4" t="n">
@@ -13701,12 +13701,12 @@
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>ਜਸਰੌਰ</t>
+          <t>ਕੋਟਲਾ ਸੂਰਜ ਲੋਹਾਰ</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>Jasraur</t>
+          <t>Kotla Suraaj Lohar</t>
         </is>
       </c>
       <c r="E61" s="8" t="n">
@@ -13742,12 +13742,12 @@
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>ਛਿੱਡਣ</t>
+          <t>ਬਰਾੜ</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>Chhiddan</t>
+          <t>Brar</t>
         </is>
       </c>
       <c r="E62" s="4" t="n">
@@ -13783,12 +13783,12 @@
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>ਸਾਰੰਗੜਾ</t>
+          <t>ਕੰਵੈ</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>Sarangra</t>
+          <t>Kanve</t>
         </is>
       </c>
       <c r="E63" s="8" t="n">
@@ -13824,12 +13824,12 @@
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>ਲੇਪੋਕੇ</t>
+          <t>ਭਿਲੋਵਾਲ ਕਾਕੇ ਜੀ</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>Lepoke</t>
+          <t>Bhilaowal Kakeji</t>
         </is>
       </c>
       <c r="E64" s="4" t="n">
@@ -13865,12 +13865,12 @@
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
-          <t>ਕੱਕੜ</t>
+          <t>ਰਾਣੀਆਂ</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>Kakkar</t>
+          <t>Ranian</t>
         </is>
       </c>
       <c r="E65" s="8" t="n">
@@ -13906,12 +13906,12 @@
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>ਚੋਗਾਵਾਂ</t>
+          <t>ਭੁੱਲਰ</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>Chogawan</t>
+          <t>Bhullar</t>
         </is>
       </c>
       <c r="E66" s="4" t="n">
@@ -13947,12 +13947,12 @@
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>ਜਸਤਰਵਾਲ</t>
+          <t>ਬੋਹਲੀਆ</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>Jastarwal</t>
+          <t>Bohlian</t>
         </is>
       </c>
       <c r="E67" s="8" t="n">
@@ -13988,12 +13988,12 @@
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>ਪੰਜ ਰਾਏ</t>
+          <t>ਲੋਪੋਕੇ</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
         <is>
-          <t>Panj Rai</t>
+          <t>Lopoke</t>
         </is>
       </c>
       <c r="E68" s="4" t="n">
@@ -14029,12 +14029,12 @@
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>ਹਰਸ਼ਾ ਛੀਨਾ (ਅਬਾਦੀ ਵਿਚਲਾ ਕਿਲਾ)</t>
+          <t>ਨੰਗਲ ਤੋਲਾ</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>Harsha Chhina (Abadi Vichla Kila)</t>
+          <t>Nangal Tola</t>
         </is>
       </c>
       <c r="E69" s="8" t="n">
@@ -14070,12 +14070,12 @@
       </c>
       <c r="C70" s="3" t="inlineStr">
         <is>
-          <t>ਵਾਰਡ ਨੰ 2 ਮੁਹੱਲਾ ਗਾਧੀ ਨਗਰ ਰਾਜਾਸਾਂਸੀ + ਵਾਰਡ ਨੰ 2 ਮੁਹੱਲਾ ਗਾਧੀ ਨਗਰ ਰਾਜਾਸਾਂਸੀ</t>
+          <t>ਰਾਜਾ ਸਾਂਸੀ</t>
         </is>
       </c>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>Ward No 2 Muhalla Gandhi Nagar Rajasansi + Ward No 2 Muhalla Gandhi Nagar Rajasansi</t>
+          <t>Raja Sansi</t>
         </is>
       </c>
       <c r="E70" s="4" t="n">
@@ -14095,7 +14095,7 @@
       </c>
       <c r="J70" s="11" t="inlineStr">
         <is>
-          <t>Mukhwinder Singh Mahal (BJP)</t>
+          <t>Mukhwinder Singh (BJP)</t>
         </is>
       </c>
       <c r="K70" s="4" t="n">
@@ -14111,12 +14111,12 @@
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>ਤਰੀਨ + ਕਾਕੜ</t>
+          <t>ਕਰਿਆਲ</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>Tareen + Kakar</t>
+          <t>Karyal</t>
         </is>
       </c>
       <c r="E71" s="8" t="n">
@@ -14152,12 +14152,12 @@
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>ਸ਼ਹੂਰਾ</t>
+          <t>ਵੈਣੇਕੇ</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>Shahura</t>
+          <t>Vaineke</t>
         </is>
       </c>
       <c r="E72" s="4" t="n">
@@ -14193,12 +14193,12 @@
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>ਬੋਪਾਰਾਏ ਖੁਰਦ</t>
+          <t>ਖਿਆਲਾ ਕਲਾਂ</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>Boparai Khurd</t>
+          <t>Khiala Kalan</t>
         </is>
       </c>
       <c r="E73" s="8" t="n">
@@ -14234,12 +14234,12 @@
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>ਧਾਰੀਵਾਲ + ਉਧਰ + ਮੁਲਾ ਕੋਟ</t>
+          <t>ਸਾਰੰਗੜਾ</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>Dhariwal + Udhar + Mulla Kot</t>
+          <t>Sarangra</t>
         </is>
       </c>
       <c r="E74" s="4" t="n">
@@ -14275,12 +14275,12 @@
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
-          <t>ਕਾਂਦੇ</t>
+          <t>ਲੋਪੋਕੇ</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>Kande</t>
+          <t>Lopoke</t>
         </is>
       </c>
       <c r="E75" s="8" t="n">
@@ -14316,12 +14316,12 @@
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>ਕੋਹਾਲੀ</t>
+          <t>ਬੱਗਾ ਕਲਾਂ</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>Kohali</t>
+          <t>Bagga Kalan</t>
         </is>
       </c>
       <c r="E76" s="4" t="n">
@@ -14357,12 +14357,12 @@
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
-          <t>ਵੈਰੋਕੇ</t>
+          <t>ਮੁੱਢ</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>Vairoke</t>
+          <t>Mudh</t>
         </is>
       </c>
       <c r="E77" s="8" t="n">
@@ -14398,12 +14398,12 @@
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>ਸੱੜੀਆਂ</t>
+          <t>ਕਰਿਆਲ</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
         <is>
-          <t>Sarrian</t>
+          <t>Karyal</t>
         </is>
       </c>
       <c r="E78" s="4" t="n">
@@ -14439,12 +14439,12 @@
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>ਲਦੇਹ</t>
+          <t>ਜਗਦੇਵ ਕਲਾਂ</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>Ladeh</t>
+          <t>Jagdev Kalan</t>
         </is>
       </c>
       <c r="E79" s="8" t="n">
@@ -14480,12 +14480,12 @@
       </c>
       <c r="C80" s="3" t="inlineStr">
         <is>
-          <t>ਚੋਗਾਵਾਂ</t>
+          <t>ਭੁੱਲਰ</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
         <is>
-          <t>Chogawan</t>
+          <t>Bhullar</t>
         </is>
       </c>
       <c r="E80" s="4" t="n">
@@ -14521,12 +14521,12 @@
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>ਚੋਗਾਵਾਂ</t>
+          <t>ਭੁੱਲਰ</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>Chogawan</t>
+          <t>Bhullar</t>
         </is>
       </c>
       <c r="E81" s="8" t="n">
@@ -14562,12 +14562,12 @@
       </c>
       <c r="C82" s="3" t="inlineStr">
         <is>
-          <t>ਪੰਜ ਕਲਾ + ਚੱਕ ਬਾਜੀਦ</t>
+          <t>ਭਿੰਡੀ ਸੈਦਾਂ</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
         <is>
-          <t>Panj Kala + Chak Bajid</t>
+          <t>Bhindi Saidan</t>
         </is>
       </c>
       <c r="E82" s="4" t="n">
@@ -14603,12 +14603,12 @@
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>ਉਮਰਪੁਰਾ + ਚਾਹੀਆਂ</t>
+          <t>ਧਰਮਕੋਟ</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>Umarpura + Chahian</t>
+          <t>Dharamkot</t>
         </is>
       </c>
       <c r="E83" s="8" t="n">
@@ -14644,12 +14644,12 @@
       </c>
       <c r="C84" s="3" t="inlineStr">
         <is>
-          <t>ਬੋਪਾਰਾਏ ਕਲਾਂ</t>
+          <t>ਬਰਾੜ</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
         <is>
-          <t>Boparai Kalan</t>
+          <t>Brar</t>
         </is>
       </c>
       <c r="E84" s="4" t="n">
@@ -14685,12 +14685,12 @@
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>ਮੇਹਾਰ</t>
+          <t>ਓਠੀਆਂ</t>
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>Mehar</t>
+          <t>Othian</t>
         </is>
       </c>
       <c r="E85" s="8" t="n">
@@ -14726,12 +14726,12 @@
       </c>
       <c r="C86" s="3" t="inlineStr">
         <is>
-          <t>ਕੋਹਾਲੀ + ਰੱਖ ਕੋਹਾਲੀ</t>
+          <t>ਬੱਗਾ ਕਲਾਂ</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>Kohali + Rakh Kohali</t>
+          <t>Bagga Kalan</t>
         </is>
       </c>
       <c r="E86" s="4" t="n">
@@ -14767,12 +14767,12 @@
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>ਤੁਤ</t>
+          <t>ਮੋਹਲੇਕੇ</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>Tut</t>
+          <t>Mohaleke</t>
         </is>
       </c>
       <c r="E87" s="8" t="n">
@@ -14808,12 +14808,12 @@
       </c>
       <c r="C88" s="3" t="inlineStr">
         <is>
-          <t>ਤੱਲਾ</t>
+          <t>ਮਿਆਦੀ ਕਲਾਂ</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
         <is>
-          <t>Talla</t>
+          <t>Miadi Kalan</t>
         </is>
       </c>
       <c r="E88" s="4" t="n">
@@ -14849,12 +14849,12 @@
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>ਸ਼ਾਹਪੁਰ + ਮਿਆਦੀ ਖੁਰਦ + ਆਲਮਪੁਰ + ਚੱਕ ਫਤਿਹ ਖਾਂ</t>
+          <t>ਭਿੰਡੀ ਸੈਦਾਂ</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>Shahpur + Miadi Khurd + Alampur + Chak Fateh Khan</t>
+          <t>Bhindi Saidan</t>
         </is>
       </c>
       <c r="E89" s="8" t="n">
@@ -14890,12 +14890,12 @@
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>ਵਾਰਡ ਨੰ.12 ਰਾਜਾਸਾਂਸੀ ਮੁਹੱਲਾ ਗਾਂਧੀ ਨਗਰ + ਵਾਰਡ ਨੰ.12 ਮੁਹੱਲਾ ਗਾਂਧੀ ਨਗਰ</t>
+          <t>ਰਾਜਾ ਸਾਂਸੀ</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>Ward No. 12 Rajasansi Muhalla Gandhi Nagar + Ward No. 12 Muhalla Gandhi Nagar</t>
+          <t>Raja Sansi</t>
         </is>
       </c>
       <c r="E90" s="4" t="n">
@@ -14972,12 +14972,12 @@
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>ਬੋਪਾ ਰਾਏ ਬਾਜ ਸਿੰਘ</t>
+          <t>ਕੋਹਾਲੀ</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>Bopa Rai Baj Singh</t>
+          <t>Kohali</t>
         </is>
       </c>
       <c r="E92" s="4" t="n">
@@ -15013,12 +15013,12 @@
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
-          <t>ਭਿੰਡੀ ਅੌਲਖ ਖੁਰਦ</t>
+          <t>ਜਸਰੌਰ</t>
         </is>
       </c>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>Bhindi Aulakh Khurd</t>
+          <t>Jasarour</t>
         </is>
       </c>
       <c r="E93" s="8" t="n">
@@ -15054,12 +15054,12 @@
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>ਚੁਚਕਵਾਲ + ਮੁਜੱਫਰਪੁਰਾ</t>
+          <t>ਤਰੀਨ</t>
         </is>
       </c>
       <c r="D94" s="3" t="inlineStr">
         <is>
-          <t>Chuchakwal + Mujaffarpura</t>
+          <t>Tareen</t>
         </is>
       </c>
       <c r="E94" s="4" t="n">
@@ -15095,12 +15095,12 @@
       </c>
       <c r="C95" s="7" t="inlineStr">
         <is>
-          <t>ਮੁਗਲਾਣੀ ਕੋਟ</t>
+          <t>ਮੱਲੂ ਨੰਗਲ</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>Muglani Kot</t>
+          <t>Mallu Nangal</t>
         </is>
       </c>
       <c r="E95" s="8" t="n">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>ਧਰਮਕੋਟ</t>
+          <t>ਚੱਕ ਮਿਸ਼ਰੀ ਖ਼ਾਨ</t>
         </is>
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>Dharmkot</t>
+          <t>Chakk Mishri Khan</t>
         </is>
       </c>
       <c r="E96" s="4" t="n">
@@ -15177,12 +15177,12 @@
       </c>
       <c r="C97" s="7" t="inlineStr">
         <is>
-          <t>ਵਾਰਡ ਨੰ.9 ਮੇਨ ਬਜਾਰ ਗਲੀ ਲੋਹਾਰਾਂ ਵਾਲੀ + ਵਾਰਡ ਨੰ.9 ਗਲੀ ਮਿਸਤਰੀ ਮੇਹਰ ਸਿੰਘ ਵਾਲੀ + ਵਾਰਡ ਨੰ.9 ਗਲੀ ਮਿਸਤਰੀ ਮੇਹਰ ਸਿੰਘ ਵਾਲੀ + ਵਾਰਡ ਨੰ. 9 ਸਾਹਮਣੇ ਬਗੀਚੀ</t>
+          <t>ਜਗਦੇਵ ਕਲਾਂ</t>
         </is>
       </c>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>Ward No. 9 Main Bazar Gali Lohara Wali + Ward No. 9 Gali Mistri Mehar Singh Wali + Ward No. 9 Gali Mistri Mehar Singh Wali + Ward No. 9 Sahamne Bagichi</t>
+          <t>Jagdev Kalan</t>
         </is>
       </c>
       <c r="E97" s="8" t="n">
@@ -15218,12 +15218,12 @@
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>ਕੋਟਲੀ ਖਹਿਰਾ + ਵੰਡਾਲ + ਭਲੋਟ</t>
+          <t>ਸ਼ਾਹਪੁਰ</t>
         </is>
       </c>
       <c r="D98" s="3" t="inlineStr">
         <is>
-          <t>Kotli Khaira + Vandal + Bhalot</t>
+          <t>Shahpur</t>
         </is>
       </c>
       <c r="E98" s="4" t="n">
@@ -15259,12 +15259,12 @@
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
-          <t>ਲੇਪੋਕੇ</t>
+          <t>ਲੋਪੋਕੇ</t>
         </is>
       </c>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>Lepoke</t>
+          <t>Lopoke</t>
         </is>
       </c>
       <c r="E99" s="8" t="n">
@@ -15300,12 +15300,12 @@
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>ਚਵਿੰਡਾ ਕਲਾਂ</t>
+          <t>ਛਿੱਦਣ</t>
         </is>
       </c>
       <c r="D100" s="3" t="inlineStr">
         <is>
-          <t>Chawinda Kalan</t>
+          <t>Chhidan</t>
         </is>
       </c>
       <c r="E100" s="4" t="n">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="C101" s="7" t="inlineStr">
         <is>
-          <t>ਕੋਟਲੀ ਕੋਰੇਟਾਨਾ</t>
+          <t>ਮਤੀਆ</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>Kotli Koretana</t>
+          <t>Matiya</t>
         </is>
       </c>
       <c r="E101" s="8" t="n">
@@ -15382,12 +15382,12 @@
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>ਡੱਲੇਕੀ</t>
+          <t>ਕੋਹਾਲਾ</t>
         </is>
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
-          <t>Dalleki</t>
+          <t>Kohala</t>
         </is>
       </c>
       <c r="E102" s="4" t="n">
@@ -15423,12 +15423,12 @@
       </c>
       <c r="C103" s="7" t="inlineStr">
         <is>
-          <t>ਚਵਿੰਡਾ ਖੁਰਦ</t>
+          <t>ਛਿੱਦਣ</t>
         </is>
       </c>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>Chawinda Khurd</t>
+          <t>Chhidan</t>
         </is>
       </c>
       <c r="E103" s="8" t="n">
@@ -15464,12 +15464,12 @@
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>ਡਾਲਾ</t>
+          <t>ਬਹਿੜਵਾਲ</t>
         </is>
       </c>
       <c r="D104" s="3" t="inlineStr">
         <is>
-          <t>Dala</t>
+          <t>Beharwal</t>
         </is>
       </c>
       <c r="E104" s="4" t="n">
@@ -15505,12 +15505,12 @@
       </c>
       <c r="C105" s="7" t="inlineStr">
         <is>
-          <t>ਹਰਸ਼ਾ ਛੀਨਾ (ਅਬਾਦੀ ਉੱਚਾ ਕਿਲਾ)</t>
+          <t>ਹਰਸ਼ਾ ਛੀਨਾ (ਅਬਾਦੀ ਸਬਾਜਪੁਰ)</t>
         </is>
       </c>
       <c r="D105" s="7" t="inlineStr">
         <is>
-          <t>Harsha Chhina (Abadi Ucha Kila)</t>
+          <t>Harsha Chhina (Abadi Sabajpur)</t>
         </is>
       </c>
       <c r="E105" s="8" t="n">
@@ -15546,12 +15546,12 @@
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>ਸੈਦਪੁਰ ਕਲਾਂ</t>
+          <t>ਛੰਨ ਕਲਾਂ</t>
         </is>
       </c>
       <c r="D106" s="3" t="inlineStr">
         <is>
-          <t>Saidpur Kalan</t>
+          <t>Chhan Kalan</t>
         </is>
       </c>
       <c r="E106" s="4" t="n">
@@ -15587,12 +15587,12 @@
       </c>
       <c r="C107" s="7" t="inlineStr">
         <is>
-          <t>ਰਾਏ</t>
+          <t>ਸਾਰੰਗੜਾ</t>
         </is>
       </c>
       <c r="D107" s="7" t="inlineStr">
         <is>
-          <t>Rai</t>
+          <t>Sarangra</t>
         </is>
       </c>
       <c r="E107" s="8" t="n">
@@ -15628,12 +15628,12 @@
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>ਅਵਾਨ ਬਸਾਊ + ਡਿਆਲ</t>
+          <t>ਅਵਾਨ ਬਸਾਊ</t>
         </is>
       </c>
       <c r="D108" s="3" t="inlineStr">
         <is>
-          <t>Awan Basau + Dial</t>
+          <t>Awan Basau</t>
         </is>
       </c>
       <c r="E108" s="4" t="n">
@@ -15669,12 +15669,12 @@
       </c>
       <c r="C109" s="7" t="inlineStr">
         <is>
-          <t>ਰਾਣੀਆਂ</t>
+          <t>ਰਾਏ</t>
         </is>
       </c>
       <c r="D109" s="7" t="inlineStr">
         <is>
-          <t>Rania</t>
+          <t>Rai</t>
         </is>
       </c>
       <c r="E109" s="8" t="n">
@@ -15710,12 +15710,12 @@
       </c>
       <c r="C110" s="3" t="inlineStr">
         <is>
-          <t>ਖਿਆਲਾ ਖੁਰਦ</t>
+          <t>ਭਿੱਟੇਵੱਡ</t>
         </is>
       </c>
       <c r="D110" s="3" t="inlineStr">
         <is>
-          <t>Khiala Khurd</t>
+          <t>Bhittewad</t>
         </is>
       </c>
       <c r="E110" s="4" t="n">
@@ -15751,12 +15751,12 @@
       </c>
       <c r="C111" s="7" t="inlineStr">
         <is>
-          <t>ਵਾਰਡ ਨੰ.5 ਕਲੋਨੀ ਬਾਬਾ ਜਵੰਦ ਸਿੰਘ ਅਜਨਾਲਾ ਰੋਡ + ਵਾਰਡ ਨੰ.5 ਨਵਾਂ ਅੱਡਾ ਰਾਜਾਸਾਂਸੀ + ਵਾਰਡ ਨੰ.5 ਅਜਨਾਲਾ ਰੋਡ ਨੇੜੇ ਅਜੀਤ ਪੈਲਸ + ਵਾਰਡ ਨੰ.5 ਅਜਨਾਲਾ ਰੋਡ ਖੱਬਾ ਪਾਸਾ ਖੂਹ ਚੂਹੜ ਸਿੰਘ ਵਾਲਾ + ਵਾਰਡ ਨੰ.5 ਅਜਨਾਲਾ ਰੋਡ ਖੱਬਾ ਪਾਸਾ ਖੂਹ ਚੂਹੜ ਸਿੰਘ ਵਾਲਾ + ਵਾਰਡ ਨੰ.5 ਅਜਨਾਲਾ ਰੋਡ ਖੱਬਾ ਪਾਸਾ ਖੂਹ ਚੂਹੜ ਸਿੰਘ ਵਾਲਾ + ਵਾਰਡ ਨੰ.5 ਅਜਨਾਲਾ ਰੋਡ ਸਿਵਲ ਕਲੋਨੀ ਏਅਰ ਪੋਰਟ</t>
+          <t>ਰਾਣੇਵਾਲੀ</t>
         </is>
       </c>
       <c r="D111" s="7" t="inlineStr">
         <is>
-          <t>Ward No. 5 Colony Baba Jawand Singh Ajnala Road + Ward No. 5 Nawan Adda Rajasansi + Ward No. 5 Ajnala Road Nere Ajit Palace + Ward No. 5 Ajnala Road Khabba Pasa Khooh Chuhar Singh Wala + Ward No. 5 Ajnala Road Khabba Pasa Khooh Chuhar Singh Wala + Ward No. 5 Ajnala Road Khabba Pasa Khooh Chuhar Singh Wala + Ward No. 5 Ajnala Road Civil Colony Airport</t>
+          <t>Ranewali</t>
         </is>
       </c>
       <c r="E111" s="8" t="n">
@@ -15792,12 +15792,12 @@
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>ਚਵਿੰਡਾ ਕਲਾਂ</t>
+          <t>ਨੂਰਪੁਰ</t>
         </is>
       </c>
       <c r="D112" s="3" t="inlineStr">
         <is>
-          <t>Chawinda Kalan</t>
+          <t>Nurpur</t>
         </is>
       </c>
       <c r="E112" s="4" t="n">
@@ -15833,12 +15833,12 @@
       </c>
       <c r="C113" s="7" t="inlineStr">
         <is>
-          <t>ਲਾਂਦੇ</t>
+          <t>ਬੋਪਾਰਾਏ ਖੁਰਦ</t>
         </is>
       </c>
       <c r="D113" s="7" t="inlineStr">
         <is>
-          <t>Lande</t>
+          <t>Bopa Rai Khurd</t>
         </is>
       </c>
       <c r="E113" s="8" t="n">
@@ -15874,12 +15874,12 @@
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>ਪ੍ਰੀਤ ਨਗਰ ਰ.ਬ.ਨੰ. 167 + ਓਵਰਸੀਜ਼ ਇਲੈਕਟਰ</t>
+          <t>ਭਿਲੋਵਾਲ ਪੱਕਾ</t>
         </is>
       </c>
       <c r="D114" s="3" t="inlineStr">
         <is>
-          <t>Preet Nagar R.B.No. 167 + Overseas Elector</t>
+          <t>Bhillowal Pakka</t>
         </is>
       </c>
       <c r="E114" s="4" t="n">
@@ -15915,12 +15915,12 @@
       </c>
       <c r="C115" s="7" t="inlineStr">
         <is>
-          <t>ਕੋਟਲਾ ਡੂਮ</t>
+          <t>ਰਾਜਾ ਸਾਂਸੀ</t>
         </is>
       </c>
       <c r="D115" s="7" t="inlineStr">
         <is>
-          <t>Kotla Doom</t>
+          <t>Raja Sansi</t>
         </is>
       </c>
       <c r="E115" s="8" t="n">
@@ -15956,12 +15956,12 @@
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>ਡੱਗ ਡੋਗਰ</t>
+          <t>ਤੂਤ</t>
         </is>
       </c>
       <c r="D116" s="3" t="inlineStr">
         <is>
-          <t>Dagg Dogar</t>
+          <t>Toot</t>
         </is>
       </c>
       <c r="E116" s="4" t="n">
@@ -15997,12 +15997,12 @@
       </c>
       <c r="C117" s="7" t="inlineStr">
         <is>
-          <t>ਪੰਡੇਰੀ + ਮੱਧਪੁਰਾ</t>
+          <t>ਸਾਰੰਗੜਾ</t>
         </is>
       </c>
       <c r="D117" s="7" t="inlineStr">
         <is>
-          <t>Panderi + Madhpura</t>
+          <t>Sarangra</t>
         </is>
       </c>
       <c r="E117" s="8" t="n">
@@ -16038,12 +16038,12 @@
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>ਝੰਜੋਟੀ</t>
+          <t>ਸੈਦਪੁਰ</t>
         </is>
       </c>
       <c r="D118" s="3" t="inlineStr">
         <is>
-          <t>Jhanjoti</t>
+          <t>Saidpur</t>
         </is>
       </c>
       <c r="E118" s="4" t="n">
@@ -16079,12 +16079,12 @@
       </c>
       <c r="C119" s="7" t="inlineStr">
         <is>
-          <t>ਮੰਜ</t>
+          <t>ਕੱਕੜ</t>
         </is>
       </c>
       <c r="D119" s="7" t="inlineStr">
         <is>
-          <t>Manj</t>
+          <t>Kakkar</t>
         </is>
       </c>
       <c r="E119" s="8" t="n">
@@ -16161,12 +16161,12 @@
       </c>
       <c r="C121" s="7" t="inlineStr">
         <is>
-          <t>ਵਾਰਡ ਨੰ.13 ਗਲੀ ਲੋਹਾਰਾਂ ਵਾਲੀ + ਵਾਰਡ ਨੰ.13 ਮੁਹੱਲਾ ਮਸੀਤ ਵਾਲਾ + ਵਾਰਡ ਨੰ.13 ਮੇਨ ਬਜਾਰ ਸਾਹਮਣੇ ਮੁਹੱਲਾ ਠਾਕਰ ਸਿੰਘ ਵਾਲਾ + ਵਾਰਡ ਨੰ.13 ਮੇਨ ਬਜਾਰ ਸਾਹਮਣੇ ਮੁਹੱਲਾ ਠਾਕਰ ਸਿੰਘ ਵਾਲਾ + ਓਵਰਸੀਜ਼ ਇਲੈਕਟਰ</t>
+          <t>ਜਗਦੇਵ ਕਲਾਂ</t>
         </is>
       </c>
       <c r="D121" s="7" t="inlineStr">
         <is>
-          <t>Ward No. 13 Gali Lohara Wali + Ward No. 13 Muhalla Masit Wala + Ward No. 13 Main Bazar Sahamne Muhalla Thakar Singh Wala + Ward No. 13 Main Bazar Sahamne Muhalla Thakar Singh Wala + Overseas Elector</t>
+          <t>Jagdev Kalan</t>
         </is>
       </c>
       <c r="E121" s="8" t="n">
@@ -16243,12 +16243,12 @@
       </c>
       <c r="C123" s="7" t="inlineStr">
         <is>
-          <t>ਪੱਧਰੀ</t>
+          <t>ਬੋਪਾਰਾਏ ਕਲਾਂ</t>
         </is>
       </c>
       <c r="D123" s="7" t="inlineStr">
         <is>
-          <t>Paddhari</t>
+          <t>Bopa Rai Kalan</t>
         </is>
       </c>
       <c r="E123" s="8" t="n">
@@ -16284,12 +16284,12 @@
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>ਬੱਚੀਵਿੰਡ</t>
+          <t>ਡੱਲੇਕੇ</t>
         </is>
       </c>
       <c r="D124" s="3" t="inlineStr">
         <is>
-          <t>Bachhiwind</t>
+          <t>Dalleki</t>
         </is>
       </c>
       <c r="E124" s="4" t="n">
@@ -16325,12 +16325,12 @@
       </c>
       <c r="C125" s="7" t="inlineStr">
         <is>
-          <t>ਭਿੰਡੀ ਅੌਲਖ ਖੁਰਦ</t>
+          <t>ਜਸਰੌਰ</t>
         </is>
       </c>
       <c r="D125" s="7" t="inlineStr">
         <is>
-          <t>Bhindi Aulakh Khurd</t>
+          <t>Jasarour</t>
         </is>
       </c>
       <c r="E125" s="8" t="n">
@@ -16366,12 +16366,12 @@
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>ਵਾਰਡ ਨੰ. 1 ਮੁਹੱਲਾ ਗਾਂਧੀ ਨਗਰ + ਵਾਰਡ ਨੰ.1 ਮੁਹੱਲਾ ਗਾਂਧੀ ਨਗਰ + ਵਾਰਡ ਨੰ.1 ਮੁਹੱਲਾ ਗਾਂਧੀ ਨਗਰ + ਵਾਰਡ ਨੰ.1 ਮੁਹੱਲਾ ਗਾਂਧੀ ਨਗਰ</t>
+          <t>ਰਾਜਾ ਸਾਂਸੀ</t>
         </is>
       </c>
       <c r="D126" s="3" t="inlineStr">
         <is>
-          <t>Ward No. 1 Muhalla Gandhi Nagar + Ward No. 1 Muhalla Gandhi Nagar + Ward No. 1 Muhalla Gandhi Nagar + Ward No. 1 Muhalla Gandhi Nagar</t>
+          <t>Raja Sansi</t>
         </is>
       </c>
       <c r="E126" s="4" t="n">
@@ -16448,12 +16448,12 @@
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>ਮਟੀਆ</t>
+          <t>ਓਠੀਆਂ</t>
         </is>
       </c>
       <c r="D128" s="3" t="inlineStr">
         <is>
-          <t>Matia</t>
+          <t>Othian</t>
         </is>
       </c>
       <c r="E128" s="4" t="n">
@@ -16489,12 +16489,12 @@
       </c>
       <c r="C129" s="7" t="inlineStr">
         <is>
-          <t>ਜੋਏਕੇ</t>
+          <t>ਕਿਰਲਗੜ੍ਹ</t>
         </is>
       </c>
       <c r="D129" s="7" t="inlineStr">
         <is>
-          <t>Joeke</t>
+          <t>Kiralgarh</t>
         </is>
       </c>
       <c r="E129" s="8" t="n">
@@ -16530,12 +16530,12 @@
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>ਲੇਪੋਕੇ</t>
+          <t>ਵੇਰੋਕੇ</t>
         </is>
       </c>
       <c r="D130" s="3" t="inlineStr">
         <is>
-          <t>Lepoke</t>
+          <t>Veroke</t>
         </is>
       </c>
       <c r="E130" s="4" t="n">
@@ -16571,12 +16571,12 @@
       </c>
       <c r="C131" s="7" t="inlineStr">
         <is>
-          <t>ਨੂਰਪੁਰ</t>
+          <t>ਬੋਪਾਰਾਏ ਖੁਰਦ</t>
         </is>
       </c>
       <c r="D131" s="7" t="inlineStr">
         <is>
-          <t>Nurpur</t>
+          <t>Bopa Rai Khurd</t>
         </is>
       </c>
       <c r="E131" s="8" t="n">
@@ -16612,12 +16612,12 @@
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>ਜੱਜੇ + ਮਾਲਾਕੀੜੀ</t>
+          <t>ਮਾਨਾਵਾਲਾ</t>
         </is>
       </c>
       <c r="D132" s="3" t="inlineStr">
         <is>
-          <t>Jajje + Malakiri</t>
+          <t>Manawala</t>
         </is>
       </c>
       <c r="E132" s="4" t="n">
@@ -16658,7 +16658,7 @@
       </c>
       <c r="D133" s="7" t="inlineStr">
         <is>
-          <t>Awan Basau</t>
+          <t>Awan Bassau</t>
         </is>
       </c>
       <c r="E133" s="8" t="n">
@@ -16694,12 +16694,12 @@
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>ਮੰਜ + ਦਸਮੇਸ਼ ਨਗਰ</t>
+          <t>ਕੱਕੜ</t>
         </is>
       </c>
       <c r="D134" s="3" t="inlineStr">
         <is>
-          <t>Manj + Dasmesh Nagar</t>
+          <t>Kakkar</t>
         </is>
       </c>
       <c r="E134" s="4" t="n">
@@ -16735,12 +16735,12 @@
       </c>
       <c r="C135" s="7" t="inlineStr">
         <is>
-          <t>ਮਾਨਾਵਾਲਾ</t>
+          <t>ਚੋਗਾਵਾਂ</t>
         </is>
       </c>
       <c r="D135" s="7" t="inlineStr">
         <is>
-          <t>Manawala</t>
+          <t>Chogawan</t>
         </is>
       </c>
       <c r="E135" s="8" t="n">
@@ -16776,12 +16776,12 @@
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
-          <t>ਕੋਟਲੀ ਦੇਸਾਂ</t>
+          <t>ਵੇਹੜਾ</t>
         </is>
       </c>
       <c r="D136" s="3" t="inlineStr">
         <is>
-          <t>Kotli Desan</t>
+          <t>Vehra</t>
         </is>
       </c>
       <c r="E136" s="4" t="n">
@@ -16817,12 +16817,12 @@
       </c>
       <c r="C137" s="7" t="inlineStr">
         <is>
-          <t>ਰਾਜਾਸਾਂਸੀ ਵਾਰਡ ਨੰ. 3 ਗਲੀ ਡਾਕਟਰ ਅਮਰ ਸਿੰਘ ਵਾਲੀ + ਵਾਰਡ ਨੰ.3 ਅਦਲੀ ਵਾਲਾ ਰੋਡ ਖੱਬਾ ਪਾਸਾ ਰਾਜਾਸਾਂਸੀ + ਵਾਰਡ ਨੰ.3 ਗਲੀ ਪਰੋਹਿਤਾਂ ਵਾਲੀ + ਵਾਰਡ ਨੰ.3 ਵਾਲਾ ਖੂਹ ਲੇਲੀਆ ਵਾਲਾ, ਨਵੀ ਕਲੋਨੀ</t>
+          <t>ਰਾਜਾ ਸਾਂਸੀ</t>
         </is>
       </c>
       <c r="D137" s="7" t="inlineStr">
         <is>
-          <t>Rajasansi Ward No. 3 Gali Doctor Amar Singh Wali + Ward No. 3 Adli Wala Road Khabba Pasa Rajasansi + Ward No. 3 Gali Purohita Wali + Ward No. 3 Wala Khooh Lelia Wala, Navi Colony</t>
+          <t>Raja Sansi</t>
         </is>
       </c>
       <c r="E137" s="8" t="n">
@@ -16858,12 +16858,12 @@
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>ਝੋਜੇਟੀ</t>
+          <t>ਕੋਟਲਾ ਡੂਮ</t>
         </is>
       </c>
       <c r="D138" s="3" t="inlineStr">
         <is>
-          <t>Jhojeti</t>
+          <t>Kotla Doom</t>
         </is>
       </c>
       <c r="E138" s="4" t="n">
@@ -16899,12 +16899,12 @@
       </c>
       <c r="C139" s="7" t="inlineStr">
         <is>
-          <t>ਬੱਲਗਣ ਸਿੰਧੂ</t>
+          <t>ਰਾਜਾ ਸਾਂਸੀ</t>
         </is>
       </c>
       <c r="D139" s="7" t="inlineStr">
         <is>
-          <t>Balaggan Sindhu</t>
+          <t>Raja Sansi</t>
         </is>
       </c>
       <c r="E139" s="8" t="n">
@@ -16940,12 +16940,12 @@
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t>ਹਰਸ਼ਾ ਛੀਨਾ (ਅਬਾਦੀ ਸਬਾਜਪੁਰ)</t>
+          <t>ਝੰਜੋਟੀ</t>
         </is>
       </c>
       <c r="D140" s="3" t="inlineStr">
         <is>
-          <t>Harsha Chhina (Abadi Sabajpur)</t>
+          <t>Jhanjoti</t>
         </is>
       </c>
       <c r="E140" s="4" t="n">
@@ -16981,12 +16981,12 @@
       </c>
       <c r="C141" s="7" t="inlineStr">
         <is>
-          <t>ਬੱਚੀਵਿੰਡ</t>
+          <t>ਸ਼ਾਹੂਰਾ</t>
         </is>
       </c>
       <c r="D141" s="7" t="inlineStr">
         <is>
-          <t>Bachhiwind</t>
+          <t>Shahura</t>
         </is>
       </c>
       <c r="E141" s="8" t="n">
@@ -17063,12 +17063,12 @@
       </c>
       <c r="C143" s="7" t="inlineStr">
         <is>
-          <t>ਬਾਬਾ ਮੀਕੇ ਸ਼ਾਹ ਕਲੋਨੀ</t>
+          <t>ਭਿੱਟੇਵੱਡ</t>
         </is>
       </c>
       <c r="D143" s="7" t="inlineStr">
         <is>
-          <t>Baba Meeke Shah Colony</t>
+          <t>Bhittewad</t>
         </is>
       </c>
       <c r="E143" s="8" t="n">
@@ -17104,12 +17104,12 @@
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>ਰਡਾਲਾ</t>
+          <t>ਰਾਜਾ ਸਾਂਸੀ</t>
         </is>
       </c>
       <c r="D144" s="3" t="inlineStr">
         <is>
-          <t>Radala</t>
+          <t>Raja Sansi</t>
         </is>
       </c>
       <c r="E144" s="4" t="n">
@@ -17145,12 +17145,12 @@
       </c>
       <c r="C145" s="7" t="inlineStr">
         <is>
-          <t>ਬਰਾੜ</t>
+          <t>ਬੋਪਾਰਾਏ ਬਾਜ ਸਿੰਘ</t>
         </is>
       </c>
       <c r="D145" s="7" t="inlineStr">
         <is>
-          <t>Brar</t>
+          <t>Bopa Rai Baj Singh</t>
         </is>
       </c>
       <c r="E145" s="8" t="n">
@@ -17186,12 +17186,12 @@
       </c>
       <c r="C146" s="3" t="inlineStr">
         <is>
-          <t>ਭਿੰਡੀ ਸੈਦਾਂ</t>
+          <t>ਕੋਟਲੀ ਦੁਸੰਧੀ</t>
         </is>
       </c>
       <c r="D146" s="3" t="inlineStr">
         <is>
-          <t>Bhindi Saidan</t>
+          <t>Kotli Dosandhi</t>
         </is>
       </c>
       <c r="E146" s="4" t="n">
@@ -17227,12 +17227,12 @@
       </c>
       <c r="C147" s="7" t="inlineStr">
         <is>
-          <t>ਬੋਹਲੀਆਂ</t>
+          <t>ਉਮਰਪੁਰਾ</t>
         </is>
       </c>
       <c r="D147" s="7" t="inlineStr">
         <is>
-          <t>Bohlian</t>
+          <t>Umarpura</t>
         </is>
       </c>
       <c r="E147" s="8" t="n">
@@ -17268,12 +17268,12 @@
       </c>
       <c r="C148" s="3" t="inlineStr">
         <is>
-          <t>ਚੱਕ ਕਮਾਲ ਖਾਂ</t>
+          <t>ਮੌੜੇ</t>
         </is>
       </c>
       <c r="D148" s="3" t="inlineStr">
         <is>
-          <t>Chak Kamal Khan</t>
+          <t>Maure</t>
         </is>
       </c>
       <c r="E148" s="4" t="n">
@@ -17309,12 +17309,12 @@
       </c>
       <c r="C149" s="7" t="inlineStr">
         <is>
-          <t>ਬੱਗਾ ਖੁਰਦ + ਓਵਰਸੀਜ਼ ਇਲੈਕਟਰ</t>
+          <t>ਹਰਸ਼ਾ ਛੀਨਾ (ਅਬਾਦੀ ਉੱਚਾ ਕਿਲ੍ਹਾ)</t>
         </is>
       </c>
       <c r="D149" s="7" t="inlineStr">
         <is>
-          <t>Bagga Khurd + Overseas Elector</t>
+          <t>Harsha Chhina (Abadi Ucha Qila)</t>
         </is>
       </c>
       <c r="E149" s="8" t="n">
@@ -17350,12 +17350,12 @@
       </c>
       <c r="C150" s="3" t="inlineStr">
         <is>
-          <t>ਹਰਸ਼ਾ ਛੀਨਾ (ਕੁੱਕੜਾਂਵਾਲਾ)</t>
+          <t>ਝੰਜੋਟੀ</t>
         </is>
       </c>
       <c r="D150" s="3" t="inlineStr">
         <is>
-          <t>Harsha Chhina (Kukranwala)</t>
+          <t>Jhanjoti</t>
         </is>
       </c>
       <c r="E150" s="4" t="n">
@@ -17391,12 +17391,12 @@
       </c>
       <c r="C151" s="7" t="inlineStr">
         <is>
-          <t>ਜਸਰੌਰ</t>
+          <t>ਮੋਤਲਾ</t>
         </is>
       </c>
       <c r="D151" s="7" t="inlineStr">
         <is>
-          <t>Jasraur</t>
+          <t>Motala</t>
         </is>
       </c>
       <c r="E151" s="8" t="n">
@@ -17432,12 +17432,12 @@
       </c>
       <c r="C152" s="3" t="inlineStr">
         <is>
-          <t>ਧਾਰੀਵਾਲ</t>
+          <t>ਹਰਸ਼ਾ ਛੀਨਾ (ਅਬਾਦੀ ਵਿਚਲਾ ਕਿਲ੍ਹਾ)</t>
         </is>
       </c>
       <c r="D152" s="3" t="inlineStr">
         <is>
-          <t>Dhariwal</t>
+          <t>Harsha Chhina (Abadi Vichla Qila)</t>
         </is>
       </c>
       <c r="E152" s="4" t="n">
@@ -17514,12 +17514,12 @@
       </c>
       <c r="C154" s="3" t="inlineStr">
         <is>
-          <t>ਭਿੱਟੇਵੱਡ</t>
+          <t>ਹਰਸ਼ਾ ਛੀਨਾ (ਅਬਾਦੀ ਉੱਚਾ ਕਿਲ੍ਹਾ)</t>
         </is>
       </c>
       <c r="D154" s="3" t="inlineStr">
         <is>
-          <t>Bhittewad</t>
+          <t>Harsha Chhina (Abadi Ucha Qila)</t>
         </is>
       </c>
       <c r="E154" s="4" t="n">
@@ -17555,12 +17555,12 @@
       </c>
       <c r="C155" s="7" t="inlineStr">
         <is>
-          <t>ਝੰਜੋਟੀ</t>
+          <t>ਕੋਟਲਾ ਡੂਮ</t>
         </is>
       </c>
       <c r="D155" s="7" t="inlineStr">
         <is>
-          <t>Jhanjoti</t>
+          <t>Kotla Doom</t>
         </is>
       </c>
       <c r="E155" s="8" t="n">
@@ -17596,12 +17596,12 @@
       </c>
       <c r="C156" s="3" t="inlineStr">
         <is>
-          <t>ਪੱਧਰੀ</t>
+          <t>ਬੋਪਾਰਾਏ ਕਲਾਂ</t>
         </is>
       </c>
       <c r="D156" s="3" t="inlineStr">
         <is>
-          <t>Paddhari</t>
+          <t>Bopa Rai Kalan</t>
         </is>
       </c>
       <c r="E156" s="4" t="n">
@@ -17637,12 +17637,12 @@
       </c>
       <c r="C157" s="7" t="inlineStr">
         <is>
-          <t>ਸੈਦਪੁਰ</t>
+          <t>ਰਾਜਾ ਸਾਂਸੀ</t>
         </is>
       </c>
       <c r="D157" s="7" t="inlineStr">
         <is>
-          <t>Saidpur</t>
+          <t>Raja Sansi</t>
         </is>
       </c>
       <c r="E157" s="8" t="n">
@@ -17678,12 +17678,12 @@
       </c>
       <c r="C158" s="3" t="inlineStr">
         <is>
-          <t>ਭੀਲੇਵਾਲ ਪੱਕਾ</t>
+          <t>ਵੜਿਆਹ</t>
         </is>
       </c>
       <c r="D158" s="3" t="inlineStr">
         <is>
-          <t>Bhilewal Pakka</t>
+          <t>Waryah</t>
         </is>
       </c>
       <c r="E158" s="4" t="n">
@@ -17719,12 +17719,12 @@
       </c>
       <c r="C159" s="7" t="inlineStr">
         <is>
-          <t>ਲੇਪੀ ਗੁੱਜਰ</t>
+          <t>ਕੱਕੜ</t>
         </is>
       </c>
       <c r="D159" s="7" t="inlineStr">
         <is>
-          <t>Lepi Gujjar</t>
+          <t>Kakkar</t>
         </is>
       </c>
       <c r="E159" s="8" t="n">
@@ -17760,12 +17760,12 @@
       </c>
       <c r="C160" s="3" t="inlineStr">
         <is>
-          <t>ਕਮਾਸਕੇ + ਖਿਜਰਪੁਰਾ</t>
+          <t>ਸ਼ਾਹੂਰਾ</t>
         </is>
       </c>
       <c r="D160" s="3" t="inlineStr">
         <is>
-          <t>Kamaske + Khijarpura</t>
+          <t>Shahura</t>
         </is>
       </c>
       <c r="E160" s="4" t="n">
@@ -17801,12 +17801,12 @@
       </c>
       <c r="C161" s="7" t="inlineStr">
         <is>
-          <t>ਵਾਰਡ ਨੰ:7 ਰਾਜਾਸਾਂਸੀ ਮੁਹੱਲਾ ਸ੍ਰੀ ਪ੍ਰੀਤਮ ਸਿੰਘ ਗਲੀ ਬਜਾਜਾਂ ਵਾਲੀ ਮੇਨ ਬਜਾਰ + ਵਾਰਡ ਨੰ:7 ਮੇਨ ਬਜਾਰ ਸਾਹਮਣੇ ਗੁਰਦੁਆਰਾ ਸਿੰਘ ਸਭਾ + ਵਾਰਡ ਨੰ:7 ਮੁਹੱਲਾ ਸ੍ਰੀ ਪ੍ਰੀਤਮ ਸਿੰਘ ਗਲੀ ਲੇਹੇ ਵਾਲੀ + ਵਾਰਡ ਨੰ:7 ਮੁਹੱਲਾ ਪ੍ਰੀਤਮ ਸਿੰਘ ਗਲੀ ਲੇਹੇ ਵਾਲੀ + ਵਾਰਡ ਨੰ:7 ਗਲੀ ਸਹਿਜਾਦਾ + ਵਾਰਡ ਨੰ:7 ਗਲੀ ਲੇਹੇ ਵਾਲੀ + ਓਵਰਸੀਜ਼ ਇਲੈਕਟਰ</t>
+          <t>ਰਾਜਾ ਸਾਂਸੀ</t>
         </is>
       </c>
       <c r="D161" s="7" t="inlineStr">
         <is>
-          <t>Ward No: 7 Rajasansi Muhalla Sri Pritam Singh Gali Bajaja Wali Main Bazar + Ward No: 7 Main Bazar Sahamne Gurdwara Singh Sabha + Ward No: 7 Muhalla Sri Pritam Singh Gali Lehe Wali + Ward No: 7 Muhalla Pritam Singh Gali Lehe Wali + Ward No: 7 Gali Sahzada + Ward No: 7 Gali Lehe Wali + Overseas Elector</t>
+          <t>Raja Sansi</t>
         </is>
       </c>
       <c r="E161" s="8" t="n">
@@ -17842,12 +17842,12 @@
       </c>
       <c r="C162" s="3" t="inlineStr">
         <is>
-          <t>ਛੀਨਾ ਕਰਮ ਸਿੰਘ</t>
+          <t>ਈਸਾਪੁਰ</t>
         </is>
       </c>
       <c r="D162" s="3" t="inlineStr">
         <is>
-          <t>Chhina Karam Singh</t>
+          <t>Isapur</t>
         </is>
       </c>
       <c r="E162" s="4" t="n">
@@ -17883,12 +17883,12 @@
       </c>
       <c r="C163" s="7" t="inlineStr">
         <is>
-          <t>ਚੋਗਾਵਾਂ</t>
+          <t>ਠੱਠੀ</t>
         </is>
       </c>
       <c r="D163" s="7" t="inlineStr">
         <is>
-          <t>Chogawan</t>
+          <t>Thathi</t>
         </is>
       </c>
       <c r="E163" s="8" t="n">
@@ -17924,12 +17924,12 @@
       </c>
       <c r="C164" s="3" t="inlineStr">
         <is>
-          <t>ਕੱਕੜ</t>
+          <t>ਪੰਡੋਰੀ</t>
         </is>
       </c>
       <c r="D164" s="3" t="inlineStr">
         <is>
-          <t>Kakkar</t>
+          <t>Pandori</t>
         </is>
       </c>
       <c r="E164" s="4" t="n">
@@ -17965,12 +17965,12 @@
       </c>
       <c r="C165" s="7" t="inlineStr">
         <is>
-          <t>ਲੇਪੋਕੇ</t>
+          <t>ਭਾਗੂਪੁਰ ਉਤਾੜ</t>
         </is>
       </c>
       <c r="D165" s="7" t="inlineStr">
         <is>
-          <t>Lepoke</t>
+          <t>Bhagupur Utarh</t>
         </is>
       </c>
       <c r="E165" s="8" t="n">
@@ -18006,12 +18006,12 @@
       </c>
       <c r="C166" s="3" t="inlineStr">
         <is>
-          <t>ਚੋਗਾਵਾਂ</t>
+          <t>ਤਪਿਆਲਾ</t>
         </is>
       </c>
       <c r="D166" s="3" t="inlineStr">
         <is>
-          <t>Chogawan</t>
+          <t>Tapiala</t>
         </is>
       </c>
       <c r="E166" s="4" t="n">
@@ -18047,12 +18047,12 @@
       </c>
       <c r="C167" s="7" t="inlineStr">
         <is>
-          <t>ਭੀਲੇਵਾਲ ਕਕੇਜੀ</t>
+          <t>ਚੂਚਕਵਾਲ</t>
         </is>
       </c>
       <c r="D167" s="7" t="inlineStr">
         <is>
-          <t>Bhilewal Kakeji</t>
+          <t>Chuchakwal</t>
         </is>
       </c>
       <c r="E167" s="8" t="n">
@@ -18088,12 +18088,12 @@
       </c>
       <c r="C168" s="3" t="inlineStr">
         <is>
-          <t>ਕੱਕੜ</t>
+          <t>ਧਾਰੀਵਾਲ</t>
         </is>
       </c>
       <c r="D168" s="3" t="inlineStr">
         <is>
-          <t>Kakkar</t>
+          <t>Dhariwal</t>
         </is>
       </c>
       <c r="E168" s="4" t="n">
@@ -18129,12 +18129,12 @@
       </c>
       <c r="C169" s="7" t="inlineStr">
         <is>
-          <t>ਬੱਚੀਵਿੰਡ</t>
+          <t>ਸ਼ਾਹੂਰਾ</t>
         </is>
       </c>
       <c r="D169" s="7" t="inlineStr">
         <is>
-          <t>Bachhiwind</t>
+          <t>Shahura</t>
         </is>
       </c>
       <c r="E169" s="8" t="n">
@@ -18170,12 +18170,12 @@
       </c>
       <c r="C170" s="3" t="inlineStr">
         <is>
-          <t>ਕੋਟਲਾ ਸੁਰਾਜ ਲੋਹਾਰ + ਜੈ ਰਾਮ ਕੋਟ</t>
+          <t>ਕੋਟਲੀ ਖੇੜਾ</t>
         </is>
       </c>
       <c r="D170" s="3" t="inlineStr">
         <is>
-          <t>Kotla Suraj Lohar + Jai Ram Kot</t>
+          <t>Kotli Khera</t>
         </is>
       </c>
       <c r="E170" s="4" t="n">
@@ -18211,12 +18211,12 @@
       </c>
       <c r="C171" s="7" t="inlineStr">
         <is>
-          <t>ਲੱਲਾ ਅਫਗਾਨਾ</t>
+          <t>ਹਰਸ਼ਾ ਛੀਨਾ (ਅਬਾਦੀ ਕੁੱਕੜਾਂਵਾਲਾ)</t>
         </is>
       </c>
       <c r="D171" s="7" t="inlineStr">
         <is>
-          <t>Lalla Afgana</t>
+          <t>Harsha Chhina (Abadi Kukkranwala)</t>
         </is>
       </c>
       <c r="E171" s="8" t="n">
@@ -18252,12 +18252,12 @@
       </c>
       <c r="C172" s="3" t="inlineStr">
         <is>
-          <t>ਵਣੀਏਕੇ</t>
+          <t>ਛਵਿੰਡਾ ਕਲਾਂ</t>
         </is>
       </c>
       <c r="D172" s="3" t="inlineStr">
         <is>
-          <t>Wanieke</t>
+          <t>Chawinda Kalan</t>
         </is>
       </c>
       <c r="E172" s="4" t="n">
@@ -18293,12 +18293,12 @@
       </c>
       <c r="C173" s="7" t="inlineStr">
         <is>
-          <t>ਜੱਸ</t>
+          <t>ਚੱਕ ਕਮਾਲ ਖ਼ਾਨ</t>
         </is>
       </c>
       <c r="D173" s="7" t="inlineStr">
         <is>
-          <t>Jass</t>
+          <t>Chakk Kamal Khan</t>
         </is>
       </c>
       <c r="E173" s="8" t="n">
@@ -18334,12 +18334,12 @@
       </c>
       <c r="C174" s="3" t="inlineStr">
         <is>
-          <t>ਈਸਾਪੁਰ</t>
+          <t>ਉਮਰਪੁਰਾ</t>
         </is>
       </c>
       <c r="D174" s="3" t="inlineStr">
         <is>
-          <t>Isapur</t>
+          <t>Umarpura</t>
         </is>
       </c>
       <c r="E174" s="4" t="n">
@@ -18375,12 +18375,12 @@
       </c>
       <c r="C175" s="7" t="inlineStr">
         <is>
-          <t>ਓਠੀਆਂ</t>
+          <t>ਮਹਿਮਦਪੁਰਾ</t>
         </is>
       </c>
       <c r="D175" s="7" t="inlineStr">
         <is>
-          <t>Othian</t>
+          <t>Mehmadpura</t>
         </is>
       </c>
       <c r="E175" s="8" t="n">
@@ -18416,12 +18416,12 @@
       </c>
       <c r="C176" s="3" t="inlineStr">
         <is>
-          <t>ਜਸਤਰਵਾਲ</t>
+          <t>ਬੋਹਲੀਆ</t>
         </is>
       </c>
       <c r="D176" s="3" t="inlineStr">
         <is>
-          <t>Jastarwal</t>
+          <t>Bohlian</t>
         </is>
       </c>
       <c r="E176" s="4" t="n">
@@ -18457,12 +18457,12 @@
       </c>
       <c r="C177" s="7" t="inlineStr">
         <is>
-          <t>ਵਾਰਡ ਨੰ 4 ਨਵੀ ਕਲੋਨੀ ਸਾਹਮਣੇ ਏਅਰਪੋਰਟ ਰਾਜਾਸਾਂਸੀ + ਵਾਰਡ ਨੰ 4 ਅਜਨਾਲਾ ਰੋਡ ਏਅਰਪੋਰਟ ਕਲੋਨੀ ਰਾਜਾਸਾਂਸੀ + ਵਾਰਡ ਨੰ 4 ਅਜਨਾਲਾ ਰੋਡ ਏਅਰਪੋਰਟ ਕਲੋਨੀ ਰਾਜਾਸਾਂਸੀ</t>
+          <t>ਲੱਧੇਹ</t>
         </is>
       </c>
       <c r="D177" s="7" t="inlineStr">
         <is>
-          <t>Ward No 4 Navi Colony Sahamne Airport Rajasansi + Ward No 4 Ajnala Road Airport Colony Rajasansi + Ward No 4 Ajnala Road Airport Colony Rajasansi</t>
+          <t>Ladeh</t>
         </is>
       </c>
       <c r="E177" s="8" t="n">
@@ -18498,12 +18498,12 @@
       </c>
       <c r="C178" s="3" t="inlineStr">
         <is>
-          <t>ਬਹਿੜਵਾਲ</t>
+          <t>ਛਵਿੰਡਾ ਕਲਾਂ</t>
         </is>
       </c>
       <c r="D178" s="3" t="inlineStr">
         <is>
-          <t>Bahirwal</t>
+          <t>Chawinda Kalan</t>
         </is>
       </c>
       <c r="E178" s="4" t="n">
@@ -18539,12 +18539,12 @@
       </c>
       <c r="C179" s="7" t="inlineStr">
         <is>
-          <t>ਖਿਆਲਾ ਕਲਾਂ</t>
+          <t>ਬਾਬਾ ਮਾਈਕ ਸ਼ਾਹ ਕਾਲੋਨੀ</t>
         </is>
       </c>
       <c r="D179" s="7" t="inlineStr">
         <is>
-          <t>Khiala Kalan</t>
+          <t>Baba Mike Shah Colony</t>
         </is>
       </c>
       <c r="E179" s="8" t="n">
@@ -18580,12 +18580,12 @@
       </c>
       <c r="C180" s="3" t="inlineStr">
         <is>
-          <t>ਝੁੰਜ</t>
+          <t>ਭਿੰਡੀ ਔਲਖ ਖੁਰਦ</t>
         </is>
       </c>
       <c r="D180" s="3" t="inlineStr">
         <is>
-          <t>Jhunj</t>
+          <t>Bhindi Aulakh Khurd</t>
         </is>
       </c>
       <c r="E180" s="4" t="n">
@@ -18621,12 +18621,12 @@
       </c>
       <c r="C181" s="7" t="inlineStr">
         <is>
-          <t>ਚੋਗਾਵਾਂ</t>
+          <t>ਤਪਿਆਲਾ</t>
         </is>
       </c>
       <c r="D181" s="7" t="inlineStr">
         <is>
-          <t>Chogawan</t>
+          <t>Tapiala</t>
         </is>
       </c>
       <c r="E181" s="8" t="n">
@@ -18662,12 +18662,12 @@
       </c>
       <c r="C182" s="3" t="inlineStr">
         <is>
-          <t>ਮੁੱਧ</t>
+          <t>ਖੁਸੂਪੁਰਾ</t>
         </is>
       </c>
       <c r="D182" s="3" t="inlineStr">
         <is>
-          <t>Muddh</t>
+          <t>Khusupura</t>
         </is>
       </c>
       <c r="E182" s="4" t="n">
@@ -18703,12 +18703,12 @@
       </c>
       <c r="C183" s="7" t="inlineStr">
         <is>
-          <t>ਕੋਟਲਾ ਡੂਮ</t>
+          <t>ਰਾਜਾ ਸਾਂਸੀ</t>
         </is>
       </c>
       <c r="D183" s="7" t="inlineStr">
         <is>
-          <t>Kotla Doom</t>
+          <t>Raja Sansi</t>
         </is>
       </c>
       <c r="E183" s="8" t="n">
@@ -18744,12 +18744,12 @@
       </c>
       <c r="C184" s="3" t="inlineStr">
         <is>
-          <t>ਨੇਪਾਲ</t>
+          <t>ਰਾਏਪੁਰ ਖੁਰਦ</t>
         </is>
       </c>
       <c r="D184" s="3" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Raipur Khurd</t>
         </is>
       </c>
       <c r="E184" s="4" t="n">
@@ -18785,12 +18785,12 @@
       </c>
       <c r="C185" s="7" t="inlineStr">
         <is>
-          <t>ਮੋੜੇ</t>
+          <t>ਚੋਗਾਵਾਂ</t>
         </is>
       </c>
       <c r="D185" s="7" t="inlineStr">
         <is>
-          <t>More</t>
+          <t>Chogawan</t>
         </is>
       </c>
       <c r="E185" s="8" t="n">
@@ -18826,12 +18826,12 @@
       </c>
       <c r="C186" s="3" t="inlineStr">
         <is>
-          <t>ਭਿੱਟੇਵੱਡ</t>
+          <t>ਲੱਲਾ ਅਫ਼ਗ਼ਾਨਾ</t>
         </is>
       </c>
       <c r="D186" s="3" t="inlineStr">
         <is>
-          <t>Bhittewad</t>
+          <t>Lalla Afgana</t>
         </is>
       </c>
       <c r="E186" s="4" t="n">
@@ -18867,12 +18867,12 @@
       </c>
       <c r="C187" s="7" t="inlineStr">
         <is>
-          <t>ਬਲੱਗਣ</t>
+          <t>ਰਾਜਾ ਸਾਂਸੀ</t>
         </is>
       </c>
       <c r="D187" s="7" t="inlineStr">
         <is>
-          <t>Balaggan</t>
+          <t>Raja Sansi</t>
         </is>
       </c>
       <c r="E187" s="8" t="n">
@@ -18908,12 +18908,12 @@
       </c>
       <c r="C188" s="3" t="inlineStr">
         <is>
-          <t>ਕੁੱਤੀਵਾਲ</t>
+          <t>ਕੋਟਲੀ ਦੁਸੰਧੀ</t>
         </is>
       </c>
       <c r="D188" s="3" t="inlineStr">
         <is>
-          <t>Kuttiwal</t>
+          <t>Kotli Dosandhi</t>
         </is>
       </c>
       <c r="E188" s="4" t="n">
@@ -18949,12 +18949,12 @@
       </c>
       <c r="C189" s="7" t="inlineStr">
         <is>
-          <t>ਬਰਾੜ</t>
+          <t>ਬੋਪਾਰਾਏ ਬਾਜ ਸਿੰਘ</t>
         </is>
       </c>
       <c r="D189" s="7" t="inlineStr">
         <is>
-          <t>Brar</t>
+          <t>Bopa Rai Baj Singh</t>
         </is>
       </c>
       <c r="E189" s="8" t="n">
@@ -18990,12 +18990,12 @@
       </c>
       <c r="C190" s="3" t="inlineStr">
         <is>
-          <t>ਹਰਸ਼ਾ ਛੀਨਾ (ਅਬਾਦੀ ਉੱਚਾ ਕਿਲਾ)</t>
+          <t>ਹਰਸ਼ਾ ਛੀਨਾ (ਅਬਾਦੀ ਸਬਾਜਪੁਰ)</t>
         </is>
       </c>
       <c r="D190" s="3" t="inlineStr">
         <is>
-          <t>Harsha Chhina (Abadi Ucha Kila)</t>
+          <t>Harsha Chhina (Abadi Sabajpur)</t>
         </is>
       </c>
       <c r="E190" s="4" t="n">
@@ -19031,12 +19031,12 @@
       </c>
       <c r="C191" s="7" t="inlineStr">
         <is>
-          <t>ਖੁਸ਼ਪੁਰਾ + ਹਸਨਪੁਰਾ</t>
+          <t>ਕੋਟ ਸਿੱਧੂ</t>
         </is>
       </c>
       <c r="D191" s="7" t="inlineStr">
         <is>
-          <t>Khushpura + Hasanpura</t>
+          <t>Kot Sidhu</t>
         </is>
       </c>
       <c r="E191" s="8" t="n">
@@ -19072,12 +19072,12 @@
       </c>
       <c r="C192" s="3" t="inlineStr">
         <is>
-          <t>ਵਰਿਆਹ</t>
+          <t>ਤੱਲਾ</t>
         </is>
       </c>
       <c r="D192" s="3" t="inlineStr">
         <is>
-          <t>Wariah</t>
+          <t>Tallah</t>
         </is>
       </c>
       <c r="E192" s="4" t="n">
@@ -19113,12 +19113,12 @@
       </c>
       <c r="C193" s="7" t="inlineStr">
         <is>
-          <t>ਓਠੀਆਂ + ਰੱਖ ਓਠੀਆਂ</t>
+          <t>ਜੱਜੇ</t>
         </is>
       </c>
       <c r="D193" s="7" t="inlineStr">
         <is>
-          <t>Othian + Rakh Othian</t>
+          <t>Jajje</t>
         </is>
       </c>
       <c r="E193" s="8" t="n">
@@ -19154,12 +19154,12 @@
       </c>
       <c r="C194" s="3" t="inlineStr">
         <is>
-          <t>ਭੱਗੂਪੁਰ ਉਤਾੜ + ਛੰਨਾ</t>
+          <t>ਅਵਾਨ ਲੱਖਾ ਸਿੰਘ</t>
         </is>
       </c>
       <c r="D194" s="3" t="inlineStr">
         <is>
-          <t>Bhaggupur Utar + Chhanna</t>
+          <t>Awan Lakha Singh</t>
         </is>
       </c>
       <c r="E194" s="4" t="n">
@@ -19195,12 +19195,12 @@
       </c>
       <c r="C195" s="7" t="inlineStr">
         <is>
-          <t>ਕੋਹਾਲੀ</t>
+          <t>ਬੱਗਾ ਖੁਰਦ</t>
         </is>
       </c>
       <c r="D195" s="7" t="inlineStr">
         <is>
-          <t>Kohali</t>
+          <t>Bagga Khurd</t>
         </is>
       </c>
       <c r="E195" s="8" t="n">
@@ -19236,12 +19236,12 @@
       </c>
       <c r="C196" s="3" t="inlineStr">
         <is>
-          <t>ਸਾਰੰਗੜਾ</t>
+          <t>ਪੰਜੂ ਰਾਏ</t>
         </is>
       </c>
       <c r="D196" s="3" t="inlineStr">
         <is>
-          <t>Sarangra</t>
+          <t>Panju Rai</t>
         </is>
       </c>
       <c r="E196" s="4" t="n">
@@ -19277,12 +19277,12 @@
       </c>
       <c r="C197" s="7" t="inlineStr">
         <is>
-          <t>ਨਵਾ ਜੀਵਨ + ਨਥੂਪੁਰਾ</t>
+          <t>ਕੱਕੜ</t>
         </is>
       </c>
       <c r="D197" s="7" t="inlineStr">
         <is>
-          <t>Nawa Jeevan + Nathupura</t>
+          <t>Kakkar</t>
         </is>
       </c>
       <c r="E197" s="8" t="n">
@@ -19318,12 +19318,12 @@
       </c>
       <c r="C198" s="3" t="inlineStr">
         <is>
-          <t>ਲੇਪੋਕੇ</t>
+          <t>ਪ੍ਰੀਤ ਨਗਰ</t>
         </is>
       </c>
       <c r="D198" s="3" t="inlineStr">
         <is>
-          <t>Lepoke</t>
+          <t>Preet Nagar</t>
         </is>
       </c>
       <c r="E198" s="4" t="n">
@@ -19400,12 +19400,12 @@
       </c>
       <c r="C200" s="3" t="inlineStr">
         <is>
-          <t>ਮਿਆਦੀ ਕਲਾਂ + ਕੋਟਲੀ ਮੁਗਲਾਂ</t>
+          <t>ਕੋਟਲੀ ਕੋਰੋਟਾਣਾ</t>
         </is>
       </c>
       <c r="D200" s="3" t="inlineStr">
         <is>
-          <t>Miadi Kalan + Kotli Muglan</t>
+          <t>Kotli Korotana</t>
         </is>
       </c>
       <c r="E200" s="4" t="n">
@@ -19441,12 +19441,12 @@
       </c>
       <c r="C201" s="7" t="inlineStr">
         <is>
-          <t>ਵਾਰਡ ਨੰ.10 ਗਲੀ ਸੰਭ ਵਾਲੀ + ਵਾਰਡ ਨੰ.10 ਗਲੀ ਘਾਹ ਮੰਡੀ + ਵਾਰਡ ਨੰ.10 ਗਲੀ ਜੈਲਦਾਰਾ ਵਾਲੀ</t>
+          <t>ਰਾਜਾ ਸਾਂਸੀ</t>
         </is>
       </c>
       <c r="D201" s="7" t="inlineStr">
         <is>
-          <t>Ward No. 10 Gali Sambh Wali + Ward No. 10 Gali Ghah Mandi + Ward No. 10 Gali Zaildara Wali</t>
+          <t>Raja Sansi</t>
         </is>
       </c>
       <c r="E201" s="8" t="n">
@@ -19482,12 +19482,12 @@
       </c>
       <c r="C202" s="3" t="inlineStr">
         <is>
-          <t>ਡੱਗ</t>
+          <t>ਸੈਦਪੁਰ ਕਲਾਂ</t>
         </is>
       </c>
       <c r="D202" s="3" t="inlineStr">
         <is>
-          <t>Dagg</t>
+          <t>Saidpur Kalan</t>
         </is>
       </c>
       <c r="E202" s="4" t="n">
@@ -19523,12 +19523,12 @@
       </c>
       <c r="C203" s="7" t="inlineStr">
         <is>
-          <t>ਕੋਟਲੀ ਸੱਕਾ</t>
+          <t>ਮੌੜੇ</t>
         </is>
       </c>
       <c r="D203" s="7" t="inlineStr">
         <is>
-          <t>Kotli Sakka</t>
+          <t>Maure</t>
         </is>
       </c>
       <c r="E203" s="8" t="n">
@@ -19564,12 +19564,12 @@
       </c>
       <c r="C204" s="3" t="inlineStr">
         <is>
-          <t>ਵਾਰਡ ਨੰ. 11 ਗਲੀ ਘੁਮਿਆਰਾਂ ਵਾਲੀ + ਵਾਰਡ ਨੰ. 11 ਗਲੀ ਜੈਲਦਾਰਾਂ ਵਾਲੀ + ਵਾਰਡ ਨੰ. 11 ਗਲੀ ਗੁਰਦੁਆਰਾ ਕਲਗੀਧਰ + ਵਾਰਡ ਨੰ. 11 ਮੇਨ ਬਜਾਰ ਗੁਰਦੁਆਰਾ ਕਲਗੀਧਰ + ਵਾਰਡ ਨੰ.11 ਮੇਨ ਬਜਾਰ + ਵਾਰਡ ਨੰ.11 ਗਲੀ ਵਜੀਰਾ ਵਾਲੀ + ਵਾਰਡ ਨੰ.11 ਮੇਨ ਬਜਾਰ + ਵਾਰਡ ਨੰ.11 ਮੇਨ ਬਜਾਰ</t>
+          <t>ਰਾਜਾ ਸਾਂਸੀ</t>
         </is>
       </c>
       <c r="D204" s="3" t="inlineStr">
         <is>
-          <t>Ward No. 11 Gali Ghumiara Wali + Ward No. 11 Gali Zaildara Wali + Ward No. 11 Gali Gurdwara Kalgidhar + Ward No. 11 Main Bazar Gurdwara Kalgidhar + Ward No. 11 Main Bazar + Ward No. 11 Gali Wajira Wali + Ward No. 11 Main Bazar + Ward No. 11 Main Bazar</t>
+          <t>Raja Sansi</t>
         </is>
       </c>
       <c r="E204" s="4" t="n">
@@ -19605,12 +19605,12 @@
       </c>
       <c r="C205" s="7" t="inlineStr">
         <is>
-          <t>ਖਿਆਲਾ ਕਲਾਂ</t>
+          <t>ਕਲੇਰ</t>
         </is>
       </c>
       <c r="D205" s="7" t="inlineStr">
         <is>
-          <t>Khiala Kalan</t>
+          <t>Kaler</t>
         </is>
       </c>
       <c r="E205" s="8" t="n">
@@ -19646,12 +19646,12 @@
       </c>
       <c r="C206" s="3" t="inlineStr">
         <is>
-          <t>ਉਡਰ</t>
+          <t>ਡਾਲਾ</t>
         </is>
       </c>
       <c r="D206" s="3" t="inlineStr">
         <is>
-          <t>Udar</t>
+          <t>Dala</t>
         </is>
       </c>
       <c r="E206" s="4" t="n">
@@ -19728,12 +19728,12 @@
       </c>
       <c r="C208" s="3" t="inlineStr">
         <is>
-          <t>ਵਿਹੜਾ + ਵਿਹੜਾ ਅਬਾਦੀ ਵਾਲਾ ਨੂਰੇਵਾਲ</t>
+          <t>ਦੁੱਗ ਡੋਗਰ</t>
         </is>
       </c>
       <c r="D208" s="3" t="inlineStr">
         <is>
-          <t>Vehra + Vehra Abadi Wala Nurewal</t>
+          <t>Dugg Dogar</t>
         </is>
       </c>
       <c r="E208" s="4" t="n">
@@ -19769,12 +19769,12 @@
       </c>
       <c r="C209" s="7" t="inlineStr">
         <is>
-          <t>ਹੇਤਮਪੁਰਾ</t>
+          <t>ਲੋਪੋਕੇ</t>
         </is>
       </c>
       <c r="D209" s="7" t="inlineStr">
         <is>
-          <t>Hetampura</t>
+          <t>Lopoke</t>
         </is>
       </c>
       <c r="E209" s="8" t="n">
@@ -19810,12 +19810,12 @@
       </c>
       <c r="C210" s="3" t="inlineStr">
         <is>
-          <t>ਬੱਗਾ ਕਲਾਂ</t>
+          <t>ਹਰਸ਼ਾ ਛੀਨਾ (ਅਬਾਦੀ ਵਿਚਲਾ ਕਿਲ੍ਹਾ)</t>
         </is>
       </c>
       <c r="D210" s="3" t="inlineStr">
         <is>
-          <t>Bagga Kalan</t>
+          <t>Harsha Chhina (Abadi Vichla Qila)</t>
         </is>
       </c>
       <c r="E210" s="4" t="n">
@@ -19851,12 +19851,12 @@
       </c>
       <c r="C211" s="7" t="inlineStr">
         <is>
-          <t>ਭਿੰਡੀ ਸੈਦਾਂ</t>
+          <t>ਕੁੱਤੀਵਾਲ</t>
         </is>
       </c>
       <c r="D211" s="7" t="inlineStr">
         <is>
-          <t>Bhindi Saidan</t>
+          <t>Kuttiwal</t>
         </is>
       </c>
       <c r="E211" s="8" t="n">
@@ -19892,12 +19892,12 @@
       </c>
       <c r="C212" s="3" t="inlineStr">
         <is>
-          <t>ਸ਼ਹੂਰਾ</t>
+          <t>ਚੇਲੇਕੇ</t>
         </is>
       </c>
       <c r="D212" s="3" t="inlineStr">
         <is>
-          <t>Shahura</t>
+          <t>Cheleki</t>
         </is>
       </c>
       <c r="E212" s="4" t="n">
@@ -19933,12 +19933,12 @@
       </c>
       <c r="C213" s="7" t="inlineStr">
         <is>
-          <t>ਭੱਗੂਪੁਰ ਬੇਟ</t>
+          <t>ਦੁੱਗ</t>
         </is>
       </c>
       <c r="D213" s="7" t="inlineStr">
         <is>
-          <t>Bhaggupur Bet</t>
+          <t>Dugg</t>
         </is>
       </c>
       <c r="E213" s="8" t="n">
@@ -19974,12 +19974,12 @@
       </c>
       <c r="C214" s="3" t="inlineStr">
         <is>
-          <t>ਨੰਗਲ ਤੋਲਾ</t>
+          <t>ਬਲਾਗਣ ਸਿੱਧੂ</t>
         </is>
       </c>
       <c r="D214" s="3" t="inlineStr">
         <is>
-          <t>Nangal Tola</t>
+          <t>Balagan Sidhu</t>
         </is>
       </c>
       <c r="E214" s="4" t="n">
@@ -20015,12 +20015,12 @@
       </c>
       <c r="C215" s="7" t="inlineStr">
         <is>
-          <t>ਚੱਕ ਅੱਲਾ ਬਖਸ਼</t>
+          <t>ਗੱਗੜਮੱਲ</t>
         </is>
       </c>
       <c r="D215" s="7" t="inlineStr">
         <is>
-          <t>Chak Alla Baksh</t>
+          <t>Gagarmal</t>
         </is>
       </c>
       <c r="E215" s="8" t="n">
@@ -20056,12 +20056,12 @@
       </c>
       <c r="C216" s="3" t="inlineStr">
         <is>
-          <t>ਗਾਗਰਾਮਲ</t>
+          <t>ਲੇਲੀਅਨ</t>
         </is>
       </c>
       <c r="D216" s="3" t="inlineStr">
         <is>
-          <t>Gagramal</t>
+          <t>Lelian</t>
         </is>
       </c>
       <c r="E216" s="4" t="n">
@@ -20097,12 +20097,12 @@
       </c>
       <c r="C217" s="7" t="inlineStr">
         <is>
-          <t>ਗੁਲਗੜ + ਨਿਆਮਤਾਬਾਦ</t>
+          <t>ਗੁਲਗੜ੍ਹ</t>
         </is>
       </c>
       <c r="D217" s="7" t="inlineStr">
         <is>
-          <t>Gulgarh + Niamatabad</t>
+          <t>Gulgarh</t>
         </is>
       </c>
       <c r="E217" s="8" t="n">
@@ -20138,12 +20138,12 @@
       </c>
       <c r="C218" s="3" t="inlineStr">
         <is>
-          <t>ਟਪਿਆਲਾ</t>
+          <t>ਜੋਏਕੇ</t>
         </is>
       </c>
       <c r="D218" s="3" t="inlineStr">
         <is>
-          <t>Tapiala</t>
+          <t>Joeke</t>
         </is>
       </c>
       <c r="E218" s="4" t="n">
@@ -20179,12 +20179,12 @@
       </c>
       <c r="C219" s="7" t="inlineStr">
         <is>
-          <t>ਮੇਤਲਾ</t>
+          <t>ਪੰਜੂ ਕਲਾਲ</t>
         </is>
       </c>
       <c r="D219" s="7" t="inlineStr">
         <is>
-          <t>Metla</t>
+          <t>Panju Kalal</t>
         </is>
       </c>
       <c r="E219" s="8" t="n">
@@ -20220,12 +20220,12 @@
       </c>
       <c r="C220" s="3" t="inlineStr">
         <is>
-          <t>ਵਾਰਡ ਨੰ.6 ਮੁਹੱਲਾ ਮੰਦਰ ਦੇਵੀ ਦੁਆਰ + ਵਾਰਡ ਨੰ.6 ਮੁਹੱਲਾ ਗਾਂਧੀ ਨਗਰ + ਵਾਰਡ ਨੰ.6 ਕਲੋਨੀ ਬਾਬਾ ਜਵੰਦ ਸਿੰਘ ਖੂਹ ਚੂਹੜ ਸਿੰਘ ਵਾਲਾ</t>
+          <t>ਰਾਜਾ ਸਾਂਸੀ</t>
         </is>
       </c>
       <c r="D220" s="3" t="inlineStr">
         <is>
-          <t>Ward No. 6 Muhalla Mandir Devi Dwar + Ward No. 6 Muhalla Gandhi Nagar + Ward No. 6 Colony Baba Jawand Singh Khooh Chuhar Singh Wala</t>
+          <t>Raja Sansi</t>
         </is>
       </c>
       <c r="E220" s="4" t="n">
@@ -20261,12 +20261,12 @@
       </c>
       <c r="C221" s="7" t="inlineStr">
         <is>
-          <t>ਕੱਕੜ</t>
+          <t>ਚੱਕ ਅੱਲਾ ਬਖ਼ਸ਼</t>
         </is>
       </c>
       <c r="D221" s="7" t="inlineStr">
         <is>
-          <t>Kakkar</t>
+          <t>Chakk Alla Bakhsh</t>
         </is>
       </c>
       <c r="E221" s="8" t="n">
@@ -20302,12 +20302,12 @@
       </c>
       <c r="C222" s="3" t="inlineStr">
         <is>
-          <t>ਵਾਰਡ ਨੰ 8 ਮੁਹੱਲਾ ਠਾਕਰ ਸਿੰਘ ਗਲੀ ਘੁਮਿਆਰਾਂ ਵਾਲੀ + ਵਾਰਡ ਨੰ 8 ਮੁਹੱਲਾ ਠਾਕਰ ਸਿੰਘ ਗਲੀ ਘੁਮਿਆਰਾਂ ਵਾਲੀ + ਵਾਰਡ ਨੰ 8 ਮੁਹੱਲਾ ਠਾਕਰ ਸਿੰਘ ਗਲੀ ਘੁਮਿਆਰਾਂ ਵਾਲੀ</t>
+          <t>ਮੁਗਲਾਨੀ ਕੋਟ</t>
         </is>
       </c>
       <c r="D222" s="3" t="inlineStr">
         <is>
-          <t>Ward No 8 Muhalla Thakar Singh Gali Ghumiara Wali + Ward No 8 Muhalla Thakar Singh Gali Ghumiara Wali + Ward No 8 Muhalla Thakar Singh Gali Ghumiara Wali</t>
+          <t>Muglani Kot</t>
         </is>
       </c>
       <c r="E222" s="4" t="n">
@@ -20343,12 +20343,12 @@
       </c>
       <c r="C223" s="7" t="inlineStr">
         <is>
-          <t>ਕੋਹਾਲਾ (ਖੱਬਾ ਪਾਸਾ)</t>
+          <t>ਲਾਂਵੇ</t>
         </is>
       </c>
       <c r="D223" s="7" t="inlineStr">
         <is>
-          <t>Kohala (Khabba Pasa)</t>
+          <t>Lanven</t>
         </is>
       </c>
       <c r="E223" s="8" t="n">
@@ -20387,7 +20387,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:F20"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="2" max="2"/>
     <col width="36" customWidth="1" min="3" max="3"/>
@@ -20509,7 +20509,7 @@
     <row r="9" ht="22" customHeight="1">
       <c r="B9" s="27" t="inlineStr">
         <is>
-          <t>Mukhwinder Singh Mahal</t>
+          <t>Mukhwinder Singh</t>
         </is>
       </c>
       <c r="C9" s="27" t="inlineStr">
@@ -20638,7 +20638,7 @@
       </c>
       <c r="C18" s="33" t="inlineStr">
         <is>
-          <t>Booth 39: ਮੰਡਿਆਵਾਲਾ (941 votes)</t>
+          <t>Booth 39: ਮੰਜ (941 votes)</t>
         </is>
       </c>
     </row>
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C19" s="33" t="inlineStr">
         <is>
-          <t>Booth 143: ਕੋਹਾਲਾ (ਖੱਬਾ ਪਾਸਾ) (210 votes)</t>
+          <t>Booth 143: ਲਾਂਵੇ (210 votes)</t>
         </is>
       </c>
     </row>
